--- a/Plan/Table/TestData/00.LocaleData.xlsx
+++ b/Plan/Table/TestData/00.LocaleData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\인디\FluffyDisdog\Plan\Table\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HOME\Documents\프로젝트 Git\Plan\Table\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B55EC52A-1288-49F5-BBB3-8F664680814E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6246342F-B1D6-4474-BEE9-1E1542233D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9C3C76AC-0051-46F4-BB86-857184325AA2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5A13723D-2757-45BA-81CA-7CBE4435BD60}"/>
   </bookViews>
   <sheets>
     <sheet name="00.LocaleData" sheetId="1" r:id="rId1"/>
@@ -27,19 +27,14 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="722">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="1071">
   <si>
     <t>key</t>
   </si>
@@ -56,1770 +51,2655 @@
     <t>삽</t>
   </si>
   <si>
+    <t>Shovel</t>
+  </si>
+  <si>
     <t>Card_Rake_Name</t>
   </si>
   <si>
     <t>갈퀴</t>
   </si>
   <si>
+    <t>Rake</t>
+  </si>
+  <si>
     <t>Card_Shovel_Enhanced_Name</t>
   </si>
   <si>
     <t>삽+</t>
   </si>
   <si>
+    <t>Shovel+</t>
+  </si>
+  <si>
     <t>Card_Rake_Enhanced_Name</t>
   </si>
   <si>
     <t>갈퀴+</t>
   </si>
   <si>
+    <t>Rake+</t>
+  </si>
+  <si>
     <t>Card_GoldenShovel_Name</t>
   </si>
   <si>
     <t>황금 삽</t>
   </si>
   <si>
+    <t>Golden Shovel</t>
+  </si>
+  <si>
     <t>Card_GoldenShovel_Enhanced_Name</t>
   </si>
   <si>
     <t>황금 삽+</t>
   </si>
   <si>
+    <t>Golden Shovel+</t>
+  </si>
+  <si>
     <t>Card_Axe_Name</t>
   </si>
   <si>
     <t>도끼</t>
   </si>
   <si>
+    <t>Axe</t>
+  </si>
+  <si>
     <t>Card_Axe_Enhanced_Name</t>
   </si>
   <si>
     <t>도끼+</t>
   </si>
   <si>
+    <t>Axe+</t>
+  </si>
+  <si>
     <t>Card_Cross Chisel_Name</t>
   </si>
   <si>
     <t>십자 끌</t>
   </si>
   <si>
+    <t>Cross Chisel</t>
+  </si>
+  <si>
     <t>Card_Cross Chisel_Enhanced_Name</t>
   </si>
   <si>
     <t>십자 끌+</t>
   </si>
   <si>
+    <t>Cross Chisel+</t>
+  </si>
+  <si>
     <t>Card_Pickaxe_Name</t>
   </si>
   <si>
     <t>곡괭이</t>
   </si>
   <si>
+    <t>Pickaxe</t>
+  </si>
+  <si>
     <t>Card_Pickaxe_Enhanced_Name</t>
   </si>
   <si>
     <t>곡괭이+</t>
   </si>
   <si>
+    <t>Pickaxe+</t>
+  </si>
+  <si>
     <t>Card_Slingshot_Name</t>
   </si>
   <si>
     <t>새총</t>
   </si>
   <si>
+    <t>Slingshot</t>
+  </si>
+  <si>
     <t>Card_Slingshot_Enhanced_Name</t>
   </si>
   <si>
     <t>새총+</t>
   </si>
   <si>
+    <t>Slingshot+</t>
+  </si>
+  <si>
     <t>Card_CornerCrushingHammer_Name</t>
   </si>
   <si>
     <t>모서리 파쇄 해머</t>
   </si>
   <si>
+    <t>Corner Crushing Hammer</t>
+  </si>
+  <si>
     <t>Card_CornerCrushingHammer_Enhanced_Name</t>
   </si>
   <si>
     <t>모서리 파쇄 해머+</t>
   </si>
   <si>
+    <t>Corner Crushing Hammer+</t>
+  </si>
+  <si>
     <t>Card_ConcentratedCrossDrill_Name</t>
   </si>
   <si>
     <t>집중형 십자 드릴</t>
   </si>
   <si>
+    <t>Concentrated Cross Drill</t>
+  </si>
+  <si>
     <t>Card_ConcentratedCrossDrill_Enhanced_Name</t>
   </si>
   <si>
     <t>집중형 십자 드릴+</t>
   </si>
   <si>
+    <t>Concentrated Cross Drill+</t>
+  </si>
+  <si>
     <t>Card_GoldenAxe_Name</t>
   </si>
   <si>
     <t>황금 도끼</t>
   </si>
   <si>
+    <t>Golden Axe</t>
+  </si>
+  <si>
     <t>Card_GoldenAxe_Enhanced_Name</t>
   </si>
   <si>
     <t>황금 도끼+</t>
   </si>
   <si>
+    <t>Golden Axe+</t>
+  </si>
+  <si>
     <t>Card_Large Scissors_Name</t>
   </si>
   <si>
     <t>대형 가위</t>
   </si>
   <si>
+    <t>Large Scissors</t>
+  </si>
+  <si>
     <t>Card_Large Scissors_Enhanced_Name</t>
   </si>
   <si>
     <t>대형 가위+</t>
   </si>
   <si>
+    <t>Large Scissors+</t>
+  </si>
+  <si>
     <t>Card_WeakeningNormal_Name</t>
   </si>
   <si>
     <t>약화 카드 - 일반</t>
   </si>
   <si>
+    <t>Weakening Normal</t>
+  </si>
+  <si>
     <t>Card_WeakeningRare_Name</t>
   </si>
   <si>
     <t>약화 카드 - 레어</t>
   </si>
   <si>
+    <t>Weakening Rare</t>
+  </si>
+  <si>
     <t>Card_WeakeningUnique_Name</t>
   </si>
   <si>
     <t>약화 카드 - 유니크</t>
   </si>
   <si>
+    <t>Weakening Unique</t>
+  </si>
+  <si>
     <t>Card_Bag_Name</t>
   </si>
   <si>
     <t>가방</t>
   </si>
   <si>
+    <t>Bag</t>
+  </si>
+  <si>
     <t>Card_ToolTransformation_Name</t>
   </si>
   <si>
     <t>도구 변형</t>
   </si>
   <si>
+    <t>Too lTransformation</t>
+  </si>
+  <si>
     <t>Card_ToolEnhancement_Name</t>
   </si>
   <si>
     <t>도구 강화</t>
   </si>
   <si>
+    <t>Tool Enhancement</t>
+  </si>
+  <si>
     <t>Card_AdventurerTorch_Name</t>
   </si>
   <si>
     <t>모험가의 횃불</t>
   </si>
   <si>
+    <t>Adventurer Torch</t>
+  </si>
+  <si>
     <t>Card_AdventurerTorch_Enhanced_Name</t>
   </si>
   <si>
     <t>모험가의 횃불+</t>
   </si>
   <si>
+    <t>Adventurer Torch+</t>
+  </si>
+  <si>
     <t>Card_HammerOfMemory_Name</t>
   </si>
   <si>
     <t>기억의 망치</t>
   </si>
   <si>
+    <t>Hammer of Memory</t>
+  </si>
+  <si>
     <t>Card_HammerOfMemory_Enhanced_Name</t>
   </si>
   <si>
     <t>기억의 망치+</t>
   </si>
   <si>
+    <t>Hammer of Memory+</t>
+  </si>
+  <si>
     <t>Card_RiftStartumAnalysis_Name</t>
   </si>
   <si>
     <t>균열 지층 분석</t>
   </si>
   <si>
+    <t>Rift Startum Analysis</t>
+  </si>
+  <si>
     <t>Card_RiftStartumAnalysis_Enhanced_Name</t>
   </si>
   <si>
     <t>균열 지층 분석+</t>
   </si>
   <si>
+    <t>Rift Startum Analysis+</t>
+  </si>
+  <si>
     <t>Card_Novice_Wand_Name</t>
   </si>
   <si>
     <t>견습 지팡이</t>
   </si>
   <si>
+    <t>Novice Wand</t>
+  </si>
+  <si>
     <t>Card_Novice_Wand_Enhanced_Name</t>
   </si>
   <si>
     <t>견습 지팡이+</t>
   </si>
   <si>
+    <t>Novice_Wand+</t>
+  </si>
+  <si>
     <t>Card_Mana_Arrow_Name</t>
   </si>
   <si>
     <t>마력 화살</t>
   </si>
   <si>
+    <t>Mana Arrow</t>
+  </si>
+  <si>
     <t>Card_Mana_Arrow_Enhanced_Name</t>
   </si>
   <si>
     <t>마력 화살+</t>
   </si>
   <si>
+    <t>Mana Arrow+</t>
+  </si>
+  <si>
     <t>Card_Sparkle_Name</t>
   </si>
   <si>
     <t>번뜩임</t>
   </si>
   <si>
+    <t>Sparkle</t>
+  </si>
+  <si>
     <t>Card_Sparkle_Enhanced_Name</t>
   </si>
   <si>
     <t>번뜩임+</t>
   </si>
   <si>
+    <t>Sparkle+</t>
+  </si>
+  <si>
     <t>Card_Mana_Pierce_Name</t>
   </si>
   <si>
     <t>마력 찌르기</t>
   </si>
   <si>
+    <t>Mana Pierce</t>
+  </si>
+  <si>
     <t>Card_Mana_Pierce_Enhanced_Name</t>
   </si>
   <si>
     <t>마력 찌르기+</t>
   </si>
   <si>
+    <t>Mana Pierce+</t>
+  </si>
+  <si>
     <t>Card_Magic_Spear_Name</t>
   </si>
   <si>
     <t>마력의 창</t>
   </si>
   <si>
+    <t>Magic Spear</t>
+  </si>
+  <si>
     <t>Card_Magic_Spear_Enhanced_Name</t>
   </si>
   <si>
     <t>마력의 창+</t>
   </si>
   <si>
+    <t>Magic Spear+</t>
+  </si>
+  <si>
     <t>Card_Magic_Slash_Name</t>
   </si>
   <si>
     <t>마력 베기</t>
   </si>
   <si>
+    <t>Magic Slash</t>
+  </si>
+  <si>
     <t>Card_Magic_Slash_Enhanced_Name</t>
   </si>
   <si>
     <t>마력 베기+</t>
   </si>
   <si>
+    <t>Magic Slash+</t>
+  </si>
+  <si>
     <t>Card_Magic_Sword_Name</t>
   </si>
   <si>
     <t>마력의 검</t>
   </si>
   <si>
+    <t>Magic Sword</t>
+  </si>
+  <si>
     <t>Card_Magic_Sword_Enhanced_Name</t>
   </si>
   <si>
     <t>마력의 검+</t>
   </si>
   <si>
+    <t>Magic Sword+</t>
+  </si>
+  <si>
     <t>Card_Magic_Claw_Name</t>
   </si>
   <si>
     <t>마력의 발톱</t>
   </si>
   <si>
+    <t>Magic Claw</t>
+  </si>
+  <si>
     <t>Card_Magic_Claw_Enhanced_Name</t>
   </si>
   <si>
     <t>마력의 발톱+</t>
   </si>
   <si>
+    <t>Magic Claw+</t>
+  </si>
+  <si>
     <t>Card_Magic_Cannon_Name</t>
   </si>
   <si>
     <t>마력 포탄</t>
   </si>
   <si>
+    <t>Magic Cannon</t>
+  </si>
+  <si>
     <t>Card_Magic_Cannon_Enhanced_Name</t>
   </si>
   <si>
     <t>마력 포탄+</t>
   </si>
   <si>
+    <t>Magic Cannon+</t>
+  </si>
+  <si>
     <t>Card_Frog_Name</t>
   </si>
   <si>
     <t>개구리</t>
   </si>
   <si>
+    <t>Frog</t>
+  </si>
+  <si>
     <t>Card_Frog_Enhanced_Name</t>
   </si>
   <si>
     <t>개구리+</t>
   </si>
   <si>
+    <t>Frog+</t>
+  </si>
+  <si>
     <t>Card_Inchant_Magic_Name</t>
   </si>
   <si>
     <t>마력 부여</t>
   </si>
   <si>
+    <t>Inchant Magic</t>
+  </si>
+  <si>
     <t>Card_Inchant_Magic_Enhanced_Name</t>
   </si>
   <si>
     <t>마력 부여+</t>
   </si>
   <si>
+    <t>Inchant Magic+</t>
+  </si>
+  <si>
     <t>Card_Ignite_Name</t>
   </si>
   <si>
     <t>발화</t>
   </si>
   <si>
+    <t>Ignite</t>
+  </si>
+  <si>
     <t>Card_Ignite_Enhanced_Name</t>
   </si>
   <si>
     <t>발화+</t>
   </si>
   <si>
+    <t>Ignite+</t>
+  </si>
+  <si>
     <t>Card_Flame_Explosion_Name</t>
   </si>
   <si>
     <t>화염 폭발</t>
   </si>
   <si>
+    <t>Flame Explosion</t>
+  </si>
+  <si>
     <t>Card_Flame_Explosion_Enhanced_Name</t>
   </si>
   <si>
     <t>화염 폭발+</t>
   </si>
   <si>
+    <t>Flame Explosion+</t>
+  </si>
+  <si>
     <t>Card_Ember_Name</t>
   </si>
   <si>
     <t>잔불</t>
   </si>
   <si>
+    <t>Ember</t>
+  </si>
+  <si>
     <t>Card_Ember_Enhanced_Name</t>
   </si>
   <si>
     <t>잔불+</t>
   </si>
   <si>
+    <t>Ember+</t>
+  </si>
+  <si>
     <t>Card_Flame_Wall_Name</t>
   </si>
   <si>
     <t>화염 벽</t>
   </si>
   <si>
+    <t>Flame Wall</t>
+  </si>
+  <si>
     <t>Card_Flame_Wall_Enhanced_Name</t>
   </si>
   <si>
     <t>화염 벽+</t>
   </si>
   <si>
+    <t>Flame Wall+</t>
+  </si>
+  <si>
     <t>Card_Chain_Ignition_Name</t>
   </si>
   <si>
     <t>연쇄 발화</t>
   </si>
   <si>
+    <t>Chain Ignition</t>
+  </si>
+  <si>
     <t>Card_Chain_Ignition_Enhanced_Name</t>
   </si>
   <si>
     <t>연쇄 발화+</t>
   </si>
   <si>
+    <t>Chain Ignition+</t>
+  </si>
+  <si>
     <t>Card_Volcano_Name</t>
   </si>
   <si>
     <t>볼케이노</t>
   </si>
   <si>
+    <t>Volcano</t>
+  </si>
+  <si>
     <t>Card_Volcano_Enhanced_Name</t>
   </si>
   <si>
     <t>볼케이노+</t>
   </si>
   <si>
+    <t>Volcano+</t>
+  </si>
+  <si>
     <t>Card_Freeze_Name</t>
   </si>
   <si>
     <t>냉각</t>
   </si>
   <si>
+    <t>Freeze</t>
+  </si>
+  <si>
     <t>Card_Freeze_Enhanced_Name</t>
   </si>
   <si>
     <t>냉각+</t>
   </si>
   <si>
+    <t>Freeze+</t>
+  </si>
+  <si>
     <t>Card_Frost_Blast_Name</t>
   </si>
   <si>
     <t>냉기 폭발</t>
   </si>
   <si>
+    <t>Frost Blast</t>
+  </si>
+  <si>
     <t>Card_Frost_Blast_Enhanced_Name</t>
   </si>
   <si>
     <t>냉기 폭발+</t>
   </si>
   <si>
+    <t>Frost Blast+</t>
+  </si>
+  <si>
     <t>Card_Spreading_Frost_Name</t>
   </si>
   <si>
     <t>퍼져나가는 냉기</t>
   </si>
   <si>
+    <t>Spreading Frost</t>
+  </si>
+  <si>
     <t>Card_Spreading_Frost_Enhanced_Name</t>
   </si>
   <si>
     <t>퍼져나가는 냉기+</t>
   </si>
   <si>
+    <t>Spreading Frost+</t>
+  </si>
+  <si>
     <t>Card_Ice_Sword_Name</t>
   </si>
   <si>
     <t>얼음 검</t>
   </si>
   <si>
+    <t>Ice Sword</t>
+  </si>
+  <si>
     <t>Card_Ice_Sword_Enhanced_Name</t>
   </si>
   <si>
     <t>얼음 검+</t>
   </si>
   <si>
+    <t>Ice Sword+</t>
+  </si>
+  <si>
     <t>Card_Ice_Spear_Name</t>
   </si>
   <si>
     <t>얼음 창</t>
   </si>
   <si>
+    <t>Ice Spear</t>
+  </si>
+  <si>
     <t>Card_Ice_Spear_Enhanced_Name</t>
   </si>
   <si>
     <t>얼음 창+</t>
   </si>
   <si>
+    <t>Ice Spear+</t>
+  </si>
+  <si>
     <t>Card_Ice_Arrow_Name</t>
   </si>
   <si>
     <t>얼음 화살</t>
   </si>
   <si>
+    <t>Ice Arrow</t>
+  </si>
+  <si>
     <t>Card_Ice_Arrow_Enhanced_Name</t>
   </si>
   <si>
     <t>얼음 화살+</t>
   </si>
   <si>
+    <t>Ice Arrow+</t>
+  </si>
+  <si>
     <t>Card_Current_Name</t>
   </si>
   <si>
     <t>전류</t>
   </si>
   <si>
+    <t>Current</t>
+  </si>
+  <si>
     <t>Card_Current_Enhanced_Name</t>
   </si>
   <si>
     <t>전류+</t>
   </si>
   <si>
+    <t>Current+</t>
+  </si>
+  <si>
     <t>Card_Lightning_Storm_Name</t>
   </si>
   <si>
     <t>전기 폭풍</t>
   </si>
   <si>
+    <t>Lightning Storm</t>
+  </si>
+  <si>
     <t>Card_Lightning_Storm_Enhanced_Name</t>
   </si>
   <si>
     <t>전기 폭풍+</t>
   </si>
   <si>
+    <t>Lightning Storm+</t>
+  </si>
+  <si>
     <t>Card_Overcurrent_Name</t>
   </si>
   <si>
     <t>과전류</t>
   </si>
   <si>
+    <t>Overcurrent</t>
+  </si>
+  <si>
     <t>Card_Overcurrent_Enhanced_Name</t>
   </si>
   <si>
     <t>과전류+</t>
   </si>
   <si>
+    <t>Overcurrent+</t>
+  </si>
+  <si>
     <t>Card_Lightning_Spear_Name</t>
   </si>
   <si>
     <t>뇌창</t>
   </si>
   <si>
+    <t>Lightning Spear</t>
+  </si>
+  <si>
     <t>Card_Lightning_Spear_Enhanced_Name</t>
   </si>
   <si>
     <t>뇌창+</t>
   </si>
   <si>
+    <t>Lightning Spear+</t>
+  </si>
+  <si>
     <t>Card_Spark_Name</t>
   </si>
   <si>
     <t>스파크</t>
   </si>
   <si>
+    <t>Spark</t>
+  </si>
+  <si>
     <t>Card_Spark_Enhanced_Name</t>
   </si>
   <si>
     <t>스파크+</t>
   </si>
   <si>
+    <t>Spark+</t>
+  </si>
+  <si>
     <t>Card_Thunderbolt_Name</t>
   </si>
   <si>
     <t>벼락</t>
   </si>
   <si>
+    <t>Thunderbolt</t>
+  </si>
+  <si>
     <t>Card_Thunderbolt_Enhanced_Name</t>
   </si>
   <si>
     <t>벼락+</t>
   </si>
   <si>
+    <t>Thunderbolt+</t>
+  </si>
+  <si>
     <t>Card_Shovel_Des</t>
   </si>
   <si>
     <t>삽_설명</t>
   </si>
   <si>
+    <t>Shovel Des</t>
+  </si>
+  <si>
     <t>Card_Rake_Des</t>
   </si>
   <si>
     <t>갈퀴_설명</t>
   </si>
   <si>
+    <t>Rake Des</t>
+  </si>
+  <si>
     <t>Card_Shovel_Enhanced_Des</t>
   </si>
   <si>
     <t>삽+_설명</t>
   </si>
   <si>
+    <t>Shovel+ Des</t>
+  </si>
+  <si>
     <t>Card_Rake_Enhanced_Des</t>
   </si>
   <si>
     <t>갈퀴+_설명</t>
   </si>
   <si>
+    <t>Rake+ Des</t>
+  </si>
+  <si>
     <t>Card_GoldenShovel_Des</t>
   </si>
   <si>
     <t>황금 삽_설명</t>
   </si>
   <si>
+    <t>Golden Shovel Des</t>
+  </si>
+  <si>
     <t>Card_GoldenShovel_Enhanced_Des</t>
   </si>
   <si>
     <t>황금 삽+_설명</t>
   </si>
   <si>
+    <t>Golden Shovel+ Des</t>
+  </si>
+  <si>
     <t>Card_Axe_Des</t>
   </si>
   <si>
     <t>도끼_설명</t>
   </si>
   <si>
+    <t>Axe Des</t>
+  </si>
+  <si>
     <t>Card_Axe_Enhanced_Des</t>
   </si>
   <si>
     <t>도끼+_설명</t>
   </si>
   <si>
+    <t>Axe+ Des</t>
+  </si>
+  <si>
     <t>Card_Cross Chisel_Des</t>
   </si>
   <si>
     <t>십자 끌_설명</t>
   </si>
   <si>
+    <t>Cross Chisel Des</t>
+  </si>
+  <si>
     <t>Card_Cross Chisel_Enhanced_Des</t>
   </si>
   <si>
     <t>십자 끌+_설명</t>
   </si>
   <si>
+    <t>Cross Chisel+ Des</t>
+  </si>
+  <si>
     <t>Card_Pickaxe_Des</t>
   </si>
   <si>
     <t>곡괭이_설명</t>
   </si>
   <si>
+    <t>Pickaxe Des</t>
+  </si>
+  <si>
     <t>Card_Pickaxe_Enhanced_Des</t>
   </si>
   <si>
     <t>곡괭이+_설명</t>
   </si>
   <si>
+    <t>Pickaxe+ Des</t>
+  </si>
+  <si>
     <t>Card_Slingshot_Des</t>
   </si>
   <si>
     <t>새총_설명</t>
   </si>
   <si>
+    <t>Slingshot Des</t>
+  </si>
+  <si>
     <t>Card_Slingshot_Enhanced_Des</t>
   </si>
   <si>
     <t>새총+_설명</t>
   </si>
   <si>
+    <t>Slingshot+ Des</t>
+  </si>
+  <si>
     <t>Card_CornerCrushingHammer_Des</t>
   </si>
   <si>
     <t>모서리 파쇄 해머_설명</t>
   </si>
   <si>
+    <t>Corner CrushingHammer Des</t>
+  </si>
+  <si>
     <t>Card_CornerCrushingHammer_Enhanced_Des</t>
   </si>
   <si>
     <t>모서리 파쇄 해머+_설명</t>
   </si>
   <si>
+    <t>Corner CrushingHammer+ Des</t>
+  </si>
+  <si>
     <t>Card_ConcentratedCrossDrill_Des</t>
   </si>
   <si>
     <t>집중형 십자 드릴_설명</t>
   </si>
   <si>
+    <t>Concentrated CrossDrill Des</t>
+  </si>
+  <si>
     <t>Card_ConcentratedCrossDrill_Enhanced_Des</t>
   </si>
   <si>
     <t>집중형 십자 드릴+_설명</t>
   </si>
   <si>
+    <t>Concentrated CrossDrill+ Des</t>
+  </si>
+  <si>
     <t>Card_GoldenAxe_Des</t>
   </si>
   <si>
     <t>황금 도끼_설명</t>
   </si>
   <si>
+    <t>Golden Axe Des</t>
+  </si>
+  <si>
     <t>Card_GoldenAxe_Enhanced_Des</t>
   </si>
   <si>
     <t>황금 도끼+_설명</t>
   </si>
   <si>
+    <t>Golden Axe+ Des</t>
+  </si>
+  <si>
     <t>Card_Large Scissors_Des</t>
   </si>
   <si>
     <t>대형 가위_설명</t>
   </si>
   <si>
+    <t>Large Scissors Des</t>
+  </si>
+  <si>
     <t>Card_Large Scissors_Enhanced_Des</t>
   </si>
   <si>
     <t>대형 가위+_설명</t>
   </si>
   <si>
+    <t>Large Scissors+ Des</t>
+  </si>
+  <si>
     <t>Card_WeakeningNormal_Des</t>
   </si>
   <si>
     <t>약화 카드 - 일반_설명</t>
   </si>
   <si>
+    <t>Weakening Normal Des</t>
+  </si>
+  <si>
     <t>Card_WeakeningRare_Des</t>
   </si>
   <si>
     <t>약화 카드 - 레어_설명</t>
   </si>
   <si>
+    <t>Weakening Rare Des</t>
+  </si>
+  <si>
     <t>Card_WeakeningUnique_Des</t>
   </si>
   <si>
     <t>약화 카드 - 유니크_설명</t>
   </si>
   <si>
+    <t>Weakening Unique Des</t>
+  </si>
+  <si>
     <t>Card_Bag_Des</t>
   </si>
   <si>
     <t>가방_설명</t>
   </si>
   <si>
+    <t>Bag Des</t>
+  </si>
+  <si>
     <t>Card_ToolTransformation_Des</t>
   </si>
   <si>
     <t>도구 변형_설명</t>
   </si>
   <si>
+    <t>Tool Transformation Des</t>
+  </si>
+  <si>
     <t>Card_ToolEnhancement_Des</t>
   </si>
   <si>
     <t>도구 강화_설명</t>
   </si>
   <si>
+    <t>Tool Enhancement Des</t>
+  </si>
+  <si>
     <t>Card_AdventurerTorch_Des</t>
   </si>
   <si>
     <t>모험가의 횃불_설명</t>
   </si>
   <si>
+    <t>Adventurer Torch Des</t>
+  </si>
+  <si>
     <t>Card_AdventurerTorch_Enhanced_Des</t>
   </si>
   <si>
     <t>모험가의 횃불+_설명</t>
   </si>
   <si>
+    <t>Adventurer Torch+ Des</t>
+  </si>
+  <si>
     <t>Card_HammerOfMemory_Des</t>
   </si>
   <si>
     <t>기억의 망치_설명</t>
   </si>
   <si>
+    <t>Hammer OfMemory Des</t>
+  </si>
+  <si>
     <t>Card_HammerOfMemory_Enhanced_Des</t>
   </si>
   <si>
     <t>기억의 망치+_설명</t>
   </si>
   <si>
+    <t>Hammer OfMemory+ Des</t>
+  </si>
+  <si>
     <t>Card_RiftStartumAnalysis_Des</t>
   </si>
   <si>
     <t>균열 지층 분석_설명</t>
   </si>
   <si>
+    <t>Rift StartumAnalysis Des</t>
+  </si>
+  <si>
     <t>Card_RiftStartumAnalysis_Enhanced_Des</t>
   </si>
   <si>
     <t>균열 지층 분석+_설명</t>
   </si>
   <si>
+    <t>Rift StartumAnalysis+ Des</t>
+  </si>
+  <si>
     <t>Card_Novice_Wand_Des</t>
   </si>
   <si>
     <t>견습 지팡이_설명</t>
   </si>
   <si>
+    <t>Novice Wand Des</t>
+  </si>
+  <si>
     <t>Card_Novice_Wand_Enhanced_Des</t>
   </si>
   <si>
     <t>견습 지팡이+_설명</t>
   </si>
   <si>
+    <t>Novice Wand+ Des</t>
+  </si>
+  <si>
     <t>Card_Mana_Arrow_Des</t>
   </si>
   <si>
     <t>마력 화살_설명</t>
   </si>
   <si>
+    <t>Mana Arrow Des</t>
+  </si>
+  <si>
     <t>Card_Mana_Arrow_Enhanced_Des</t>
   </si>
   <si>
     <t>마력 화살+_설명</t>
   </si>
   <si>
+    <t>Mana Arrow+ Des</t>
+  </si>
+  <si>
     <t>Card_Sparkle_Des</t>
   </si>
   <si>
     <t>번뜩임_설명</t>
   </si>
   <si>
+    <t>Sparkle Des</t>
+  </si>
+  <si>
     <t>Card_Sparkle_Enhanced_Des</t>
   </si>
   <si>
     <t>번뜩임+_설명</t>
   </si>
   <si>
+    <t>Sparkle+ Des</t>
+  </si>
+  <si>
     <t>Card_Mana_Pierce_Des</t>
   </si>
   <si>
     <t>마력 찌르기_설명</t>
   </si>
   <si>
+    <t>Mana Pierce Des</t>
+  </si>
+  <si>
     <t>Card_Mana_Pierce_Enhanced_Des</t>
   </si>
   <si>
     <t>마력 찌르기+_설명</t>
   </si>
   <si>
+    <t>Mana Pierce+ Des</t>
+  </si>
+  <si>
     <t>Card_Magic_Spear_Des</t>
   </si>
   <si>
     <t>마력의 창_설명</t>
   </si>
   <si>
+    <t>Magic Spear Des</t>
+  </si>
+  <si>
     <t>Card_Magic_Spear_Enhanced_Des</t>
   </si>
   <si>
     <t>마력의 창+_설명</t>
   </si>
   <si>
+    <t>Magic Spear+ Des</t>
+  </si>
+  <si>
     <t>Card_Magic_Slash_Des</t>
   </si>
   <si>
     <t>마력 베기_설명</t>
   </si>
   <si>
+    <t>Magic Slash Des</t>
+  </si>
+  <si>
     <t>Card_Magic_Slash_Enhanced_Des</t>
   </si>
   <si>
     <t>마력 베기+_설명</t>
   </si>
   <si>
+    <t>Magic Slash+ Des</t>
+  </si>
+  <si>
     <t>Card_Magic_Sword_Des</t>
   </si>
   <si>
     <t>마력의 검_설명</t>
   </si>
   <si>
+    <t>Magic Sword Des</t>
+  </si>
+  <si>
     <t>Card_Magic_Sword_Enhanced_Des</t>
   </si>
   <si>
     <t>마력의 검+_설명</t>
   </si>
   <si>
+    <t>Magic Sword+ Des</t>
+  </si>
+  <si>
     <t>Card_Magic_Claw_Des</t>
   </si>
   <si>
     <t>마력의 발톱_설명</t>
   </si>
   <si>
+    <t>Magic Claw Des</t>
+  </si>
+  <si>
     <t>Card_Magic_Claw_Enhanced_Des</t>
   </si>
   <si>
     <t>마력의 발톱+_설명</t>
   </si>
   <si>
+    <t>Magic Claw+ Des</t>
+  </si>
+  <si>
     <t>Card_Magic_Cannon_Des</t>
   </si>
   <si>
     <t>마력 포탄_설명</t>
   </si>
   <si>
+    <t>Magic Cannon Des</t>
+  </si>
+  <si>
     <t>Card_Magic_Cannon_Enhanced_Des</t>
   </si>
   <si>
     <t>마력 포탄+_설명</t>
   </si>
   <si>
+    <t>Magic Cannon+ Des</t>
+  </si>
+  <si>
     <t>Card_Frog_Des</t>
   </si>
   <si>
     <t>개구리_설명</t>
   </si>
   <si>
+    <t>Frog Des</t>
+  </si>
+  <si>
     <t>Card_Frog_Enhanced_Des</t>
   </si>
   <si>
     <t>개구리+_설명</t>
   </si>
   <si>
+    <t>Frog+ Des</t>
+  </si>
+  <si>
     <t>Card_Inchant_Magic_Des</t>
   </si>
   <si>
     <t>마력 부여_설명</t>
   </si>
   <si>
+    <t>Inchant Magic Des</t>
+  </si>
+  <si>
     <t>Card_Inchant_Magic_Enhanced_Des</t>
   </si>
   <si>
     <t>마력 부여+_설명</t>
   </si>
   <si>
+    <t>Inchant Magic+ Des</t>
+  </si>
+  <si>
     <t>Card_Ignite_Des</t>
   </si>
   <si>
     <t>발화_설명</t>
   </si>
   <si>
+    <t>Ignite Des</t>
+  </si>
+  <si>
     <t>Card_Ignite_Enhanced_Des</t>
   </si>
   <si>
     <t>발화+_설명</t>
   </si>
   <si>
+    <t>Ignite+ Des</t>
+  </si>
+  <si>
     <t>Card_Flame_Explosion_Des</t>
   </si>
   <si>
     <t>화염 폭발_설명</t>
   </si>
   <si>
+    <t>Flame Explosion Des</t>
+  </si>
+  <si>
     <t>Card_Flame_Explosion_Enhanced_Des</t>
   </si>
   <si>
     <t>화염 폭발+_설명</t>
   </si>
   <si>
+    <t>Flame Explosion+ Des</t>
+  </si>
+  <si>
     <t>Card_Ember_Des</t>
   </si>
   <si>
     <t>잔불_설명</t>
   </si>
   <si>
+    <t>Ember Des</t>
+  </si>
+  <si>
     <t>Card_Ember_Enhanced_Des</t>
   </si>
   <si>
     <t>잔불+_설명</t>
   </si>
   <si>
+    <t>Ember+ Des</t>
+  </si>
+  <si>
     <t>Card_Flame_Wall_Des</t>
   </si>
   <si>
     <t>화염 벽_설명</t>
   </si>
   <si>
+    <t>Flame Wall Des</t>
+  </si>
+  <si>
     <t>Card_Flame_Wall_Enhanced_Des</t>
   </si>
   <si>
     <t>화염 벽+_설명</t>
   </si>
   <si>
+    <t>Flame Wall+ Des</t>
+  </si>
+  <si>
     <t>Card_Chain_Ignition_Des</t>
   </si>
   <si>
     <t>연쇄 발화_설명</t>
   </si>
   <si>
+    <t>Chain Ignition Des</t>
+  </si>
+  <si>
     <t>Card_Chain_Ignition_Enhanced_Des</t>
   </si>
   <si>
     <t>연쇄 발화+_설명</t>
   </si>
   <si>
+    <t>Chain Ignition+ Des</t>
+  </si>
+  <si>
     <t>Card_Volcano_Des</t>
   </si>
   <si>
     <t>볼케이노_설명</t>
   </si>
   <si>
+    <t>Volcano Des</t>
+  </si>
+  <si>
     <t>Card_Volcano_Enhanced_Des</t>
   </si>
   <si>
     <t>볼케이노+_설명</t>
   </si>
   <si>
+    <t>Volcano+ Des</t>
+  </si>
+  <si>
     <t>Card_Freeze_Des</t>
   </si>
   <si>
     <t>냉각_설명</t>
   </si>
   <si>
+    <t>Freeze Des</t>
+  </si>
+  <si>
     <t>Card_Freeze_Enhanced_Des</t>
   </si>
   <si>
     <t>냉각+_설명</t>
   </si>
   <si>
+    <t>Freeze+ Des</t>
+  </si>
+  <si>
     <t>Card_Frost_Blast_Des</t>
   </si>
   <si>
     <t>냉기 폭발_설명</t>
   </si>
   <si>
+    <t>Frost Blast Des</t>
+  </si>
+  <si>
     <t>Card_Frost_Blast_Enhanced_Des</t>
   </si>
   <si>
     <t>냉기 폭발+_설명</t>
   </si>
   <si>
+    <t>Frost Blast+ Des</t>
+  </si>
+  <si>
     <t>Card_Spreading_Frost_Des</t>
   </si>
   <si>
     <t>퍼져나가는 냉기_설명</t>
   </si>
   <si>
+    <t>Spreading Frost Des</t>
+  </si>
+  <si>
     <t>Card_Spreading_Frost_Enhanced_Des</t>
   </si>
   <si>
     <t>퍼져나가는 냉기+_설명</t>
   </si>
   <si>
+    <t>Spreading Frost+ Des</t>
+  </si>
+  <si>
     <t>Card_Ice_Sword_Des</t>
   </si>
   <si>
     <t>얼음 검_설명</t>
   </si>
   <si>
+    <t>Ice Sword Des</t>
+  </si>
+  <si>
     <t>Card_Ice_Sword_Enhanced_Des</t>
   </si>
   <si>
     <t>얼음 검+_설명</t>
   </si>
   <si>
+    <t>Ice Sword+ Des</t>
+  </si>
+  <si>
     <t>Card_Ice_Spear_Des</t>
   </si>
   <si>
     <t>얼음 창_설명</t>
   </si>
   <si>
+    <t>Ice Spear Des</t>
+  </si>
+  <si>
     <t>Card_Ice_Spear_Enhanced_Des</t>
   </si>
   <si>
     <t>얼음 창+_설명</t>
   </si>
   <si>
+    <t>Ice Spear+ Des</t>
+  </si>
+  <si>
     <t>Card_Ice_Arrow_Des</t>
   </si>
   <si>
     <t>얼음 화살_설명</t>
   </si>
   <si>
+    <t>Ice Arrow Des</t>
+  </si>
+  <si>
     <t>Card_Ice_Arrow_Enhanced_Des</t>
   </si>
   <si>
     <t>얼음 화살+_설명</t>
   </si>
   <si>
+    <t>Ice Arrow+ Des</t>
+  </si>
+  <si>
     <t>Card_Current_Des</t>
   </si>
   <si>
     <t>전류_설명</t>
   </si>
   <si>
+    <t>Current Des</t>
+  </si>
+  <si>
     <t>Card_Current_Enhanced_Des</t>
   </si>
   <si>
     <t>전류+_설명</t>
   </si>
   <si>
+    <t>Current+ Des</t>
+  </si>
+  <si>
     <t>Card_Lightning_Storm_Des</t>
   </si>
   <si>
     <t>전기 폭풍_설명</t>
   </si>
   <si>
+    <t>Lightning Storm Des</t>
+  </si>
+  <si>
     <t>Card_Lightning_Storm_Enhanced_Des</t>
   </si>
   <si>
     <t>전기 폭풍+_설명</t>
   </si>
   <si>
+    <t>Lightning Storm+ Des</t>
+  </si>
+  <si>
     <t>Card_Overcurrent_Des</t>
   </si>
   <si>
     <t>과전류_설명</t>
   </si>
   <si>
+    <t>Overcurrent Des</t>
+  </si>
+  <si>
     <t>Card_Overcurrent_Enhanced_Des</t>
   </si>
   <si>
     <t>과전류+_설명</t>
   </si>
   <si>
+    <t>Overcurrent+ Des</t>
+  </si>
+  <si>
     <t>Card_Lightning_Spear_Des</t>
   </si>
   <si>
     <t>뇌창_설명</t>
   </si>
   <si>
+    <t>Lightning Spear Des</t>
+  </si>
+  <si>
     <t>Card_Lightning_Spear_Enhanced_Des</t>
   </si>
   <si>
     <t>뇌창+_설명</t>
   </si>
   <si>
+    <t>Lightning Spear+ Des</t>
+  </si>
+  <si>
     <t>Card_Spark_Des</t>
   </si>
   <si>
     <t>스파크_설명</t>
   </si>
   <si>
+    <t>Spark Des</t>
+  </si>
+  <si>
     <t>Card_Spark_Enhanced_Des</t>
   </si>
   <si>
     <t>스파크+_설명</t>
   </si>
   <si>
+    <t>Spark+ Des</t>
+  </si>
+  <si>
     <t>Card_Thunderbolt_Des</t>
   </si>
   <si>
     <t>벼락_설명</t>
   </si>
   <si>
+    <t>Thunderbolt Des</t>
+  </si>
+  <si>
     <t>Card_Thunderbolt_Enhanced_Des</t>
   </si>
   <si>
     <t>벼락+_설명</t>
   </si>
   <si>
+    <t>Thunderbolt+ Des</t>
+  </si>
+  <si>
     <t>relic101_Name</t>
   </si>
   <si>
     <t>정밀 타격 오일</t>
   </si>
   <si>
+    <t>Precision Strike Oil</t>
+  </si>
+  <si>
     <t>relic102_Name</t>
   </si>
   <si>
     <t>강화 손잡이</t>
   </si>
   <si>
+    <t>Reinforced Grip</t>
+  </si>
+  <si>
     <t>relic103_Name</t>
   </si>
   <si>
     <t>숙련공의 숫돌</t>
   </si>
   <si>
+    <t>Artisan's Whetstone</t>
+  </si>
+  <si>
     <t>relic104_Name</t>
   </si>
   <si>
     <t>부서진 도구의 기억</t>
   </si>
   <si>
+    <t>Memory of Broken Tools</t>
+  </si>
+  <si>
     <t>relic105_Name</t>
   </si>
   <si>
     <t>스프레이 마감제</t>
   </si>
   <si>
+    <t>Spray Finish</t>
+  </si>
+  <si>
     <t>relic106_Name</t>
   </si>
   <si>
     <t>작은 금괴</t>
   </si>
   <si>
+    <t>Small Gold Bar</t>
+  </si>
+  <si>
     <t>relic107_Name</t>
   </si>
   <si>
     <t>확장 배낭</t>
   </si>
   <si>
+    <t>Expanded Backpack</t>
+  </si>
+  <si>
     <t>relic108_Name</t>
   </si>
   <si>
     <t>공구 주머니</t>
   </si>
   <si>
+    <t>Tool Pouch</t>
+  </si>
+  <si>
     <t>relic109_Name</t>
   </si>
   <si>
     <t>정밀 타격 레이저</t>
   </si>
   <si>
+    <t>Precision Strike Laser</t>
+  </si>
+  <si>
     <t>relic110_Name</t>
   </si>
   <si>
     <t>광역 공격 망치</t>
   </si>
   <si>
+    <t>Area Attack Hammer</t>
+  </si>
+  <si>
     <t>relic111_Name</t>
   </si>
   <si>
     <t>덕트 테이프</t>
   </si>
   <si>
+    <t>Duct Tape</t>
+  </si>
+  <si>
     <t>relic112_Name</t>
   </si>
   <si>
     <t>고대의 나침반</t>
   </si>
   <si>
+    <t>Ancient Compass</t>
+  </si>
+  <si>
     <t>relic113_Name</t>
   </si>
   <si>
     <t>손전등</t>
   </si>
   <si>
+    <t>Flashlight</t>
+  </si>
+  <si>
     <t>relic114_Name</t>
   </si>
   <si>
     <t>유적 조사 노트</t>
   </si>
   <si>
+    <t>Ruins Investigation Notes</t>
+  </si>
+  <si>
     <t>relic115_Name</t>
   </si>
   <si>
     <t>거래기록 장부</t>
   </si>
   <si>
+    <t>Transaction Ledger</t>
+  </si>
+  <si>
     <t>relic116_Name</t>
   </si>
   <si>
     <t>균열 생성기*</t>
   </si>
   <si>
+    <t>Rift Generator</t>
+  </si>
+  <si>
     <t>relic117_Name</t>
   </si>
   <si>
     <t>균열 파편 강화*</t>
   </si>
   <si>
+    <t>Rift Fragment Reinforcement</t>
+  </si>
+  <si>
     <t>relic118_Name</t>
   </si>
   <si>
     <t>완벽한 도구함</t>
   </si>
   <si>
+    <t>Perfect Tool Box</t>
+  </si>
+  <si>
     <t>relic119_Name</t>
   </si>
   <si>
     <t>잔상 추적자*</t>
   </si>
   <si>
+    <t>Afterimage Tracer</t>
+  </si>
+  <si>
     <t>relic120_Name</t>
   </si>
   <si>
     <t>잔상 각인*</t>
   </si>
   <si>
+    <t>Afterimage Engraving</t>
+  </si>
+  <si>
     <t>relic121_Name</t>
   </si>
   <si>
     <t>정밀 조준경</t>
   </si>
   <si>
+    <t>Precision Scope</t>
+  </si>
+  <si>
     <t>relic122_Name</t>
   </si>
   <si>
     <t>가로 방향 안정 장치</t>
   </si>
   <si>
+    <t>Horizontal Stabilizer</t>
+  </si>
+  <si>
     <t>relic123_Name</t>
   </si>
   <si>
     <t>세로 방향 안정 장치</t>
   </si>
   <si>
+    <t>Vertical Stabilizer</t>
+  </si>
+  <si>
     <t>relic201_Name</t>
   </si>
   <si>
     <t>마력 부산물</t>
   </si>
   <si>
+    <t>Magical Byproduct</t>
+  </si>
+  <si>
     <t>relic202_Name</t>
   </si>
   <si>
     <t>마법사의 단검</t>
   </si>
   <si>
+    <t>Wizard's Dagger</t>
+  </si>
+  <si>
     <t>relic203_Name</t>
   </si>
   <si>
     <t>마법 주머니</t>
   </si>
   <si>
+    <t>Magic Pouch</t>
+  </si>
+  <si>
     <t>relic204_Name</t>
   </si>
   <si>
     <t>마력 자석</t>
   </si>
   <si>
+    <t>Mana Magnet</t>
+  </si>
+  <si>
     <t>relic205_Name</t>
   </si>
   <si>
     <t>응축된 오브</t>
   </si>
   <si>
+    <t>Condensed Orb</t>
+  </si>
+  <si>
     <t>relic206_Name</t>
   </si>
   <si>
     <t>혼돈의 주문서</t>
   </si>
   <si>
+    <t>Chaos Scroll</t>
+  </si>
+  <si>
     <t>relic207_Name</t>
   </si>
   <si>
     <t>마법 렌즈</t>
   </si>
   <si>
+    <t>Magic Lens</t>
+  </si>
+  <si>
     <t>relic208_Name</t>
   </si>
   <si>
     <t>마력 솥</t>
   </si>
   <si>
+    <t>Mana Cauldron</t>
+  </si>
+  <si>
     <t>relic209_Name</t>
   </si>
   <si>
     <t>마나 서클3</t>
   </si>
   <si>
+    <t>Mana Circle 3</t>
+  </si>
+  <si>
     <t>relic210_Name</t>
   </si>
   <si>
     <t>마나 서클5</t>
   </si>
   <si>
+    <t>Mana Circle 5</t>
+  </si>
+  <si>
     <t>relic211_Name</t>
   </si>
   <si>
     <t>마나 서클7</t>
   </si>
   <si>
+    <t>Mana Circle 7</t>
+  </si>
+  <si>
     <t>relic212_Name</t>
   </si>
   <si>
     <t>마나 서클11</t>
   </si>
   <si>
+    <t>Mana Circle 11</t>
+  </si>
+  <si>
     <t>relic213_Name</t>
   </si>
   <si>
     <t>마법 포션</t>
   </si>
   <si>
+    <t>Magic Potion</t>
+  </si>
+  <si>
     <t>relic214_Name</t>
   </si>
   <si>
     <t>마법사의 붉은 돌</t>
   </si>
   <si>
+    <t>Wizard's Red Stone</t>
+  </si>
+  <si>
     <t>relic215_Name</t>
   </si>
   <si>
     <t>마법사의 푸른 돌</t>
   </si>
   <si>
+    <t>Wizard's Blue Stone</t>
+  </si>
+  <si>
     <t>relic216_Name</t>
   </si>
   <si>
     <t>마법사의 보랏빛 돌</t>
   </si>
   <si>
+    <t>Wizard's Purple Stone</t>
+  </si>
+  <si>
     <t>relic217_Name</t>
   </si>
   <si>
     <t>마법사의 무지개석</t>
   </si>
   <si>
+    <t>Wizard's Rainbow Stone</t>
+  </si>
+  <si>
     <t>relic218_Name</t>
   </si>
   <si>
     <t xml:space="preserve">불타는 마법 스크롤 </t>
   </si>
   <si>
+    <t>Flaming Magic Scroll</t>
+  </si>
+  <si>
     <t>relic219_Name</t>
   </si>
   <si>
     <t>얼어붙은 마법 스크롤</t>
   </si>
   <si>
+    <t>Frozen Magic Scrol</t>
+  </si>
+  <si>
     <t>relic220_Name</t>
   </si>
   <si>
     <t>번쩍이는 마법 스크롤</t>
   </si>
   <si>
+    <t>Sparking Magic Scroll</t>
+  </si>
+  <si>
     <t>relic221_Name</t>
   </si>
   <si>
     <t>불사조의 깃털</t>
   </si>
   <si>
+    <t>Phoenix Feather</t>
+  </si>
+  <si>
     <t>relic222_Name</t>
   </si>
   <si>
     <t>다용도 횃불기름</t>
   </si>
   <si>
+    <t>Multi-purpose Torch Oil</t>
+  </si>
+  <si>
     <t>relic223_Name</t>
   </si>
   <si>
     <t>되살아난 불씨</t>
   </si>
   <si>
+    <t>Revived Ember</t>
+  </si>
+  <si>
     <t>relic224_Name</t>
   </si>
   <si>
     <t>버려진 성냥갑</t>
   </si>
   <si>
+    <t>Discarded Matchbox</t>
+  </si>
+  <si>
     <t>relic225_Name</t>
   </si>
   <si>
     <t>불사조의 알</t>
   </si>
   <si>
+    <t>Phoenix Egg</t>
+  </si>
+  <si>
     <t>relic226_Name</t>
   </si>
   <si>
     <t>촛불</t>
   </si>
   <si>
+    <t>Candle</t>
+  </si>
+  <si>
     <t>relic227_Name</t>
   </si>
   <si>
     <t>목탄</t>
   </si>
   <si>
+    <t>Charcoal</t>
+  </si>
+  <si>
     <t>relic228_Name</t>
   </si>
   <si>
     <t>그을린 망토</t>
   </si>
   <si>
+    <t>Singed Cloak</t>
+  </si>
+  <si>
     <t>relic229_Name</t>
   </si>
   <si>
     <t>그을린 왕관</t>
   </si>
   <si>
+    <t>Singed Crown</t>
+  </si>
+  <si>
     <t>relic230_Name</t>
   </si>
   <si>
     <t>그을린 갑옷</t>
   </si>
   <si>
+    <t>Singed Armor</t>
+  </si>
+  <si>
     <t>relic231_Name</t>
   </si>
   <si>
     <t>그을린 장검</t>
   </si>
   <si>
+    <t>Singed Longsword</t>
+  </si>
+  <si>
     <t>relic232_Name</t>
   </si>
   <si>
     <t>눈 오리</t>
   </si>
   <si>
+    <t>Snow Duck</t>
+  </si>
+  <si>
     <t>relic233_Name</t>
   </si>
   <si>
     <t>녹지않는 얼음</t>
   </si>
   <si>
+    <t>Never Melt Ice</t>
+  </si>
+  <si>
     <t>relic234_Name</t>
   </si>
   <si>
     <t>얼어붙은 뿌리</t>
   </si>
   <si>
+    <t>Frozen Root</t>
+  </si>
+  <si>
     <t>relic235_Name</t>
   </si>
   <si>
     <t>얼음 폭죽</t>
   </si>
   <si>
+    <t>Icework</t>
+  </si>
+  <si>
     <t>relic236_Name</t>
   </si>
   <si>
     <t>얼음 도미노</t>
   </si>
   <si>
+    <t>Ice Domino</t>
+  </si>
+  <si>
     <t>relic237_Name</t>
   </si>
   <si>
     <t>스케이트</t>
   </si>
   <si>
+    <t>Skates</t>
+  </si>
+  <si>
     <t>relic238_Name</t>
   </si>
   <si>
     <t>아이스크림</t>
   </si>
   <si>
+    <t>Ice Cream</t>
+  </si>
+  <si>
     <t>relic239_Name</t>
   </si>
   <si>
     <t>떨어진 고드름</t>
   </si>
   <si>
+    <t>Fallen Icicle</t>
+  </si>
+  <si>
     <t>relic240_Name</t>
   </si>
   <si>
     <t>얼어붙은 대검</t>
   </si>
   <si>
+    <t>Frozen Greatsword</t>
+  </si>
+  <si>
     <t>relic241_Name</t>
   </si>
   <si>
     <t>전기석</t>
   </si>
   <si>
+    <t>Tourmaline</t>
+  </si>
+  <si>
     <t>relic242_Name</t>
   </si>
   <si>
     <t>배터리</t>
   </si>
   <si>
+    <t>Battery</t>
+  </si>
+  <si>
     <t>relic243_Name</t>
   </si>
   <si>
     <t>스위치</t>
   </si>
   <si>
+    <t>Switch</t>
+  </si>
+  <si>
     <t>relic244_Name</t>
   </si>
   <si>
     <t>고무 장갑</t>
   </si>
   <si>
+    <t>Rubber Gloves</t>
+  </si>
+  <si>
     <t>relic245_Name</t>
   </si>
   <si>
     <t>플라즈마 글로브</t>
   </si>
   <si>
+    <t>Plasma Globe</t>
+  </si>
+  <si>
     <t>relic246_Name</t>
   </si>
   <si>
     <t>퓨즈</t>
   </si>
   <si>
+    <t>Fuse</t>
+  </si>
+  <si>
     <t>relic247_Name</t>
   </si>
   <si>
     <t>전선</t>
   </si>
   <si>
+    <t>Electrical Wire</t>
+  </si>
+  <si>
     <t>relic248_Name</t>
   </si>
   <si>
     <t>크고 빨간 버튼</t>
   </si>
   <si>
+    <t>Big Red Button</t>
+  </si>
+  <si>
     <t>relic249_Name</t>
   </si>
   <si>
     <t>먹구름 플라스크</t>
   </si>
   <si>
+    <t>Dark Cloud Flask</t>
+  </si>
+  <si>
     <t>relic250_Name</t>
   </si>
   <si>
     <t>피뢰침 자검</t>
   </si>
   <si>
+    <t>Lightning Rod Rapier</t>
+  </si>
+  <si>
     <t>relic251_Name</t>
   </si>
   <si>
     <t>속성제어장치</t>
   </si>
   <si>
+    <t>Elemental Controller</t>
+  </si>
+  <si>
     <t>relic252_Name</t>
   </si>
   <si>
     <t>속성증폭장치</t>
   </si>
   <si>
+    <t>Elemental Amplifier</t>
+  </si>
+  <si>
     <t>relic253_Name</t>
   </si>
   <si>
     <t>냉각소화기</t>
   </si>
   <si>
+    <t>Cooling Fire Extinguisher</t>
+  </si>
+  <si>
     <t>relic254_Name</t>
   </si>
   <si>
     <t>초전도체</t>
   </si>
   <si>
+    <t>Superconductor</t>
+  </si>
+  <si>
     <t>relic255_Name</t>
   </si>
   <si>
     <t>과열회로</t>
   </si>
   <si>
+    <t>Overheated Circuit</t>
+  </si>
+  <si>
     <t>relic256_Name</t>
   </si>
   <si>
     <t>삼위일체</t>
   </si>
   <si>
+    <t>Trinity</t>
+  </si>
+  <si>
     <t>relic101_Des</t>
   </si>
   <si>
     <t>도구 태그 카드를 사용하여 타일을 파괴할 때, 파괴된 타일 하나당 +3점을 추가로 얻습니다.</t>
   </si>
   <si>
+    <t>When destroying tiles using a Tool tag card, gain +3 additional points for each destroyed tile.</t>
+  </si>
+  <si>
     <t>relic102_Des</t>
   </si>
   <si>
     <t>도구 태그 카드로 타일을 파괴할 때, 해당 타일 파괴 점수 총합에 1.25배수를 적용합니다.</t>
   </si>
   <si>
+    <t>When destroying tiles with a Tool tag card, apply a 1.25x multiplier to the total destruction score of those tiles.</t>
+  </si>
+  <si>
     <t>relic103_Des</t>
   </si>
   <si>
     <t>도구 태그가 붙은 카드의 파괴 확률이 30% 증가합니다.</t>
   </si>
   <si>
+    <t>Destruction probability of cards with the Tool tag increases by 30%.</t>
+  </si>
+  <si>
     <t>relic104_Des</t>
   </si>
   <si>
     <t>유물을 가진 시점을 기준으로 도구 태그 카드가 파괴되었을 경우 1스택 증가. 스테이지 클리어 시 스택의 따른 골드를 제공한다.</t>
   </si>
   <si>
+    <t>Gain 1 stack if a Tool tag card is destroyed while possessing this relic. Provides gold based on stacks upon clearing the stage.</t>
+  </si>
+  <si>
     <t>relic105_Des</t>
   </si>
   <si>
     <t>강화되지 않은 도구 태그 카드의 파괴를 방지합니다.</t>
   </si>
   <si>
+    <t>Prevents the destruction of unenhanced Tool tag cards.</t>
+  </si>
+  <si>
     <t>relic106_Des</t>
   </si>
   <si>
     <t>스테이지 시작 시 보유한 골드 10G당 점수 +5점을 추가합니다. (최대 50G까지)</t>
   </si>
   <si>
+    <t>At the start of the stage, add +5 points for every 10G held. (Up to 50G)</t>
+  </si>
+  <si>
     <t>relic107_Des</t>
   </si>
   <si>
     <t>스테이지 시작 시 드로우 +1</t>
   </si>
   <si>
+    <t>Draw +1 at the start of the stage.</t>
+  </si>
+  <si>
     <t>relic108_Des</t>
   </si>
   <si>
     <t>유물 획득 시 덱에 있는 도구 태그 카드를 선택, 선택된 카드는 유물에 귀속되며 해당 카드는 매 스테이지 시작 시 추가로 제공</t>
   </si>
   <si>
+    <t>Upon acquiring the relic, select a Tool tag card in your deck; the selected card becomes bound to the relic and is provided additionally at the start of each stage.</t>
+  </si>
+  <si>
     <t>relic109_Des</t>
   </si>
   <si>
     <t>1x1 단일 타일 파괴 카드로 타일을 파괴할 때, 3배수의 점수를 획득한다.</t>
   </si>
   <si>
+    <t>When destroying a tile with a 1x1 single-tile destruction card, gain 3x the score.</t>
+  </si>
+  <si>
     <t>relic110_Des</t>
   </si>
   <si>
     <t>카드 한장으로 8칸 이상 파괴 할 경우, 1.5배수의 점수를 획득한다.</t>
   </si>
   <si>
+    <t>If 8 or more tiles are destroyed with a single card, gain 1.5x the score.</t>
+  </si>
+  <si>
     <t>relic111_Des</t>
   </si>
   <si>
     <t>도구 카드가 파괴될 때, 30% 확률로 파괴되지 않고 손패로 돌아갑니다.</t>
   </si>
   <si>
+    <t>When a Tool card is destroyed, there is a 30% chance it returns to your hand instead of being destroyed.</t>
+  </si>
+  <si>
     <t>relic112_Des</t>
   </si>
   <si>
     <t>매 스테이지 처음으로 사용되는 도구 카드는 인접한 타일 하나를 추가로 파괴합니다. (무작위 방향 상하좌우)</t>
   </si>
   <si>
+    <t>The first Tool card used in each stage destroys one additional adjacent tile. (Random direction: Up, Down, Left, Right)</t>
+  </si>
+  <si>
     <t>relic113_Des</t>
   </si>
   <si>
     <t>암흑 타일을 파괴하거나 밝힐 때, 2.25배수의 점수를 획득한다.</t>
   </si>
   <si>
+    <t>Gain 2.25x the score when destroying or revealing Dark tiles.</t>
+  </si>
+  <si>
     <t>relic114_Des</t>
   </si>
   <si>
     <t>모든 점수의 1배수의 추가 점수를 부여한다. 스테이지 클리어 시 0.1배수 씩 배수가 늘어난다.</t>
   </si>
   <si>
+    <t>Grants additional points equal to 1x the score. The multiplier increases by 0.1x upon clearing each stage.</t>
+  </si>
+  <si>
     <t>relic115_Des</t>
   </si>
   <si>
     <t>상점 의뢰시 실패 확률 30% 감소</t>
   </si>
   <si>
+    <t>Decreases shop request failure probability by 30%.</t>
+  </si>
+  <si>
     <t>relic116_Des</t>
   </si>
   <si>
     <t>타일 파괴 실패 시, 해당 타일이 30% 확률로 균열 타일로 변경된다.</t>
   </si>
   <si>
+    <t>Upon failing to destroy a tile, there is a 30% chance the tile changes into a Rift tile.</t>
+  </si>
+  <si>
     <t>relic117_Des</t>
   </si>
   <si>
     <t>균열 타일 파괴 시, +5 점수 추가</t>
   </si>
   <si>
+    <t>Gain +5 additional points when destroying a Rift tile.</t>
+  </si>
+  <si>
     <t>relic118_Des</t>
   </si>
   <si>
     <t>드로우 시 강화된 도구 카드 1개당 +3 골드</t>
   </si>
   <si>
+    <t>Gain +3 gold for each enhanced Tool card upon drawing.</t>
+  </si>
+  <si>
     <t>relic119_Des</t>
   </si>
   <si>
     <t>잔상 타일을 타격 지점으로 선택하여 타일 파괴시, +2.5배수의 점수를 제공</t>
   </si>
   <si>
+    <t>Gain 2.5x the score when destroying tiles by selecting an Afterimage tile as the impact point.</t>
+  </si>
+  <si>
     <t>relic120_Des</t>
   </si>
   <si>
     <t>스테이지 시작 시 7개의 일반 타일을 잔상 타일로 변경</t>
   </si>
   <si>
+    <t>Changes 7 normal tiles into Afterimage tiles at the start of the stage.</t>
+  </si>
+  <si>
     <t>relic121_Des</t>
   </si>
   <si>
     <t>타격 지점에서 멀리 떨어진 타일의 파괴 확률을 점진적으로 증가 시킨다.</t>
   </si>
   <si>
+    <t>Gradually increases the destruction probability of tiles located far from the impact point.</t>
+  </si>
+  <si>
     <t>relic122_Des</t>
   </si>
   <si>
     <t>타격점을 기준으로 가로 방향으로 파괴 시, 해당 방향 타일의 파괴 확률이 20% 증가합니다.</t>
   </si>
   <si>
+    <t>When destroying tiles horizontally from the impact point, the destruction probability of tiles in that direction increases by 20%.</t>
+  </si>
+  <si>
     <t>relic123_Des</t>
   </si>
   <si>
     <t>타격점을 기준으로 세로 방향으로 파괴 시, 해당 방향 타일의 파괴 확률이 20% 증가합니다.</t>
   </si>
   <si>
+    <t>When destroying tiles vertically from the impact point, the destruction probability of tiles in that direction increases by 20%.</t>
+  </si>
+  <si>
     <t>relic201_Des</t>
   </si>
   <si>
     <t>마나 태그 카드를 사용할 때, x% 확률로 마나를 x 획득합니다.</t>
   </si>
   <si>
+    <t>When using a Mana tag card, there is an x% chance to gain x Mana.</t>
+  </si>
+  <si>
     <t>relic202_Des</t>
   </si>
   <si>
     <t>마나가 x이하일 때, 마나 태그 카드로 파괴한 타일의 점수가 x배수가 됩니다.</t>
   </si>
   <si>
+    <t>When Mana is x or below, the score for tiles destroyed by Mana tag cards is multiplied by x.</t>
+  </si>
+  <si>
     <t>relic203_Des</t>
   </si>
   <si>
     <t>누적 파괴 타일 x개마다, 마나를 x 획득합니다.</t>
   </si>
   <si>
+    <t>Gain x Mana for every x cumulative tiles destroyed.</t>
+  </si>
+  <si>
     <t>relic204_Des</t>
   </si>
   <si>
     <t>스테이지 종료시 남은 마나 x 마다, 골드를 x 획득합니다.</t>
   </si>
   <si>
+    <t>Gain x Gold for every x Mana remaining at the end of the stage.</t>
+  </si>
+  <si>
     <t>relic205_Des</t>
   </si>
   <si>
     <t>마법 카드의 요구 마나가 x배, 파괴 확률이 x배가 됩니다. 마법 카드로 파괴한 타일의 점수가 x배수가 됩니다.</t>
   </si>
   <si>
+    <t>Magic card Mana cost becomes x times, and destruction probability becomes x times. Scores for tiles destroyed by Magic cards are multiplied by x.</t>
+  </si>
+  <si>
     <t>relic206_Des</t>
   </si>
   <si>
     <t>매 스테이지마다 마법 카드의 요구 마나가 x부터 x사이의 수치로 무작위 변경됩니다. 마법 카드로 파괴한 타일의 점수가 x배수가 됩니다.</t>
   </si>
   <si>
+    <t>Every stage, the Mana cost of Magic cards randomly changes between x and x. Scores for tiles destroyed by Magic cards are multiplied by x.</t>
+  </si>
+  <si>
     <t>relic207_Des</t>
   </si>
   <si>
     <t>마법 태그 카드로 파괴한 타일에 +x 배수의 점수를 추가합니다. 마법 태그 카드의 요구 마나 x마다 효과가 x만큼 줄어듭니다.</t>
   </si>
   <si>
+    <t>Adds an x multiplier to the score of tiles destroyed by Magic tag cards. The effect decreases by x for every x Mana required by the Magic tag card.</t>
+  </si>
+  <si>
     <t>relic208_Des</t>
   </si>
   <si>
     <t>마법 태그 카드를 사용할 때, x% 확률로 이번 스테이지에서 동일한 카드를 생성합니다. x%확률로 사용한 카드가 영구적으로 개구리가 됩니다.</t>
   </si>
   <si>
+    <t>When using a Magic tag card, there is an x% chance to create a duplicate card for this stage. There is an x% chance the used card permanently turns into a Frog.</t>
+  </si>
+  <si>
     <t>relic209_Des</t>
   </si>
   <si>
     <t>누적 x번째로 사용하는 마법 카드의 요구 마나가 x 감소합니다.</t>
   </si>
   <si>
+    <t>The Mana cost of the cumulative x-th Magic card used is reduced by x.</t>
+  </si>
+  <si>
     <t>relic210_Des</t>
   </si>
   <si>
@@ -1835,96 +2715,144 @@
     <t>사용 시 다음에 사용하는 마법 태그 카드의 요구 마나가 x로 고정됩니다.</t>
   </si>
   <si>
+    <t>Upon use, the Mana cost of the next Magic tag card is fixed at x.</t>
+  </si>
+  <si>
     <t>relic214_Des</t>
   </si>
   <si>
     <t>본래 #얼음,#전기 태그가 없는 #마법 카드에 #화염 태그 추가</t>
   </si>
   <si>
+    <t>Adds #Fire tag to #Magic cards that originally do not have #Ice or #Electric tags.</t>
+  </si>
+  <si>
     <t>relic215_Des</t>
   </si>
   <si>
     <t>본래 #화염,#전기 태그가 없는 #마법 카드에 #얼음 태그 추가</t>
   </si>
   <si>
+    <t>Adds #Ice tag to #Magic cards that originally do not have #Fire or #Electric tags.</t>
+  </si>
+  <si>
     <t>relic216_Des</t>
   </si>
   <si>
     <t>본래 #화염,#얼음 태그가 없는 #마법 카드에 #전기 태그 추가</t>
   </si>
   <si>
+    <t>Adds #Electric tag to #Magic cards that originally do not have #Fire or #Ice tags.</t>
+  </si>
+  <si>
     <t>relic217_Des</t>
   </si>
   <si>
     <t>#화염#얼음#전기가 없는 #마법 카드에 매 턴 #화염, #얼음, #전기 중 하나를 순차적으로 부여</t>
   </si>
   <si>
+    <t>Every turn, sequentially grants either #Fire, #Ice, or #Electric to #Magic cards without those tags.</t>
+  </si>
+  <si>
     <t>relic218_Des</t>
   </si>
   <si>
     <t>#화염,#마법 태그가 있는 카드의 #마법 태그 제거, 파괴확률/효과확률 (Value1)배</t>
   </si>
   <si>
+    <t>Removes #Magic tag from cards with #Fire and #Magic tags; increases destruction/effect probability by (Value1)x.</t>
+  </si>
+  <si>
     <t>relic219_Des</t>
   </si>
   <si>
     <t>#얼음,#마법 태그가 있는 카드의 #마법 태그 제거, 파괴확률/효과확률 (Value1)배</t>
   </si>
   <si>
+    <t>Removes #Magic tag from cards with #Ice and #Magic tags; increases destruction/effect probability by (Value1)x.</t>
+  </si>
+  <si>
     <t>relic220_Des</t>
   </si>
   <si>
     <t>#전기,#마법 태그가 있는 카드의 #마법 태그 제거, 파괴확률/효과확률 (Value1)배</t>
   </si>
   <si>
+    <t>Removes #Magic tag from cards with #Electric and #Magic tags; increases destruction/effect probability by (Value1)x.</t>
+  </si>
+  <si>
     <t>relic221_Des</t>
   </si>
   <si>
     <t>#화염 태그 카드 사용시, (Value1)%확률로 손패에 사용한 카드 생성</t>
   </si>
   <si>
+    <t>When using a #Fire tag card, there is a (Value1)% chance to create a copy of the card in hand.</t>
+  </si>
+  <si>
     <t>relic222_Des</t>
   </si>
   <si>
     <t>#도구 카드에 #화염 태그 추가, 도구 카드 파괴 고정확률 +(Value1)%</t>
   </si>
   <si>
+    <t>Adds #Fire tag to #Tool cards; adds +(Value1)% to the fixed destruction probability of Tool cards.</t>
+  </si>
+  <si>
     <t>relic223_Des</t>
   </si>
   <si>
     <t>매 턴 각 #연소 타일이 (Value1)%확률로 연소를 고려하지않은 파괴 점수를 다시 얻음</t>
   </si>
   <si>
+    <t>Each turn, each #Burn tile has a (Value1)% chance to regain its destruction score (excluding the burn bonus).</t>
+  </si>
+  <si>
     <t>relic224_Des</t>
   </si>
   <si>
     <t>#연소 타일 파괴시 (Value1)% 확률로 손패에 랜덤한 #화염 카드 임시(이번 스테이지) 생성</t>
   </si>
   <si>
+    <t>When a #Burn tile is destroyed, there is a (Value1)% chance to create a temporary random #Fire card in hand for this stage.</t>
+  </si>
+  <si>
     <t>relic225_Des</t>
   </si>
   <si>
     <t>#연소 타일 파괴시 (Value1)% 확률로 새 타일 생성</t>
   </si>
   <si>
+    <t>When a #Burn tile is destroyed, there is a (Value1)% chance to generate a new tile.</t>
+  </si>
+  <si>
     <t>relic226_Des</t>
   </si>
   <si>
     <t>#연소 부여시 얻는 점수 배율 +(value1)</t>
   </si>
   <si>
+    <t>Increases score multiplier when applying #Burn by +(Value1).</t>
+  </si>
+  <si>
     <t>relic227_Des</t>
   </si>
   <si>
     <t>존재하는 #연소 타일 1개당 타일 기본 파괴 점수 +(Value1)</t>
   </si>
   <si>
+    <t>Adds +(Value1) to the base tile destruction score for each existing #Burn tile.</t>
+  </si>
+  <si>
     <t>relic228_Des</t>
   </si>
   <si>
     <t>#연소 타일의 파괴 점수가 +(Value1)가 된다. #연소 타일 점수 배율 +0.25</t>
   </si>
   <si>
+    <t>#Burn tile destruction score becomes +(Value1). Increases #Burn tile score multiplier by +0.25.</t>
+  </si>
+  <si>
     <t>relic229_Des</t>
   </si>
   <si>
@@ -1934,223 +2862,337 @@
     <t>#연소 타일의 파괴 점수가 +(Value1)가 된다.</t>
   </si>
   <si>
+    <t>#Burn tile destruction score becomes +(Value1).</t>
+  </si>
+  <si>
     <t>relic231_Des</t>
   </si>
   <si>
     <t>#연소 타일 점수 배율 +(Value1)</t>
   </si>
   <si>
+    <t>Increases #Burn tile score multiplier by +(Value1).</t>
+  </si>
+  <si>
     <t>relic232_Des</t>
   </si>
   <si>
     <t>#얼음 태그 카드의 파괴 확률이 (Value1)%까지 감소, 감소한 확률만큼 #빙결 부여 확률 상승</t>
   </si>
   <si>
+    <t>#Ice tag card destruction probability decreases to (Value1)%; #Freeze application probability increases by the amount reduced.</t>
+  </si>
+  <si>
     <t>relic233_Des</t>
   </si>
   <si>
     <t>#얼음 태그 카드 사용시, (Value1)%확률로 손패에 사용한 카드 생성</t>
   </si>
   <si>
+    <t>When using an #Ice tag card, there is a (Value1)% chance to create a copy of the card in hand.</t>
+  </si>
+  <si>
     <t>relic234_Des</t>
   </si>
   <si>
     <t>매 턴 각 #빙결 타일이 (V1)%확률로 인접한 타일 한 칸에 #빙결 부여</t>
   </si>
   <si>
+    <t>Each turn, each #Freeze tile has a (V1)% chance to apply #Freeze to one adjacent tile.</t>
+  </si>
+  <si>
     <t>relic235_Des</t>
   </si>
   <si>
     <t>#빙결 타일 파괴 연쇄시 #빙결 타일 파괴 점수 배율 +(V1), 턴 시작시 배율 초기화</t>
   </si>
   <si>
+    <t>When #Freeze tiles are destroyed in a chain, #Freeze tile destruction score multiplier increases by +(V1); multiplier resets at the start of the turn.</t>
+  </si>
+  <si>
     <t>relic236_Des</t>
   </si>
   <si>
     <t>#빙결 타일 파괴 연쇄시 #빙결 타일 파괴 점수가 +(V1)이 된다. 턴 시작시 파괴 점수 초기화</t>
   </si>
   <si>
+    <t>When #Freeze tiles are destroyed in a chain, #Freeze tile destruction score becomes +(V1); destruction score resets at the start of the turn.</t>
+  </si>
+  <si>
     <t>relic237_Des</t>
   </si>
   <si>
     <t>#빙결 타일을 직선 8칸으로 이을 때마다 #빙결 타일 파괴 점수 배율 +(V1) (최대 +(V2))</t>
   </si>
   <si>
+    <t>Gain +#Freeze tile destruction score multiplier of +(V1) for every 8 #Freeze tiles connected in a straight line (Up to +(V2)).</t>
+  </si>
+  <si>
     <t>relic238_Des</t>
   </si>
   <si>
     <t>#빙결 타일 파괴 점수 배율 +(V1)</t>
   </si>
   <si>
+    <t>Increases #Freeze tile destruction score multiplier by +(V1).</t>
+  </si>
+  <si>
     <t>relic239_Des</t>
   </si>
   <si>
     <t>마지막 카드 사용 후 무작위 타일 1칸 파괴, #빙결 타일에 우선 적용</t>
   </si>
   <si>
+    <t>After using the last card, destroy one random tile; prioritizes #Freeze tiles.</t>
+  </si>
+  <si>
     <t>relic240_Des</t>
   </si>
   <si>
     <t>#빙결 타일의 파괴 점수가 +(V1)가 된다. #빙결 타일 점수 배율 +(V2)</t>
   </si>
   <si>
+    <t>#Freeze tile destruction score becomes +(V1). Increases #Freeze tile score multiplier by +(V2).</t>
+  </si>
+  <si>
     <t>relic241_Des</t>
   </si>
   <si>
     <t>#전기 태그 카드 사용시 (V1)% 확률로 마나 (V2) 획득</t>
   </si>
   <si>
+    <t>When using an #Electric tag card, there is a (V1)% chance to gain (V2) Mana.</t>
+  </si>
+  <si>
     <t>relic242_Des</t>
   </si>
   <si>
     <t>#전기 태그 카드 (V1)장 사용시 손패에 #전기 카드 생성</t>
   </si>
   <si>
+    <t>After using (V1) #Electric tag cards, create an #Electric card in hand.</t>
+  </si>
+  <si>
     <t>relic243_Des</t>
   </si>
   <si>
     <t>매 턴 각 #감전 타일이 점수를 얻을 때 (V1)%확률로 한 번 더 발동</t>
   </si>
   <si>
+    <t>Each turn, when an #Electrified tile gains points, there is a (V1)% chance it triggers once more.</t>
+  </si>
+  <si>
     <t>relic244_Des</t>
   </si>
   <si>
     <t>#감전 타일 파괴 시 점수를 얻지도 잃지도 않음</t>
   </si>
   <si>
+    <t>Neither gain nor lose points when an #Electrified tile is destroyed.</t>
+  </si>
+  <si>
     <t>relic245_Des</t>
   </si>
   <si>
     <t>#감전 타일의 파괴 점수 +(V1)</t>
   </si>
   <si>
+    <t>Adds +(V1) to the destruction score of #Electrified tiles.</t>
+  </si>
+  <si>
     <t>relic246_Des</t>
   </si>
   <si>
     <t>#감전 타일 효과 배율 +(V1)</t>
   </si>
   <si>
+    <t>Increases #Electrified tile effect multiplier by +(V1).</t>
+  </si>
+  <si>
     <t>relic247_Des</t>
   </si>
   <si>
     <t>#감전 타일이 인접한 감전 타일 하나마다 #감전 타일 효과 배율+(V1)(상하좌우 최대 4번)</t>
   </si>
   <si>
+    <t>Each #Electrified tile increases its effect multiplier by +(V1) for every adjacent electrified tile (Max 4 times: Up, Down, Left, Right).</t>
+  </si>
+  <si>
     <t>relic248_Des</t>
   </si>
   <si>
     <t>마지막 카드를 사용했을 때 #감전 타일 효과가 (V1)번 더 발동</t>
   </si>
   <si>
+    <t>Trigger #Electrified tile effect (V1) additional times when the last card is used.</t>
+  </si>
+  <si>
     <t>relic249_Des</t>
   </si>
   <si>
     <t>매 턴 랜덤 타일 1개에 #감전 부여, #감전, 함정 타일에 발동하지 않음</t>
   </si>
   <si>
+    <t>Every turn, apply #Electrified to one random tile; does not apply to already electrified or trap tiles.</t>
+  </si>
+  <si>
     <t>relic250_Des</t>
   </si>
   <si>
     <t>#감전 타일의 파괴 점수가 +(V1)가 된다. #감전 타일 효과 배율 +(V2)</t>
   </si>
   <si>
+    <t>#Electrified tile destruction score becomes +(V1). Increases #Electrified tile effect multiplier by +(V2).</t>
+  </si>
+  <si>
     <t>relic251_Des</t>
   </si>
   <si>
     <t>#마법 카드의 소모 마나 (V1)증가, #화염,#얼음,#전기 카드 사용시 각각 다음에 사용하는 #얼음,#전기,#화염 카드의 소모 마나 (V2) 감소</t>
   </si>
   <si>
+    <t>Increase #Magic card Mana cost by (V1). Using #Fire, #Ice, or #Electric cards reduces the Mana cost of the next #Ice, #Electric, or #Fire card used by (V2), respectively.</t>
+  </si>
+  <si>
     <t>relic252_Des</t>
   </si>
   <si>
     <t>#화염 #얼음 #전기 순으로 카드 (V1)장 사용시 손 패에 #화염,#얼음,#전기 카드 중 1장 랜덤 (이번 스테이지) 생성</t>
   </si>
   <si>
+    <t>After using (V1) cards in the order of #Fire, #Ice, and #Electric, create one random #Fire, #Ice, or #Electric card in hand (Temporary for this stage).</t>
+  </si>
+  <si>
     <t>relic253_Des</t>
   </si>
   <si>
     <t>#연소 부여 점수 제거, #연소 타일에 #빙결이 부여되었을 때 #연소 부여 점수(파괴 점수)의 (V1)배를 얻음</t>
   </si>
   <si>
+    <t>Removes score for applying #Burn. When #Freeze is applied to a #Burn tile, gain (V1)x the burn application score (destruction score).</t>
+  </si>
+  <si>
     <t>relic254_Des</t>
   </si>
   <si>
     <t>#빙결의 연쇄 파괴 효과 제거, #빙결 타일에 #감전이 부여되었을 때 인접한 #빙결 타일에 모두 #감전을 부여</t>
   </si>
   <si>
+    <t>Removes the chain destruction effect of #Freeze. When #Electrified is applied to a #Freeze tile, apply #Electrified to all adjacent #Freeze tiles.</t>
+  </si>
+  <si>
     <t>relic255_Des</t>
   </si>
   <si>
     <t>#감전의 점수 배율 (V1)배, #감전 파괴 리스크 제거, #감전 타일에 #연소가 부여되어 있을 때 #감전의 점수 배율 (V2)배로 변경</t>
   </si>
   <si>
+    <t>#Electrified score multiplier becomes (V1)x and removes electrification destruction risk. If #Burn is applied to an #Electrified tile, the score multiplier changes to (V2)x.</t>
+  </si>
+  <si>
     <t>relic256_Des</t>
   </si>
   <si>
     <t>#연소, #빙결, #감전이 모두 부여된 타일의 파괴 점수 +(V1), 그을린 장검/얼어붙은 대검/피뢰침 자검을 모두 소지 시 효과가 (V2)배 증가</t>
   </si>
   <si>
+    <t>Destruction score +(V1) for tiles with all three tags: #Burn, #Freeze, and #Electrified. Effect increases (V2)x if possessing Singed Longsword, Frozen Greatsword, and Lightning Rod Rapier simultaneously.</t>
+  </si>
+  <si>
     <t>Tag_Name_1</t>
   </si>
   <si>
     <t>무기</t>
   </si>
   <si>
+    <t>Weapon</t>
+  </si>
+  <si>
     <t>Tag_Name_2</t>
   </si>
   <si>
+    <t>Name</t>
+  </si>
+  <si>
     <t>Tag_Name_3</t>
   </si>
   <si>
     <t>화염</t>
   </si>
   <si>
+    <t>Flame</t>
+  </si>
+  <si>
     <t>Tag_Name_4</t>
   </si>
   <si>
     <t>얼음</t>
   </si>
   <si>
+    <t>Ice</t>
+  </si>
+  <si>
     <t>Tag_Name_5</t>
   </si>
   <si>
     <t>전기</t>
   </si>
   <si>
+    <t>Lightning</t>
+  </si>
+  <si>
     <t>Tag_Name_6</t>
   </si>
   <si>
     <t>도구</t>
   </si>
   <si>
+    <t>Tool</t>
+  </si>
+  <si>
     <t>Tag_Name_7</t>
   </si>
   <si>
     <t>황금</t>
   </si>
   <si>
+    <t>Golden</t>
+  </si>
+  <si>
     <t>Tag_Name_8</t>
   </si>
   <si>
     <t>일회성</t>
   </si>
   <si>
+    <t>One-time</t>
+  </si>
+  <si>
     <t>Tag_Name_9</t>
   </si>
   <si>
     <t>마나</t>
   </si>
   <si>
+    <t>Mana</t>
+  </si>
+  <si>
     <t>Tag_Name_10</t>
   </si>
   <si>
     <t>마법</t>
   </si>
   <si>
+    <t>Magic</t>
+  </si>
+  <si>
     <t>Tag_Des_1</t>
   </si>
   <si>
     <t>무기_설명</t>
+  </si>
+  <si>
+    <t>Des</t>
   </si>
   <si>
     <t>Tag_Des_2</t>
@@ -2282,39 +3324,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -2366,7 +3408,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -2477,6 +3519,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -2485,13 +3534,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -2556,38 +3598,18 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A1C65B3-0719-48A1-B58C-DDECFA97572F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{145269B2-AE5F-425A-BBAD-F17DF001F17D}">
   <dimension ref="A1:C363"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -2610,3978 +3632,3978 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="C19" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="C20" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="B21" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C21" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="C22" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="B23" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="C23" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="B24" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="C24" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="B25" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="C25" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="B26" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="C26" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="B27" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="C27" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="B28" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="C28" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="C29" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="B30" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="B31" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="C31" t="s">
-        <v>62</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="B32" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="C32" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="B33" t="s">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="C33" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="B34" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="C34" t="s">
-        <v>68</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="B35" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="C35" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="B36" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="C36" t="s">
-        <v>72</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="B37" t="s">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="C37" t="s">
-        <v>74</v>
+        <v>110</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="B38" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="C38" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="B39" t="s">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="C39" t="s">
-        <v>78</v>
+        <v>116</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="B40" t="s">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="C40" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="B41" t="s">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="C41" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="B42" t="s">
-        <v>84</v>
+        <v>124</v>
       </c>
       <c r="C42" t="s">
-        <v>84</v>
+        <v>125</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="B43" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="C43" t="s">
-        <v>86</v>
+        <v>128</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>87</v>
+        <v>129</v>
       </c>
       <c r="B44" t="s">
-        <v>88</v>
+        <v>130</v>
       </c>
       <c r="C44" t="s">
-        <v>88</v>
+        <v>131</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>89</v>
+        <v>132</v>
       </c>
       <c r="B45" t="s">
-        <v>90</v>
+        <v>133</v>
       </c>
       <c r="C45" t="s">
-        <v>90</v>
+        <v>134</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="B46" t="s">
-        <v>92</v>
+        <v>136</v>
       </c>
       <c r="C46" t="s">
-        <v>92</v>
+        <v>137</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>93</v>
+        <v>138</v>
       </c>
       <c r="B47" t="s">
-        <v>94</v>
+        <v>139</v>
       </c>
       <c r="C47" t="s">
-        <v>94</v>
+        <v>140</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>95</v>
+        <v>141</v>
       </c>
       <c r="B48" t="s">
-        <v>96</v>
+        <v>142</v>
       </c>
       <c r="C48" t="s">
-        <v>96</v>
+        <v>143</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>97</v>
+        <v>144</v>
       </c>
       <c r="B49" t="s">
-        <v>98</v>
+        <v>145</v>
       </c>
       <c r="C49" t="s">
-        <v>98</v>
+        <v>146</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>99</v>
+        <v>147</v>
       </c>
       <c r="B50" t="s">
-        <v>100</v>
+        <v>148</v>
       </c>
       <c r="C50" t="s">
-        <v>100</v>
+        <v>149</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>101</v>
+        <v>150</v>
       </c>
       <c r="B51" t="s">
-        <v>102</v>
+        <v>151</v>
       </c>
       <c r="C51" t="s">
-        <v>102</v>
+        <v>152</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>103</v>
+        <v>153</v>
       </c>
       <c r="B52" t="s">
-        <v>104</v>
+        <v>154</v>
       </c>
       <c r="C52" t="s">
-        <v>104</v>
+        <v>155</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>105</v>
+        <v>156</v>
       </c>
       <c r="B53" t="s">
-        <v>106</v>
+        <v>157</v>
       </c>
       <c r="C53" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>107</v>
+        <v>159</v>
       </c>
       <c r="B54" t="s">
-        <v>108</v>
+        <v>160</v>
       </c>
       <c r="C54" t="s">
-        <v>108</v>
+        <v>161</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>109</v>
+        <v>162</v>
       </c>
       <c r="B55" t="s">
-        <v>110</v>
+        <v>163</v>
       </c>
       <c r="C55" t="s">
-        <v>110</v>
+        <v>164</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>111</v>
+        <v>165</v>
       </c>
       <c r="B56" t="s">
-        <v>112</v>
+        <v>166</v>
       </c>
       <c r="C56" t="s">
-        <v>112</v>
+        <v>167</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>113</v>
+        <v>168</v>
       </c>
       <c r="B57" t="s">
-        <v>114</v>
+        <v>169</v>
       </c>
       <c r="C57" t="s">
-        <v>114</v>
+        <v>170</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="B58" t="s">
-        <v>116</v>
+        <v>172</v>
       </c>
       <c r="C58" t="s">
-        <v>116</v>
+        <v>173</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="B59" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="C59" t="s">
-        <v>118</v>
+        <v>176</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>119</v>
+        <v>177</v>
       </c>
       <c r="B60" t="s">
-        <v>120</v>
+        <v>178</v>
       </c>
       <c r="C60" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>121</v>
+        <v>180</v>
       </c>
       <c r="B61" t="s">
-        <v>122</v>
+        <v>181</v>
       </c>
       <c r="C61" t="s">
-        <v>122</v>
+        <v>182</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>123</v>
+        <v>183</v>
       </c>
       <c r="B62" t="s">
-        <v>124</v>
+        <v>184</v>
       </c>
       <c r="C62" t="s">
-        <v>124</v>
+        <v>185</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>125</v>
+        <v>186</v>
       </c>
       <c r="B63" t="s">
-        <v>126</v>
+        <v>187</v>
       </c>
       <c r="C63" t="s">
-        <v>126</v>
+        <v>188</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>127</v>
+        <v>189</v>
       </c>
       <c r="B64" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="C64" t="s">
-        <v>128</v>
+        <v>191</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>129</v>
+        <v>192</v>
       </c>
       <c r="B65" t="s">
-        <v>130</v>
+        <v>193</v>
       </c>
       <c r="C65" t="s">
-        <v>130</v>
+        <v>194</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>131</v>
+        <v>195</v>
       </c>
       <c r="B66" t="s">
-        <v>132</v>
+        <v>196</v>
       </c>
       <c r="C66" t="s">
-        <v>132</v>
+        <v>197</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>133</v>
+        <v>198</v>
       </c>
       <c r="B67" t="s">
-        <v>134</v>
+        <v>199</v>
       </c>
       <c r="C67" t="s">
-        <v>134</v>
+        <v>200</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>135</v>
+        <v>201</v>
       </c>
       <c r="B68" t="s">
-        <v>136</v>
+        <v>202</v>
       </c>
       <c r="C68" t="s">
-        <v>136</v>
+        <v>203</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>137</v>
+        <v>204</v>
       </c>
       <c r="B69" t="s">
-        <v>138</v>
+        <v>205</v>
       </c>
       <c r="C69" t="s">
-        <v>138</v>
+        <v>206</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>139</v>
+        <v>207</v>
       </c>
       <c r="B70" t="s">
-        <v>140</v>
+        <v>208</v>
       </c>
       <c r="C70" t="s">
-        <v>140</v>
+        <v>209</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>141</v>
+        <v>210</v>
       </c>
       <c r="B71" t="s">
-        <v>142</v>
+        <v>211</v>
       </c>
       <c r="C71" t="s">
-        <v>142</v>
+        <v>212</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>143</v>
+        <v>213</v>
       </c>
       <c r="B72" t="s">
-        <v>144</v>
+        <v>214</v>
       </c>
       <c r="C72" t="s">
-        <v>144</v>
+        <v>215</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>145</v>
+        <v>216</v>
       </c>
       <c r="B73" t="s">
-        <v>146</v>
+        <v>217</v>
       </c>
       <c r="C73" t="s">
-        <v>146</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>147</v>
+        <v>219</v>
       </c>
       <c r="B74" t="s">
-        <v>148</v>
+        <v>220</v>
       </c>
       <c r="C74" t="s">
-        <v>148</v>
+        <v>221</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>149</v>
+        <v>222</v>
       </c>
       <c r="B75" t="s">
-        <v>150</v>
+        <v>223</v>
       </c>
       <c r="C75" t="s">
-        <v>150</v>
+        <v>224</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>151</v>
+        <v>225</v>
       </c>
       <c r="B76" t="s">
-        <v>152</v>
+        <v>226</v>
       </c>
       <c r="C76" t="s">
-        <v>152</v>
+        <v>227</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>153</v>
+        <v>228</v>
       </c>
       <c r="B77" t="s">
-        <v>154</v>
+        <v>229</v>
       </c>
       <c r="C77" t="s">
-        <v>154</v>
+        <v>230</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>155</v>
+        <v>231</v>
       </c>
       <c r="B78" t="s">
-        <v>156</v>
+        <v>232</v>
       </c>
       <c r="C78" t="s">
-        <v>156</v>
+        <v>233</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>157</v>
+        <v>234</v>
       </c>
       <c r="B79" t="s">
-        <v>158</v>
+        <v>235</v>
       </c>
       <c r="C79" t="s">
-        <v>158</v>
+        <v>236</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>159</v>
+        <v>237</v>
       </c>
       <c r="B80" t="s">
-        <v>160</v>
+        <v>238</v>
       </c>
       <c r="C80" t="s">
-        <v>160</v>
+        <v>239</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>161</v>
+        <v>240</v>
       </c>
       <c r="B81" t="s">
-        <v>162</v>
+        <v>241</v>
       </c>
       <c r="C81" t="s">
-        <v>162</v>
+        <v>242</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>163</v>
+        <v>243</v>
       </c>
       <c r="B82" t="s">
-        <v>164</v>
+        <v>244</v>
       </c>
       <c r="C82" t="s">
-        <v>164</v>
+        <v>245</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>165</v>
+        <v>246</v>
       </c>
       <c r="B83" t="s">
-        <v>166</v>
+        <v>247</v>
       </c>
       <c r="C83" t="s">
-        <v>166</v>
+        <v>248</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>167</v>
+        <v>249</v>
       </c>
       <c r="B84" t="s">
-        <v>168</v>
+        <v>250</v>
       </c>
       <c r="C84" t="s">
-        <v>168</v>
+        <v>251</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>169</v>
+        <v>252</v>
       </c>
       <c r="B85" t="s">
-        <v>170</v>
+        <v>253</v>
       </c>
       <c r="C85" t="s">
-        <v>170</v>
+        <v>254</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>171</v>
+        <v>255</v>
       </c>
       <c r="B86" t="s">
-        <v>172</v>
+        <v>256</v>
       </c>
       <c r="C86" t="s">
-        <v>172</v>
+        <v>257</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>173</v>
+        <v>258</v>
       </c>
       <c r="B87" t="s">
-        <v>174</v>
+        <v>259</v>
       </c>
       <c r="C87" t="s">
-        <v>174</v>
+        <v>260</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>175</v>
+        <v>261</v>
       </c>
       <c r="B88" t="s">
-        <v>176</v>
+        <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>176</v>
+        <v>263</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>177</v>
+        <v>264</v>
       </c>
       <c r="B89" t="s">
-        <v>178</v>
+        <v>265</v>
       </c>
       <c r="C89" t="s">
-        <v>178</v>
+        <v>266</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>179</v>
+        <v>267</v>
       </c>
       <c r="B90" t="s">
-        <v>180</v>
+        <v>268</v>
       </c>
       <c r="C90" t="s">
-        <v>180</v>
+        <v>269</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>181</v>
+        <v>270</v>
       </c>
       <c r="B91" t="s">
-        <v>182</v>
+        <v>271</v>
       </c>
       <c r="C91" t="s">
-        <v>182</v>
+        <v>272</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>183</v>
+        <v>273</v>
       </c>
       <c r="B92" t="s">
-        <v>184</v>
+        <v>274</v>
       </c>
       <c r="C92" t="s">
-        <v>184</v>
+        <v>275</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>185</v>
+        <v>276</v>
       </c>
       <c r="B93" t="s">
-        <v>186</v>
+        <v>277</v>
       </c>
       <c r="C93" t="s">
-        <v>186</v>
+        <v>278</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>187</v>
+        <v>279</v>
       </c>
       <c r="B94" t="s">
-        <v>188</v>
+        <v>280</v>
       </c>
       <c r="C94" t="s">
-        <v>188</v>
+        <v>281</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>189</v>
+        <v>282</v>
       </c>
       <c r="B95" t="s">
-        <v>190</v>
+        <v>283</v>
       </c>
       <c r="C95" t="s">
-        <v>190</v>
+        <v>284</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>191</v>
+        <v>285</v>
       </c>
       <c r="B96" t="s">
-        <v>192</v>
+        <v>286</v>
       </c>
       <c r="C96" t="s">
-        <v>192</v>
+        <v>287</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>193</v>
+        <v>288</v>
       </c>
       <c r="B97" t="s">
-        <v>194</v>
+        <v>289</v>
       </c>
       <c r="C97" t="s">
-        <v>194</v>
+        <v>290</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>195</v>
+        <v>291</v>
       </c>
       <c r="B98" t="s">
-        <v>196</v>
+        <v>292</v>
       </c>
       <c r="C98" t="s">
-        <v>196</v>
+        <v>293</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>197</v>
+        <v>294</v>
       </c>
       <c r="B99" t="s">
-        <v>198</v>
+        <v>295</v>
       </c>
       <c r="C99" t="s">
-        <v>198</v>
+        <v>296</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>199</v>
+        <v>297</v>
       </c>
       <c r="B100" t="s">
-        <v>200</v>
+        <v>298</v>
       </c>
       <c r="C100" t="s">
-        <v>200</v>
+        <v>299</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>201</v>
+        <v>300</v>
       </c>
       <c r="B101" t="s">
-        <v>202</v>
+        <v>301</v>
       </c>
       <c r="C101" t="s">
-        <v>202</v>
+        <v>302</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>203</v>
+        <v>303</v>
       </c>
       <c r="B102" t="s">
-        <v>204</v>
+        <v>304</v>
       </c>
       <c r="C102" t="s">
-        <v>204</v>
+        <v>305</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>205</v>
+        <v>306</v>
       </c>
       <c r="B103" t="s">
-        <v>206</v>
+        <v>307</v>
       </c>
       <c r="C103" t="s">
-        <v>206</v>
+        <v>308</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>207</v>
+        <v>309</v>
       </c>
       <c r="B104" t="s">
-        <v>208</v>
+        <v>310</v>
       </c>
       <c r="C104" t="s">
-        <v>208</v>
+        <v>311</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>209</v>
+        <v>312</v>
       </c>
       <c r="B105" t="s">
-        <v>210</v>
+        <v>313</v>
       </c>
       <c r="C105" t="s">
-        <v>210</v>
+        <v>314</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>211</v>
+        <v>315</v>
       </c>
       <c r="B106" t="s">
-        <v>212</v>
+        <v>316</v>
       </c>
       <c r="C106" t="s">
-        <v>212</v>
+        <v>317</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>213</v>
+        <v>318</v>
       </c>
       <c r="B107" t="s">
-        <v>214</v>
+        <v>319</v>
       </c>
       <c r="C107" t="s">
-        <v>214</v>
+        <v>320</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>215</v>
+        <v>321</v>
       </c>
       <c r="B108" t="s">
-        <v>216</v>
+        <v>322</v>
       </c>
       <c r="C108" t="s">
-        <v>216</v>
+        <v>323</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>217</v>
+        <v>324</v>
       </c>
       <c r="B109" t="s">
-        <v>218</v>
+        <v>325</v>
       </c>
       <c r="C109" t="s">
-        <v>218</v>
+        <v>326</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>219</v>
+        <v>327</v>
       </c>
       <c r="B110" t="s">
-        <v>220</v>
+        <v>328</v>
       </c>
       <c r="C110" t="s">
-        <v>220</v>
+        <v>329</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>221</v>
+        <v>330</v>
       </c>
       <c r="B111" t="s">
-        <v>222</v>
+        <v>331</v>
       </c>
       <c r="C111" t="s">
-        <v>222</v>
+        <v>332</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>223</v>
+        <v>333</v>
       </c>
       <c r="B112" t="s">
-        <v>224</v>
+        <v>334</v>
       </c>
       <c r="C112" t="s">
-        <v>224</v>
+        <v>335</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>225</v>
+        <v>336</v>
       </c>
       <c r="B113" t="s">
-        <v>226</v>
+        <v>337</v>
       </c>
       <c r="C113" t="s">
-        <v>226</v>
+        <v>338</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>227</v>
+        <v>339</v>
       </c>
       <c r="B114" t="s">
-        <v>228</v>
+        <v>340</v>
       </c>
       <c r="C114" t="s">
-        <v>228</v>
+        <v>341</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>229</v>
+        <v>342</v>
       </c>
       <c r="B115" t="s">
-        <v>230</v>
+        <v>343</v>
       </c>
       <c r="C115" t="s">
-        <v>230</v>
+        <v>344</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>231</v>
+        <v>345</v>
       </c>
       <c r="B116" t="s">
-        <v>232</v>
+        <v>346</v>
       </c>
       <c r="C116" t="s">
-        <v>232</v>
+        <v>347</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>233</v>
+        <v>348</v>
       </c>
       <c r="B117" t="s">
-        <v>234</v>
+        <v>349</v>
       </c>
       <c r="C117" t="s">
-        <v>234</v>
+        <v>350</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>235</v>
+        <v>351</v>
       </c>
       <c r="B118" t="s">
-        <v>236</v>
+        <v>352</v>
       </c>
       <c r="C118" t="s">
-        <v>236</v>
+        <v>353</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>237</v>
+        <v>354</v>
       </c>
       <c r="B119" t="s">
-        <v>238</v>
+        <v>355</v>
       </c>
       <c r="C119" t="s">
-        <v>238</v>
+        <v>356</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>239</v>
+        <v>357</v>
       </c>
       <c r="B120" t="s">
-        <v>240</v>
+        <v>358</v>
       </c>
       <c r="C120" t="s">
-        <v>240</v>
+        <v>359</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>241</v>
+        <v>360</v>
       </c>
       <c r="B121" t="s">
-        <v>242</v>
+        <v>361</v>
       </c>
       <c r="C121" t="s">
-        <v>242</v>
+        <v>362</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>243</v>
+        <v>363</v>
       </c>
       <c r="B122" t="s">
-        <v>244</v>
+        <v>364</v>
       </c>
       <c r="C122" t="s">
-        <v>244</v>
+        <v>365</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>245</v>
+        <v>366</v>
       </c>
       <c r="B123" t="s">
-        <v>246</v>
+        <v>367</v>
       </c>
       <c r="C123" t="s">
-        <v>246</v>
+        <v>368</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>247</v>
+        <v>369</v>
       </c>
       <c r="B124" t="s">
-        <v>248</v>
+        <v>370</v>
       </c>
       <c r="C124" t="s">
-        <v>248</v>
+        <v>371</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>249</v>
+        <v>372</v>
       </c>
       <c r="B125" t="s">
-        <v>250</v>
+        <v>373</v>
       </c>
       <c r="C125" t="s">
-        <v>250</v>
+        <v>374</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>251</v>
+        <v>375</v>
       </c>
       <c r="B126" t="s">
-        <v>252</v>
+        <v>376</v>
       </c>
       <c r="C126" t="s">
-        <v>252</v>
+        <v>377</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>253</v>
+        <v>378</v>
       </c>
       <c r="B127" t="s">
-        <v>254</v>
+        <v>379</v>
       </c>
       <c r="C127" t="s">
-        <v>254</v>
+        <v>380</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>255</v>
+        <v>381</v>
       </c>
       <c r="B128" t="s">
-        <v>256</v>
+        <v>382</v>
       </c>
       <c r="C128" t="s">
-        <v>256</v>
+        <v>383</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>257</v>
+        <v>384</v>
       </c>
       <c r="B129" t="s">
-        <v>258</v>
+        <v>385</v>
       </c>
       <c r="C129" t="s">
-        <v>258</v>
+        <v>386</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>259</v>
+        <v>387</v>
       </c>
       <c r="B130" t="s">
-        <v>260</v>
+        <v>388</v>
       </c>
       <c r="C130" t="s">
-        <v>260</v>
+        <v>389</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>261</v>
+        <v>390</v>
       </c>
       <c r="B131" t="s">
-        <v>262</v>
+        <v>391</v>
       </c>
       <c r="C131" t="s">
-        <v>262</v>
+        <v>392</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>263</v>
+        <v>393</v>
       </c>
       <c r="B132" t="s">
-        <v>264</v>
+        <v>394</v>
       </c>
       <c r="C132" t="s">
-        <v>264</v>
+        <v>395</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>265</v>
+        <v>396</v>
       </c>
       <c r="B133" t="s">
-        <v>266</v>
+        <v>397</v>
       </c>
       <c r="C133" t="s">
-        <v>266</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>267</v>
+        <v>399</v>
       </c>
       <c r="B134" t="s">
-        <v>268</v>
+        <v>400</v>
       </c>
       <c r="C134" t="s">
-        <v>268</v>
+        <v>401</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>269</v>
+        <v>402</v>
       </c>
       <c r="B135" t="s">
-        <v>270</v>
+        <v>403</v>
       </c>
       <c r="C135" t="s">
-        <v>270</v>
+        <v>404</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>271</v>
+        <v>405</v>
       </c>
       <c r="B136" t="s">
-        <v>272</v>
+        <v>406</v>
       </c>
       <c r="C136" t="s">
-        <v>272</v>
+        <v>407</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>273</v>
+        <v>408</v>
       </c>
       <c r="B137" t="s">
-        <v>274</v>
+        <v>409</v>
       </c>
       <c r="C137" t="s">
-        <v>274</v>
+        <v>410</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>275</v>
+        <v>411</v>
       </c>
       <c r="B138" t="s">
-        <v>276</v>
+        <v>412</v>
       </c>
       <c r="C138" t="s">
-        <v>276</v>
+        <v>413</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>277</v>
+        <v>414</v>
       </c>
       <c r="B139" t="s">
-        <v>278</v>
+        <v>415</v>
       </c>
       <c r="C139" t="s">
-        <v>278</v>
+        <v>416</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>279</v>
+        <v>417</v>
       </c>
       <c r="B140" t="s">
-        <v>280</v>
+        <v>418</v>
       </c>
       <c r="C140" t="s">
-        <v>280</v>
+        <v>419</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>281</v>
+        <v>420</v>
       </c>
       <c r="B141" t="s">
-        <v>282</v>
+        <v>421</v>
       </c>
       <c r="C141" t="s">
-        <v>282</v>
+        <v>422</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>283</v>
+        <v>423</v>
       </c>
       <c r="B142" t="s">
-        <v>284</v>
+        <v>424</v>
       </c>
       <c r="C142" t="s">
-        <v>284</v>
+        <v>425</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>285</v>
+        <v>426</v>
       </c>
       <c r="B143" t="s">
-        <v>286</v>
+        <v>427</v>
       </c>
       <c r="C143" t="s">
-        <v>286</v>
+        <v>428</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>287</v>
+        <v>429</v>
       </c>
       <c r="B144" t="s">
-        <v>288</v>
+        <v>430</v>
       </c>
       <c r="C144" t="s">
-        <v>288</v>
+        <v>431</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>289</v>
+        <v>432</v>
       </c>
       <c r="B145" t="s">
-        <v>290</v>
+        <v>433</v>
       </c>
       <c r="C145" t="s">
-        <v>290</v>
+        <v>434</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>291</v>
+        <v>435</v>
       </c>
       <c r="B146" t="s">
-        <v>292</v>
+        <v>436</v>
       </c>
       <c r="C146" t="s">
-        <v>292</v>
+        <v>437</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>293</v>
+        <v>438</v>
       </c>
       <c r="B147" t="s">
-        <v>294</v>
+        <v>439</v>
       </c>
       <c r="C147" t="s">
-        <v>294</v>
+        <v>440</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>295</v>
+        <v>441</v>
       </c>
       <c r="B148" t="s">
-        <v>296</v>
+        <v>442</v>
       </c>
       <c r="C148" t="s">
-        <v>296</v>
+        <v>443</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>297</v>
+        <v>444</v>
       </c>
       <c r="B149" t="s">
-        <v>298</v>
+        <v>445</v>
       </c>
       <c r="C149" t="s">
-        <v>298</v>
+        <v>446</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>299</v>
+        <v>447</v>
       </c>
       <c r="B150" t="s">
-        <v>300</v>
+        <v>448</v>
       </c>
       <c r="C150" t="s">
-        <v>300</v>
+        <v>449</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>301</v>
+        <v>450</v>
       </c>
       <c r="B151" t="s">
-        <v>302</v>
+        <v>451</v>
       </c>
       <c r="C151" t="s">
-        <v>302</v>
+        <v>452</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>303</v>
+        <v>453</v>
       </c>
       <c r="B152" t="s">
-        <v>304</v>
+        <v>454</v>
       </c>
       <c r="C152" t="s">
-        <v>304</v>
+        <v>455</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>305</v>
+        <v>456</v>
       </c>
       <c r="B153" t="s">
-        <v>306</v>
+        <v>457</v>
       </c>
       <c r="C153" t="s">
-        <v>306</v>
+        <v>458</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>307</v>
+        <v>459</v>
       </c>
       <c r="B154" t="s">
-        <v>308</v>
+        <v>460</v>
       </c>
       <c r="C154" t="s">
-        <v>308</v>
+        <v>461</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>309</v>
+        <v>462</v>
       </c>
       <c r="B155" t="s">
-        <v>310</v>
+        <v>463</v>
       </c>
       <c r="C155" t="s">
-        <v>310</v>
+        <v>464</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>311</v>
+        <v>465</v>
       </c>
       <c r="B156" t="s">
-        <v>312</v>
+        <v>466</v>
       </c>
       <c r="C156" t="s">
-        <v>312</v>
+        <v>467</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>313</v>
+        <v>468</v>
       </c>
       <c r="B157" t="s">
-        <v>314</v>
+        <v>469</v>
       </c>
       <c r="C157" t="s">
-        <v>314</v>
+        <v>470</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>315</v>
+        <v>471</v>
       </c>
       <c r="B158" t="s">
-        <v>316</v>
+        <v>472</v>
       </c>
       <c r="C158" t="s">
-        <v>316</v>
+        <v>473</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>317</v>
+        <v>474</v>
       </c>
       <c r="B159" t="s">
-        <v>318</v>
+        <v>475</v>
       </c>
       <c r="C159" t="s">
-        <v>318</v>
+        <v>476</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>319</v>
+        <v>477</v>
       </c>
       <c r="B160" t="s">
-        <v>320</v>
+        <v>478</v>
       </c>
       <c r="C160" t="s">
-        <v>320</v>
+        <v>479</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>321</v>
+        <v>480</v>
       </c>
       <c r="B161" t="s">
-        <v>322</v>
+        <v>481</v>
       </c>
       <c r="C161" t="s">
-        <v>322</v>
+        <v>482</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>323</v>
+        <v>483</v>
       </c>
       <c r="B162" t="s">
-        <v>324</v>
+        <v>484</v>
       </c>
       <c r="C162" t="s">
-        <v>324</v>
+        <v>485</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>325</v>
+        <v>486</v>
       </c>
       <c r="B163" t="s">
-        <v>326</v>
+        <v>487</v>
       </c>
       <c r="C163" t="s">
-        <v>326</v>
+        <v>488</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>327</v>
+        <v>489</v>
       </c>
       <c r="B164" t="s">
-        <v>328</v>
+        <v>490</v>
       </c>
       <c r="C164" t="s">
-        <v>328</v>
+        <v>491</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>329</v>
+        <v>492</v>
       </c>
       <c r="B165" t="s">
-        <v>330</v>
+        <v>493</v>
       </c>
       <c r="C165" t="s">
-        <v>330</v>
+        <v>494</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>331</v>
+        <v>495</v>
       </c>
       <c r="B166" t="s">
-        <v>332</v>
+        <v>496</v>
       </c>
       <c r="C166" t="s">
-        <v>332</v>
+        <v>497</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>333</v>
+        <v>498</v>
       </c>
       <c r="B167" t="s">
-        <v>334</v>
+        <v>499</v>
       </c>
       <c r="C167" t="s">
-        <v>334</v>
+        <v>500</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>335</v>
+        <v>501</v>
       </c>
       <c r="B168" t="s">
-        <v>336</v>
+        <v>502</v>
       </c>
       <c r="C168" t="s">
-        <v>336</v>
+        <v>503</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>337</v>
+        <v>504</v>
       </c>
       <c r="B169" t="s">
-        <v>338</v>
+        <v>505</v>
       </c>
       <c r="C169" t="s">
-        <v>338</v>
+        <v>506</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>339</v>
+        <v>507</v>
       </c>
       <c r="B170" t="s">
-        <v>340</v>
+        <v>508</v>
       </c>
       <c r="C170" t="s">
-        <v>340</v>
+        <v>509</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>341</v>
+        <v>510</v>
       </c>
       <c r="B171" t="s">
-        <v>342</v>
+        <v>511</v>
       </c>
       <c r="C171" t="s">
-        <v>342</v>
+        <v>512</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>343</v>
+        <v>513</v>
       </c>
       <c r="B172" t="s">
-        <v>344</v>
+        <v>514</v>
       </c>
       <c r="C172" t="s">
-        <v>344</v>
+        <v>515</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>345</v>
+        <v>516</v>
       </c>
       <c r="B173" t="s">
-        <v>346</v>
+        <v>517</v>
       </c>
       <c r="C173" t="s">
-        <v>346</v>
+        <v>518</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>347</v>
+        <v>519</v>
       </c>
       <c r="B174" t="s">
-        <v>348</v>
+        <v>520</v>
       </c>
       <c r="C174" t="s">
-        <v>348</v>
+        <v>521</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>349</v>
+        <v>522</v>
       </c>
       <c r="B175" t="s">
-        <v>350</v>
+        <v>523</v>
       </c>
       <c r="C175" t="s">
-        <v>350</v>
+        <v>524</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>351</v>
+        <v>525</v>
       </c>
       <c r="B176" t="s">
-        <v>352</v>
+        <v>526</v>
       </c>
       <c r="C176" t="s">
-        <v>352</v>
+        <v>527</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>353</v>
+        <v>528</v>
       </c>
       <c r="B177" t="s">
-        <v>354</v>
+        <v>529</v>
       </c>
       <c r="C177" t="s">
-        <v>354</v>
+        <v>530</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>355</v>
+        <v>531</v>
       </c>
       <c r="B178" t="s">
-        <v>356</v>
+        <v>532</v>
       </c>
       <c r="C178" t="s">
-        <v>356</v>
+        <v>533</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>357</v>
+        <v>534</v>
       </c>
       <c r="B179" t="s">
-        <v>358</v>
+        <v>535</v>
       </c>
       <c r="C179" t="s">
-        <v>358</v>
+        <v>536</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>359</v>
+        <v>537</v>
       </c>
       <c r="B180" t="s">
-        <v>360</v>
+        <v>538</v>
       </c>
       <c r="C180" t="s">
-        <v>360</v>
+        <v>539</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>361</v>
+        <v>540</v>
       </c>
       <c r="B181" t="s">
-        <v>362</v>
+        <v>541</v>
       </c>
       <c r="C181" t="s">
-        <v>362</v>
+        <v>542</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>363</v>
+        <v>543</v>
       </c>
       <c r="B182" t="s">
-        <v>364</v>
+        <v>544</v>
       </c>
       <c r="C182" t="s">
-        <v>364</v>
+        <v>545</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>365</v>
+        <v>546</v>
       </c>
       <c r="B183" t="s">
-        <v>366</v>
+        <v>547</v>
       </c>
       <c r="C183" t="s">
-        <v>366</v>
+        <v>548</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>367</v>
+        <v>549</v>
       </c>
       <c r="B184" t="s">
-        <v>368</v>
+        <v>550</v>
       </c>
       <c r="C184" t="s">
-        <v>368</v>
+        <v>551</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>369</v>
+        <v>552</v>
       </c>
       <c r="B185" t="s">
-        <v>370</v>
+        <v>553</v>
       </c>
       <c r="C185" t="s">
-        <v>370</v>
+        <v>554</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>371</v>
+        <v>555</v>
       </c>
       <c r="B186" t="s">
-        <v>372</v>
+        <v>556</v>
       </c>
       <c r="C186" t="s">
-        <v>372</v>
+        <v>557</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>373</v>
+        <v>558</v>
       </c>
       <c r="B187" t="s">
-        <v>374</v>
+        <v>559</v>
       </c>
       <c r="C187" t="s">
-        <v>374</v>
+        <v>560</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>375</v>
+        <v>561</v>
       </c>
       <c r="B188" t="s">
-        <v>376</v>
+        <v>562</v>
       </c>
       <c r="C188" t="s">
-        <v>376</v>
+        <v>563</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>377</v>
+        <v>564</v>
       </c>
       <c r="B189" t="s">
-        <v>378</v>
+        <v>565</v>
       </c>
       <c r="C189" t="s">
-        <v>378</v>
+        <v>566</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>379</v>
+        <v>567</v>
       </c>
       <c r="B190" t="s">
-        <v>380</v>
+        <v>568</v>
       </c>
       <c r="C190" t="s">
-        <v>380</v>
+        <v>569</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>381</v>
+        <v>570</v>
       </c>
       <c r="B191" t="s">
-        <v>382</v>
+        <v>571</v>
       </c>
       <c r="C191" t="s">
-        <v>382</v>
+        <v>572</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>383</v>
+        <v>573</v>
       </c>
       <c r="B192" t="s">
-        <v>384</v>
+        <v>574</v>
       </c>
       <c r="C192" t="s">
-        <v>384</v>
+        <v>575</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>385</v>
+        <v>576</v>
       </c>
       <c r="B193" t="s">
-        <v>386</v>
+        <v>577</v>
       </c>
       <c r="C193" t="s">
-        <v>386</v>
+        <v>578</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>387</v>
+        <v>579</v>
       </c>
       <c r="B194" t="s">
-        <v>388</v>
+        <v>580</v>
       </c>
       <c r="C194" t="s">
-        <v>388</v>
+        <v>581</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>389</v>
+        <v>582</v>
       </c>
       <c r="B195" t="s">
-        <v>390</v>
+        <v>583</v>
       </c>
       <c r="C195" t="s">
-        <v>390</v>
+        <v>584</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>391</v>
+        <v>585</v>
       </c>
       <c r="B196" t="s">
-        <v>392</v>
+        <v>586</v>
       </c>
       <c r="C196" t="s">
-        <v>392</v>
+        <v>587</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>393</v>
+        <v>588</v>
       </c>
       <c r="B197" t="s">
-        <v>394</v>
+        <v>589</v>
       </c>
       <c r="C197" t="s">
-        <v>394</v>
+        <v>590</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>395</v>
+        <v>591</v>
       </c>
       <c r="B198" t="s">
-        <v>396</v>
+        <v>592</v>
       </c>
       <c r="C198" t="s">
-        <v>396</v>
+        <v>593</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>397</v>
+        <v>594</v>
       </c>
       <c r="B199" t="s">
-        <v>398</v>
+        <v>595</v>
       </c>
       <c r="C199" t="s">
-        <v>398</v>
+        <v>596</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>399</v>
+        <v>597</v>
       </c>
       <c r="B200" t="s">
-        <v>400</v>
+        <v>598</v>
       </c>
       <c r="C200" t="s">
-        <v>400</v>
+        <v>599</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>401</v>
+        <v>600</v>
       </c>
       <c r="B201" t="s">
-        <v>402</v>
+        <v>601</v>
       </c>
       <c r="C201" t="s">
-        <v>402</v>
+        <v>602</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>403</v>
+        <v>603</v>
       </c>
       <c r="B202" t="s">
-        <v>404</v>
+        <v>604</v>
       </c>
       <c r="C202" t="s">
-        <v>404</v>
+        <v>605</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>405</v>
+        <v>606</v>
       </c>
       <c r="B203" t="s">
-        <v>406</v>
+        <v>607</v>
       </c>
       <c r="C203" t="s">
-        <v>406</v>
+        <v>608</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>407</v>
+        <v>609</v>
       </c>
       <c r="B204" t="s">
-        <v>408</v>
+        <v>610</v>
       </c>
       <c r="C204" t="s">
-        <v>408</v>
+        <v>611</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>409</v>
+        <v>612</v>
       </c>
       <c r="B205" t="s">
-        <v>410</v>
+        <v>613</v>
       </c>
       <c r="C205" t="s">
-        <v>410</v>
+        <v>614</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>411</v>
+        <v>615</v>
       </c>
       <c r="B206" t="s">
-        <v>412</v>
+        <v>616</v>
       </c>
       <c r="C206" t="s">
-        <v>412</v>
+        <v>617</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>413</v>
+        <v>618</v>
       </c>
       <c r="B207" t="s">
-        <v>414</v>
+        <v>619</v>
       </c>
       <c r="C207" t="s">
-        <v>414</v>
+        <v>620</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>415</v>
+        <v>621</v>
       </c>
       <c r="B208" t="s">
-        <v>416</v>
+        <v>622</v>
       </c>
       <c r="C208" t="s">
-        <v>416</v>
+        <v>623</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>417</v>
+        <v>624</v>
       </c>
       <c r="B209" t="s">
-        <v>418</v>
+        <v>625</v>
       </c>
       <c r="C209" t="s">
-        <v>418</v>
+        <v>626</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>419</v>
+        <v>627</v>
       </c>
       <c r="B210" t="s">
-        <v>420</v>
+        <v>628</v>
       </c>
       <c r="C210" t="s">
-        <v>420</v>
+        <v>629</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>421</v>
+        <v>630</v>
       </c>
       <c r="B211" t="s">
-        <v>422</v>
+        <v>631</v>
       </c>
       <c r="C211" t="s">
-        <v>422</v>
+        <v>632</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>423</v>
+        <v>633</v>
       </c>
       <c r="B212" t="s">
-        <v>424</v>
+        <v>634</v>
       </c>
       <c r="C212" t="s">
-        <v>424</v>
+        <v>635</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>425</v>
+        <v>636</v>
       </c>
       <c r="B213" t="s">
-        <v>426</v>
+        <v>637</v>
       </c>
       <c r="C213" t="s">
-        <v>426</v>
+        <v>638</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>427</v>
+        <v>639</v>
       </c>
       <c r="B214" t="s">
-        <v>428</v>
+        <v>640</v>
       </c>
       <c r="C214" t="s">
-        <v>428</v>
+        <v>641</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>429</v>
+        <v>642</v>
       </c>
       <c r="B215" t="s">
-        <v>430</v>
+        <v>643</v>
       </c>
       <c r="C215" t="s">
-        <v>430</v>
+        <v>644</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>431</v>
+        <v>645</v>
       </c>
       <c r="B216" t="s">
-        <v>432</v>
+        <v>646</v>
       </c>
       <c r="C216" t="s">
-        <v>432</v>
+        <v>647</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>433</v>
+        <v>648</v>
       </c>
       <c r="B217" t="s">
-        <v>434</v>
+        <v>649</v>
       </c>
       <c r="C217" t="s">
-        <v>434</v>
+        <v>650</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>435</v>
+        <v>651</v>
       </c>
       <c r="B218" t="s">
-        <v>436</v>
+        <v>652</v>
       </c>
       <c r="C218" t="s">
-        <v>436</v>
+        <v>653</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>437</v>
+        <v>654</v>
       </c>
       <c r="B219" t="s">
-        <v>438</v>
+        <v>655</v>
       </c>
       <c r="C219" t="s">
-        <v>438</v>
+        <v>656</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>439</v>
+        <v>657</v>
       </c>
       <c r="B220" t="s">
-        <v>440</v>
+        <v>658</v>
       </c>
       <c r="C220" t="s">
-        <v>440</v>
+        <v>659</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>441</v>
+        <v>660</v>
       </c>
       <c r="B221" t="s">
-        <v>442</v>
+        <v>661</v>
       </c>
       <c r="C221" t="s">
-        <v>442</v>
+        <v>662</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>443</v>
+        <v>663</v>
       </c>
       <c r="B222" t="s">
-        <v>444</v>
+        <v>664</v>
       </c>
       <c r="C222" t="s">
-        <v>444</v>
+        <v>665</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>445</v>
+        <v>666</v>
       </c>
       <c r="B223" t="s">
-        <v>446</v>
+        <v>667</v>
       </c>
       <c r="C223" t="s">
-        <v>446</v>
+        <v>668</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>447</v>
+        <v>669</v>
       </c>
       <c r="B224" t="s">
-        <v>448</v>
+        <v>670</v>
       </c>
       <c r="C224" t="s">
-        <v>448</v>
+        <v>671</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>449</v>
+        <v>672</v>
       </c>
       <c r="B225" t="s">
-        <v>450</v>
+        <v>673</v>
       </c>
       <c r="C225" t="s">
-        <v>450</v>
+        <v>674</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>451</v>
+        <v>675</v>
       </c>
       <c r="B226" t="s">
-        <v>452</v>
+        <v>676</v>
       </c>
       <c r="C226" t="s">
-        <v>452</v>
+        <v>677</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>453</v>
+        <v>678</v>
       </c>
       <c r="B227" t="s">
-        <v>454</v>
+        <v>679</v>
       </c>
       <c r="C227" t="s">
-        <v>454</v>
+        <v>680</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>455</v>
+        <v>681</v>
       </c>
       <c r="B228" t="s">
-        <v>456</v>
+        <v>682</v>
       </c>
       <c r="C228" t="s">
-        <v>456</v>
+        <v>683</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>457</v>
+        <v>684</v>
       </c>
       <c r="B229" t="s">
-        <v>458</v>
+        <v>685</v>
       </c>
       <c r="C229" t="s">
-        <v>458</v>
+        <v>686</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>459</v>
+        <v>687</v>
       </c>
       <c r="B230" t="s">
-        <v>460</v>
+        <v>688</v>
       </c>
       <c r="C230" t="s">
-        <v>460</v>
+        <v>689</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>461</v>
+        <v>690</v>
       </c>
       <c r="B231" t="s">
-        <v>462</v>
+        <v>691</v>
       </c>
       <c r="C231" t="s">
-        <v>462</v>
+        <v>692</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>463</v>
+        <v>693</v>
       </c>
       <c r="B232" t="s">
-        <v>464</v>
+        <v>694</v>
       </c>
       <c r="C232" t="s">
-        <v>464</v>
+        <v>695</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>465</v>
+        <v>696</v>
       </c>
       <c r="B233" t="s">
-        <v>466</v>
+        <v>697</v>
       </c>
       <c r="C233" t="s">
-        <v>466</v>
+        <v>698</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>467</v>
+        <v>699</v>
       </c>
       <c r="B234" t="s">
-        <v>468</v>
+        <v>700</v>
       </c>
       <c r="C234" t="s">
-        <v>468</v>
+        <v>701</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>469</v>
+        <v>702</v>
       </c>
       <c r="B235" t="s">
-        <v>470</v>
+        <v>703</v>
       </c>
       <c r="C235" t="s">
-        <v>470</v>
+        <v>704</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>471</v>
+        <v>705</v>
       </c>
       <c r="B236" t="s">
-        <v>472</v>
+        <v>706</v>
       </c>
       <c r="C236" t="s">
-        <v>472</v>
+        <v>707</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>473</v>
+        <v>708</v>
       </c>
       <c r="B237" t="s">
-        <v>474</v>
+        <v>709</v>
       </c>
       <c r="C237" t="s">
-        <v>474</v>
+        <v>710</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>475</v>
+        <v>711</v>
       </c>
       <c r="B238" t="s">
-        <v>476</v>
+        <v>712</v>
       </c>
       <c r="C238" t="s">
-        <v>476</v>
+        <v>713</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>477</v>
+        <v>714</v>
       </c>
       <c r="B239" t="s">
-        <v>478</v>
+        <v>715</v>
       </c>
       <c r="C239" t="s">
-        <v>478</v>
+        <v>716</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>479</v>
+        <v>717</v>
       </c>
       <c r="B240" t="s">
-        <v>480</v>
+        <v>718</v>
       </c>
       <c r="C240" t="s">
-        <v>480</v>
+        <v>719</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>481</v>
+        <v>720</v>
       </c>
       <c r="B241" t="s">
-        <v>482</v>
+        <v>721</v>
       </c>
       <c r="C241" t="s">
-        <v>482</v>
+        <v>722</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>483</v>
+        <v>723</v>
       </c>
       <c r="B242" t="s">
-        <v>484</v>
+        <v>724</v>
       </c>
       <c r="C242" t="s">
-        <v>484</v>
+        <v>725</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>485</v>
+        <v>726</v>
       </c>
       <c r="B243" t="s">
-        <v>486</v>
+        <v>727</v>
       </c>
       <c r="C243" t="s">
-        <v>486</v>
+        <v>728</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>487</v>
+        <v>729</v>
       </c>
       <c r="B244" t="s">
-        <v>488</v>
+        <v>730</v>
       </c>
       <c r="C244" t="s">
-        <v>488</v>
+        <v>731</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>489</v>
+        <v>732</v>
       </c>
       <c r="B245" t="s">
-        <v>490</v>
+        <v>733</v>
       </c>
       <c r="C245" t="s">
-        <v>490</v>
+        <v>734</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>491</v>
+        <v>735</v>
       </c>
       <c r="B246" t="s">
-        <v>492</v>
+        <v>736</v>
       </c>
       <c r="C246" t="s">
-        <v>492</v>
+        <v>737</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>493</v>
+        <v>738</v>
       </c>
       <c r="B247" t="s">
-        <v>494</v>
+        <v>739</v>
       </c>
       <c r="C247" t="s">
-        <v>494</v>
+        <v>740</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>495</v>
+        <v>741</v>
       </c>
       <c r="B248" t="s">
-        <v>496</v>
+        <v>742</v>
       </c>
       <c r="C248" t="s">
-        <v>496</v>
+        <v>743</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>497</v>
+        <v>744</v>
       </c>
       <c r="B249" t="s">
-        <v>498</v>
+        <v>745</v>
       </c>
       <c r="C249" t="s">
-        <v>498</v>
+        <v>746</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>499</v>
+        <v>747</v>
       </c>
       <c r="B250" t="s">
-        <v>500</v>
+        <v>748</v>
       </c>
       <c r="C250" t="s">
-        <v>500</v>
+        <v>749</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>501</v>
+        <v>750</v>
       </c>
       <c r="B251" t="s">
-        <v>502</v>
+        <v>751</v>
       </c>
       <c r="C251" t="s">
-        <v>502</v>
+        <v>752</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>503</v>
+        <v>753</v>
       </c>
       <c r="B252" t="s">
-        <v>504</v>
+        <v>754</v>
       </c>
       <c r="C252" t="s">
-        <v>504</v>
+        <v>755</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>505</v>
+        <v>756</v>
       </c>
       <c r="B253" t="s">
-        <v>506</v>
+        <v>757</v>
       </c>
       <c r="C253" t="s">
-        <v>506</v>
+        <v>758</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>507</v>
+        <v>759</v>
       </c>
       <c r="B254" t="s">
-        <v>508</v>
+        <v>760</v>
       </c>
       <c r="C254" t="s">
-        <v>508</v>
+        <v>761</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>509</v>
+        <v>762</v>
       </c>
       <c r="B255" t="s">
-        <v>510</v>
+        <v>763</v>
       </c>
       <c r="C255" t="s">
-        <v>510</v>
+        <v>764</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>511</v>
+        <v>765</v>
       </c>
       <c r="B256" t="s">
-        <v>512</v>
+        <v>766</v>
       </c>
       <c r="C256" t="s">
-        <v>512</v>
+        <v>767</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>513</v>
+        <v>768</v>
       </c>
       <c r="B257" t="s">
-        <v>514</v>
+        <v>769</v>
       </c>
       <c r="C257" t="s">
-        <v>514</v>
+        <v>770</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>515</v>
+        <v>771</v>
       </c>
       <c r="B258" t="s">
-        <v>516</v>
+        <v>772</v>
       </c>
       <c r="C258" t="s">
-        <v>516</v>
+        <v>773</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>517</v>
+        <v>774</v>
       </c>
       <c r="B259" t="s">
-        <v>518</v>
+        <v>775</v>
       </c>
       <c r="C259" t="s">
-        <v>518</v>
+        <v>776</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>519</v>
+        <v>777</v>
       </c>
       <c r="B260" t="s">
-        <v>520</v>
+        <v>778</v>
       </c>
       <c r="C260" t="s">
-        <v>520</v>
+        <v>779</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>521</v>
+        <v>780</v>
       </c>
       <c r="B261" t="s">
-        <v>522</v>
+        <v>781</v>
       </c>
       <c r="C261" t="s">
-        <v>522</v>
+        <v>782</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>523</v>
+        <v>783</v>
       </c>
       <c r="B262" t="s">
-        <v>524</v>
+        <v>784</v>
       </c>
       <c r="C262" t="s">
-        <v>524</v>
+        <v>785</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>525</v>
+        <v>786</v>
       </c>
       <c r="B263" t="s">
-        <v>526</v>
+        <v>787</v>
       </c>
       <c r="C263" t="s">
-        <v>526</v>
+        <v>788</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>527</v>
+        <v>789</v>
       </c>
       <c r="B264" t="s">
-        <v>528</v>
+        <v>790</v>
       </c>
       <c r="C264" t="s">
-        <v>528</v>
+        <v>791</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>529</v>
+        <v>792</v>
       </c>
       <c r="B265" t="s">
-        <v>530</v>
+        <v>793</v>
       </c>
       <c r="C265" t="s">
-        <v>530</v>
+        <v>794</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>531</v>
+        <v>795</v>
       </c>
       <c r="B266" t="s">
-        <v>532</v>
+        <v>796</v>
       </c>
       <c r="C266" t="s">
-        <v>532</v>
+        <v>797</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>533</v>
+        <v>798</v>
       </c>
       <c r="B267" t="s">
-        <v>534</v>
+        <v>799</v>
       </c>
       <c r="C267" t="s">
-        <v>534</v>
+        <v>800</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>535</v>
+        <v>801</v>
       </c>
       <c r="B268" t="s">
-        <v>536</v>
+        <v>802</v>
       </c>
       <c r="C268" t="s">
-        <v>536</v>
+        <v>803</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>537</v>
+        <v>804</v>
       </c>
       <c r="B269" t="s">
-        <v>538</v>
+        <v>805</v>
       </c>
       <c r="C269" t="s">
-        <v>538</v>
+        <v>806</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>539</v>
+        <v>807</v>
       </c>
       <c r="B270" t="s">
-        <v>540</v>
+        <v>808</v>
       </c>
       <c r="C270" t="s">
-        <v>540</v>
+        <v>809</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>541</v>
+        <v>810</v>
       </c>
       <c r="B271" t="s">
-        <v>542</v>
+        <v>811</v>
       </c>
       <c r="C271" t="s">
-        <v>542</v>
+        <v>812</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>543</v>
+        <v>813</v>
       </c>
       <c r="B272" t="s">
-        <v>544</v>
+        <v>814</v>
       </c>
       <c r="C272" t="s">
-        <v>544</v>
+        <v>815</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>545</v>
+        <v>816</v>
       </c>
       <c r="B273" t="s">
-        <v>546</v>
+        <v>817</v>
       </c>
       <c r="C273" t="s">
-        <v>546</v>
+        <v>818</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>547</v>
+        <v>819</v>
       </c>
       <c r="B274" t="s">
-        <v>548</v>
+        <v>820</v>
       </c>
       <c r="C274" t="s">
-        <v>548</v>
+        <v>821</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>549</v>
+        <v>822</v>
       </c>
       <c r="B275" t="s">
-        <v>550</v>
+        <v>823</v>
       </c>
       <c r="C275" t="s">
-        <v>550</v>
+        <v>824</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>551</v>
+        <v>825</v>
       </c>
       <c r="B276" t="s">
-        <v>552</v>
+        <v>826</v>
       </c>
       <c r="C276" t="s">
-        <v>552</v>
+        <v>827</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>553</v>
+        <v>828</v>
       </c>
       <c r="B277" t="s">
-        <v>554</v>
+        <v>829</v>
       </c>
       <c r="C277" t="s">
-        <v>554</v>
+        <v>830</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>555</v>
+        <v>831</v>
       </c>
       <c r="B278" t="s">
-        <v>556</v>
+        <v>832</v>
       </c>
       <c r="C278" t="s">
-        <v>556</v>
+        <v>833</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>557</v>
+        <v>834</v>
       </c>
       <c r="B279" t="s">
-        <v>558</v>
+        <v>835</v>
       </c>
       <c r="C279" t="s">
-        <v>558</v>
+        <v>836</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>559</v>
+        <v>837</v>
       </c>
       <c r="B280" t="s">
-        <v>560</v>
+        <v>838</v>
       </c>
       <c r="C280" t="s">
-        <v>560</v>
+        <v>839</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>561</v>
+        <v>840</v>
       </c>
       <c r="B281" t="s">
-        <v>562</v>
+        <v>841</v>
       </c>
       <c r="C281" t="s">
-        <v>562</v>
+        <v>842</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>563</v>
+        <v>843</v>
       </c>
       <c r="B282" t="s">
-        <v>564</v>
+        <v>844</v>
       </c>
       <c r="C282" t="s">
-        <v>564</v>
+        <v>845</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>565</v>
+        <v>846</v>
       </c>
       <c r="B283" t="s">
-        <v>566</v>
+        <v>847</v>
       </c>
       <c r="C283" t="s">
-        <v>566</v>
+        <v>848</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>567</v>
+        <v>849</v>
       </c>
       <c r="B284" t="s">
-        <v>568</v>
+        <v>850</v>
       </c>
       <c r="C284" t="s">
-        <v>568</v>
+        <v>851</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>569</v>
+        <v>852</v>
       </c>
       <c r="B285" t="s">
-        <v>570</v>
+        <v>853</v>
       </c>
       <c r="C285" t="s">
-        <v>570</v>
+        <v>854</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>571</v>
+        <v>855</v>
       </c>
       <c r="B286" t="s">
-        <v>572</v>
+        <v>856</v>
       </c>
       <c r="C286" t="s">
-        <v>572</v>
+        <v>857</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>573</v>
+        <v>858</v>
       </c>
       <c r="B287" t="s">
-        <v>574</v>
+        <v>859</v>
       </c>
       <c r="C287" t="s">
-        <v>574</v>
+        <v>860</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>575</v>
+        <v>861</v>
       </c>
       <c r="B288" t="s">
-        <v>576</v>
+        <v>862</v>
       </c>
       <c r="C288" t="s">
-        <v>576</v>
+        <v>863</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>577</v>
+        <v>864</v>
       </c>
       <c r="B289" t="s">
-        <v>578</v>
+        <v>865</v>
       </c>
       <c r="C289" t="s">
-        <v>578</v>
+        <v>866</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>579</v>
+        <v>867</v>
       </c>
       <c r="B290" t="s">
-        <v>580</v>
+        <v>868</v>
       </c>
       <c r="C290" t="s">
-        <v>580</v>
+        <v>869</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>581</v>
+        <v>870</v>
       </c>
       <c r="B291" t="s">
-        <v>582</v>
+        <v>871</v>
       </c>
       <c r="C291" t="s">
-        <v>582</v>
+        <v>872</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>583</v>
+        <v>873</v>
       </c>
       <c r="B292" t="s">
-        <v>584</v>
+        <v>874</v>
       </c>
       <c r="C292" t="s">
-        <v>584</v>
+        <v>875</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>585</v>
+        <v>876</v>
       </c>
       <c r="B293" t="s">
-        <v>586</v>
+        <v>877</v>
       </c>
       <c r="C293" t="s">
-        <v>586</v>
+        <v>878</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>587</v>
+        <v>879</v>
       </c>
       <c r="B294" t="s">
-        <v>588</v>
+        <v>880</v>
       </c>
       <c r="C294" t="s">
-        <v>588</v>
+        <v>881</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>589</v>
+        <v>882</v>
       </c>
       <c r="B295" t="s">
-        <v>590</v>
+        <v>883</v>
       </c>
       <c r="C295" t="s">
-        <v>590</v>
+        <v>884</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>591</v>
+        <v>885</v>
       </c>
       <c r="B296" t="s">
-        <v>592</v>
+        <v>886</v>
       </c>
       <c r="C296" t="s">
-        <v>592</v>
+        <v>887</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>593</v>
+        <v>888</v>
       </c>
       <c r="B297" t="s">
-        <v>592</v>
+        <v>886</v>
       </c>
       <c r="C297" t="s">
-        <v>592</v>
+        <v>887</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>594</v>
+        <v>889</v>
       </c>
       <c r="B298" t="s">
-        <v>592</v>
+        <v>886</v>
       </c>
       <c r="C298" t="s">
-        <v>592</v>
+        <v>887</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>595</v>
+        <v>890</v>
       </c>
       <c r="B299" t="s">
-        <v>592</v>
+        <v>886</v>
       </c>
       <c r="C299" t="s">
-        <v>592</v>
+        <v>887</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>596</v>
+        <v>891</v>
       </c>
       <c r="B300" t="s">
-        <v>597</v>
+        <v>892</v>
       </c>
       <c r="C300" t="s">
-        <v>597</v>
+        <v>893</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>598</v>
+        <v>894</v>
       </c>
       <c r="B301" t="s">
-        <v>599</v>
+        <v>895</v>
       </c>
       <c r="C301" t="s">
-        <v>599</v>
+        <v>896</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>600</v>
+        <v>897</v>
       </c>
       <c r="B302" t="s">
-        <v>601</v>
+        <v>898</v>
       </c>
       <c r="C302" t="s">
-        <v>601</v>
+        <v>899</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>602</v>
+        <v>900</v>
       </c>
       <c r="B303" t="s">
-        <v>603</v>
+        <v>901</v>
       </c>
       <c r="C303" t="s">
-        <v>603</v>
+        <v>902</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>604</v>
+        <v>903</v>
       </c>
       <c r="B304" t="s">
-        <v>605</v>
+        <v>904</v>
       </c>
       <c r="C304" t="s">
-        <v>605</v>
+        <v>905</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>606</v>
+        <v>906</v>
       </c>
       <c r="B305" t="s">
-        <v>607</v>
+        <v>907</v>
       </c>
       <c r="C305" t="s">
-        <v>607</v>
+        <v>908</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>608</v>
+        <v>909</v>
       </c>
       <c r="B306" t="s">
-        <v>609</v>
+        <v>910</v>
       </c>
       <c r="C306" t="s">
-        <v>609</v>
+        <v>911</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>610</v>
+        <v>912</v>
       </c>
       <c r="B307" t="s">
-        <v>611</v>
+        <v>913</v>
       </c>
       <c r="C307" t="s">
-        <v>611</v>
+        <v>914</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>612</v>
+        <v>915</v>
       </c>
       <c r="B308" t="s">
-        <v>613</v>
+        <v>916</v>
       </c>
       <c r="C308" t="s">
-        <v>613</v>
+        <v>917</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>614</v>
+        <v>918</v>
       </c>
       <c r="B309" t="s">
-        <v>615</v>
+        <v>919</v>
       </c>
       <c r="C309" t="s">
-        <v>615</v>
+        <v>920</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>616</v>
+        <v>921</v>
       </c>
       <c r="B310" t="s">
-        <v>617</v>
+        <v>922</v>
       </c>
       <c r="C310" t="s">
-        <v>617</v>
+        <v>923</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>618</v>
+        <v>924</v>
       </c>
       <c r="B311" t="s">
-        <v>619</v>
+        <v>925</v>
       </c>
       <c r="C311" t="s">
-        <v>619</v>
+        <v>926</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>620</v>
+        <v>927</v>
       </c>
       <c r="B312" t="s">
-        <v>621</v>
+        <v>928</v>
       </c>
       <c r="C312" t="s">
-        <v>621</v>
+        <v>929</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>622</v>
+        <v>930</v>
       </c>
       <c r="B313" t="s">
-        <v>623</v>
+        <v>931</v>
       </c>
       <c r="C313" t="s">
-        <v>623</v>
+        <v>932</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>624</v>
+        <v>933</v>
       </c>
       <c r="B314" t="s">
-        <v>625</v>
+        <v>934</v>
       </c>
       <c r="C314" t="s">
-        <v>625</v>
+        <v>935</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>626</v>
+        <v>936</v>
       </c>
       <c r="B315" t="s">
-        <v>627</v>
+        <v>937</v>
       </c>
       <c r="C315" t="s">
-        <v>627</v>
+        <v>938</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>628</v>
+        <v>939</v>
       </c>
       <c r="B316" t="s">
-        <v>627</v>
+        <v>937</v>
       </c>
       <c r="C316" t="s">
-        <v>627</v>
+        <v>938</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>629</v>
+        <v>940</v>
       </c>
       <c r="B317" t="s">
-        <v>630</v>
+        <v>941</v>
       </c>
       <c r="C317" t="s">
-        <v>630</v>
+        <v>942</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>631</v>
+        <v>943</v>
       </c>
       <c r="B318" t="s">
-        <v>632</v>
+        <v>944</v>
       </c>
       <c r="C318" t="s">
-        <v>632</v>
+        <v>945</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>633</v>
+        <v>946</v>
       </c>
       <c r="B319" t="s">
-        <v>634</v>
+        <v>947</v>
       </c>
       <c r="C319" t="s">
-        <v>634</v>
+        <v>948</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>635</v>
+        <v>949</v>
       </c>
       <c r="B320" t="s">
-        <v>636</v>
+        <v>950</v>
       </c>
       <c r="C320" t="s">
-        <v>636</v>
+        <v>951</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>637</v>
+        <v>952</v>
       </c>
       <c r="B321" t="s">
-        <v>638</v>
+        <v>953</v>
       </c>
       <c r="C321" t="s">
-        <v>638</v>
+        <v>954</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>639</v>
+        <v>955</v>
       </c>
       <c r="B322" t="s">
-        <v>640</v>
+        <v>956</v>
       </c>
       <c r="C322" t="s">
-        <v>640</v>
+        <v>957</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>641</v>
+        <v>958</v>
       </c>
       <c r="B323" t="s">
-        <v>642</v>
+        <v>959</v>
       </c>
       <c r="C323" t="s">
-        <v>642</v>
+        <v>960</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>643</v>
+        <v>961</v>
       </c>
       <c r="B324" t="s">
-        <v>644</v>
+        <v>962</v>
       </c>
       <c r="C324" t="s">
-        <v>644</v>
+        <v>963</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>645</v>
+        <v>964</v>
       </c>
       <c r="B325" t="s">
-        <v>646</v>
+        <v>965</v>
       </c>
       <c r="C325" t="s">
-        <v>646</v>
+        <v>966</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>647</v>
+        <v>967</v>
       </c>
       <c r="B326" t="s">
-        <v>648</v>
+        <v>968</v>
       </c>
       <c r="C326" t="s">
-        <v>648</v>
+        <v>969</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>649</v>
+        <v>970</v>
       </c>
       <c r="B327" t="s">
-        <v>650</v>
+        <v>971</v>
       </c>
       <c r="C327" t="s">
-        <v>650</v>
+        <v>972</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>651</v>
+        <v>973</v>
       </c>
       <c r="B328" t="s">
-        <v>652</v>
+        <v>974</v>
       </c>
       <c r="C328" t="s">
-        <v>652</v>
+        <v>975</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>653</v>
+        <v>976</v>
       </c>
       <c r="B329" t="s">
-        <v>654</v>
+        <v>977</v>
       </c>
       <c r="C329" t="s">
-        <v>654</v>
+        <v>978</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>655</v>
+        <v>979</v>
       </c>
       <c r="B330" t="s">
-        <v>656</v>
+        <v>980</v>
       </c>
       <c r="C330" t="s">
-        <v>656</v>
+        <v>981</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>657</v>
+        <v>982</v>
       </c>
       <c r="B331" t="s">
-        <v>658</v>
+        <v>983</v>
       </c>
       <c r="C331" t="s">
-        <v>658</v>
+        <v>984</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>659</v>
+        <v>985</v>
       </c>
       <c r="B332" t="s">
-        <v>660</v>
+        <v>986</v>
       </c>
       <c r="C332" t="s">
-        <v>660</v>
+        <v>987</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>661</v>
+        <v>988</v>
       </c>
       <c r="B333" t="s">
-        <v>662</v>
+        <v>989</v>
       </c>
       <c r="C333" t="s">
-        <v>662</v>
+        <v>990</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>663</v>
+        <v>991</v>
       </c>
       <c r="B334" t="s">
-        <v>664</v>
+        <v>992</v>
       </c>
       <c r="C334" t="s">
-        <v>664</v>
+        <v>993</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>665</v>
+        <v>994</v>
       </c>
       <c r="B335" t="s">
-        <v>666</v>
+        <v>995</v>
       </c>
       <c r="C335" t="s">
-        <v>666</v>
+        <v>996</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>667</v>
+        <v>997</v>
       </c>
       <c r="B336" t="s">
-        <v>668</v>
+        <v>998</v>
       </c>
       <c r="C336" t="s">
-        <v>668</v>
+        <v>999</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>669</v>
+        <v>1000</v>
       </c>
       <c r="B337" t="s">
-        <v>670</v>
+        <v>1001</v>
       </c>
       <c r="C337" t="s">
-        <v>670</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>671</v>
+        <v>1003</v>
       </c>
       <c r="B338" t="s">
-        <v>672</v>
+        <v>1004</v>
       </c>
       <c r="C338" t="s">
-        <v>672</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>673</v>
+        <v>1006</v>
       </c>
       <c r="B339" t="s">
-        <v>674</v>
+        <v>1007</v>
       </c>
       <c r="C339" t="s">
-        <v>674</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>675</v>
+        <v>1009</v>
       </c>
       <c r="B340" t="s">
-        <v>676</v>
+        <v>1010</v>
       </c>
       <c r="C340" t="s">
-        <v>676</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>677</v>
+        <v>1012</v>
       </c>
       <c r="B341" t="s">
-        <v>678</v>
+        <v>1013</v>
       </c>
       <c r="C341" t="s">
-        <v>678</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>679</v>
+        <v>1015</v>
       </c>
       <c r="B342" t="s">
-        <v>680</v>
+        <v>1016</v>
       </c>
       <c r="C342" t="s">
-        <v>680</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>681</v>
+        <v>1018</v>
       </c>
       <c r="B343" t="s">
-        <v>682</v>
+        <v>1019</v>
       </c>
       <c r="C343" t="s">
-        <v>682</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>683</v>
+        <v>1021</v>
       </c>
       <c r="B344" t="s">
-        <v>684</v>
+        <v>1022</v>
       </c>
       <c r="C344" t="s">
-        <v>684</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>685</v>
+        <v>1024</v>
       </c>
       <c r="B345">
         <v>0</v>
       </c>
-      <c r="C345">
-        <v>0</v>
+      <c r="C345" t="s">
+        <v>1025</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>686</v>
+        <v>1026</v>
       </c>
       <c r="B346" t="s">
-        <v>687</v>
+        <v>1027</v>
       </c>
       <c r="C346" t="s">
-        <v>687</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>688</v>
+        <v>1029</v>
       </c>
       <c r="B347" t="s">
-        <v>689</v>
+        <v>1030</v>
       </c>
       <c r="C347" t="s">
-        <v>689</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>690</v>
+        <v>1032</v>
       </c>
       <c r="B348" t="s">
-        <v>691</v>
+        <v>1033</v>
       </c>
       <c r="C348" t="s">
-        <v>691</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>692</v>
+        <v>1035</v>
       </c>
       <c r="B349" t="s">
-        <v>693</v>
+        <v>1036</v>
       </c>
       <c r="C349" t="s">
-        <v>693</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>694</v>
+        <v>1038</v>
       </c>
       <c r="B350" t="s">
-        <v>695</v>
+        <v>1039</v>
       </c>
       <c r="C350" t="s">
-        <v>695</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>696</v>
+        <v>1041</v>
       </c>
       <c r="B351" t="s">
-        <v>697</v>
+        <v>1042</v>
       </c>
       <c r="C351" t="s">
-        <v>697</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>698</v>
+        <v>1044</v>
       </c>
       <c r="B352" t="s">
-        <v>699</v>
+        <v>1045</v>
       </c>
       <c r="C352" t="s">
-        <v>699</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>700</v>
+        <v>1047</v>
       </c>
       <c r="B353" t="s">
-        <v>701</v>
+        <v>1048</v>
       </c>
       <c r="C353" t="s">
-        <v>701</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>702</v>
+        <v>1050</v>
       </c>
       <c r="B354" t="s">
-        <v>703</v>
+        <v>1051</v>
       </c>
       <c r="C354" t="s">
-        <v>703</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>704</v>
+        <v>1053</v>
       </c>
       <c r="B355" t="s">
-        <v>705</v>
+        <v>1054</v>
       </c>
       <c r="C355" t="s">
-        <v>705</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>706</v>
+        <v>1055</v>
       </c>
       <c r="B356" t="s">
-        <v>707</v>
+        <v>1056</v>
       </c>
       <c r="C356" t="s">
-        <v>707</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>708</v>
+        <v>1057</v>
       </c>
       <c r="B357" t="s">
-        <v>709</v>
+        <v>1058</v>
       </c>
       <c r="C357" t="s">
-        <v>709</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>710</v>
+        <v>1059</v>
       </c>
       <c r="B358" t="s">
-        <v>711</v>
+        <v>1060</v>
       </c>
       <c r="C358" t="s">
-        <v>711</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>712</v>
+        <v>1061</v>
       </c>
       <c r="B359" t="s">
-        <v>713</v>
+        <v>1062</v>
       </c>
       <c r="C359" t="s">
-        <v>713</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>714</v>
+        <v>1063</v>
       </c>
       <c r="B360" t="s">
-        <v>715</v>
+        <v>1064</v>
       </c>
       <c r="C360" t="s">
-        <v>715</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>716</v>
+        <v>1065</v>
       </c>
       <c r="B361" t="s">
-        <v>717</v>
+        <v>1066</v>
       </c>
       <c r="C361" t="s">
-        <v>717</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>718</v>
+        <v>1067</v>
       </c>
       <c r="B362" t="s">
-        <v>719</v>
+        <v>1068</v>
       </c>
       <c r="C362" t="s">
-        <v>719</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>720</v>
+        <v>1069</v>
       </c>
       <c r="B363" t="s">
-        <v>721</v>
+        <v>1070</v>
       </c>
       <c r="C363" t="s">
-        <v>721</v>
+        <v>1052</v>
       </c>
     </row>
   </sheetData>

--- a/Plan/Table/TestData/00.LocaleData.xlsx
+++ b/Plan/Table/TestData/00.LocaleData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HOME\Documents\프로젝트 Git\Plan\Table\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\인디\FluffyDisdog\Plan\Table\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6246342F-B1D6-4474-BEE9-1E1542233D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7490191C-CDD7-4CA3-B34E-6B3A4DF6246E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5A13723D-2757-45BA-81CA-7CBE4435BD60}"/>
+    <workbookView xWindow="13230" yWindow="4980" windowWidth="14505" windowHeight="13485" xr2:uid="{DAD7A119-9706-4215-B2C0-59D23418D445}"/>
   </bookViews>
   <sheets>
     <sheet name="00.LocaleData" sheetId="1" r:id="rId1"/>
@@ -27,14 +27,19 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="1071">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="1066">
   <si>
     <t>key</t>
   </si>
@@ -120,19 +125,13 @@
     <t>Card_Cross Chisel_Name</t>
   </si>
   <si>
-    <t>십자 끌</t>
-  </si>
-  <si>
-    <t>Cross Chisel</t>
+    <t>나무 망치</t>
   </si>
   <si>
     <t>Card_Cross Chisel_Enhanced_Name</t>
   </si>
   <si>
-    <t>십자 끌+</t>
-  </si>
-  <si>
-    <t>Cross Chisel+</t>
+    <t>나무 망치+</t>
   </si>
   <si>
     <t>Card_Pickaxe_Name</t>
@@ -1794,10 +1793,7 @@
     <t>relic111_Name</t>
   </si>
   <si>
-    <t>덕트 테이프</t>
-  </si>
-  <si>
-    <t>Duct Tape</t>
+    <t>긴급 수리 테이프</t>
   </si>
   <si>
     <t>relic112_Name</t>
@@ -1839,7 +1835,7 @@
     <t>relic116_Name</t>
   </si>
   <si>
-    <t>균열 생성기*</t>
+    <t>대못</t>
   </si>
   <si>
     <t>Rift Generator</t>
@@ -1893,19 +1889,13 @@
     <t>relic122_Name</t>
   </si>
   <si>
-    <t>가로 방향 안정 장치</t>
-  </si>
-  <si>
-    <t>Horizontal Stabilizer</t>
+    <t>수평계</t>
   </si>
   <si>
     <t>relic123_Name</t>
   </si>
   <si>
-    <t>세로 방향 안정 장치</t>
-  </si>
-  <si>
-    <t>Vertical Stabilizer</t>
+    <t>세로추</t>
   </si>
   <si>
     <t>relic201_Name</t>
@@ -3324,39 +3314,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -3408,7 +3398,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -3519,13 +3509,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -3534,6 +3517,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -3598,18 +3588,38 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{145269B2-AE5F-425A-BBAD-F17DF001F17D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C96EE684-554F-4E0F-82E4-9992425F531C}">
   <dimension ref="A1:C363"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -3720,3890 +3730,3890 @@
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s">
         <v>30</v>
       </c>
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" t="s">
         <v>33</v>
-      </c>
-      <c r="B12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
         <v>36</v>
-      </c>
-      <c r="B13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" t="s">
         <v>39</v>
-      </c>
-      <c r="B14" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" t="s">
         <v>42</v>
-      </c>
-      <c r="B15" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" t="s">
         <v>45</v>
-      </c>
-      <c r="B16" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" t="s">
         <v>48</v>
-      </c>
-      <c r="B17" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" t="s">
         <v>51</v>
-      </c>
-      <c r="B18" t="s">
-        <v>52</v>
-      </c>
-      <c r="C18" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" t="s">
         <v>54</v>
-      </c>
-      <c r="B19" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" t="s">
         <v>57</v>
-      </c>
-      <c r="B20" t="s">
-        <v>58</v>
-      </c>
-      <c r="C20" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" t="s">
         <v>60</v>
-      </c>
-      <c r="B21" t="s">
-        <v>61</v>
-      </c>
-      <c r="C21" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" t="s">
         <v>63</v>
-      </c>
-      <c r="B22" t="s">
-        <v>64</v>
-      </c>
-      <c r="C22" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>64</v>
+      </c>
+      <c r="B23" t="s">
+        <v>65</v>
+      </c>
+      <c r="C23" t="s">
         <v>66</v>
-      </c>
-      <c r="B23" t="s">
-        <v>67</v>
-      </c>
-      <c r="C23" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>67</v>
+      </c>
+      <c r="B24" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" t="s">
         <v>69</v>
-      </c>
-      <c r="B24" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>70</v>
+      </c>
+      <c r="B25" t="s">
+        <v>71</v>
+      </c>
+      <c r="C25" t="s">
         <v>72</v>
-      </c>
-      <c r="B25" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" t="s">
+        <v>74</v>
+      </c>
+      <c r="C26" t="s">
         <v>75</v>
-      </c>
-      <c r="B26" t="s">
-        <v>76</v>
-      </c>
-      <c r="C26" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>76</v>
+      </c>
+      <c r="B27" t="s">
+        <v>77</v>
+      </c>
+      <c r="C27" t="s">
         <v>78</v>
-      </c>
-      <c r="B27" t="s">
-        <v>79</v>
-      </c>
-      <c r="C27" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>79</v>
+      </c>
+      <c r="B28" t="s">
+        <v>80</v>
+      </c>
+      <c r="C28" t="s">
         <v>81</v>
-      </c>
-      <c r="B28" t="s">
-        <v>82</v>
-      </c>
-      <c r="C28" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>82</v>
+      </c>
+      <c r="B29" t="s">
+        <v>83</v>
+      </c>
+      <c r="C29" t="s">
         <v>84</v>
-      </c>
-      <c r="B29" t="s">
-        <v>85</v>
-      </c>
-      <c r="C29" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>85</v>
+      </c>
+      <c r="B30" t="s">
+        <v>86</v>
+      </c>
+      <c r="C30" t="s">
         <v>87</v>
-      </c>
-      <c r="B30" t="s">
-        <v>88</v>
-      </c>
-      <c r="C30" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>88</v>
+      </c>
+      <c r="B31" t="s">
+        <v>89</v>
+      </c>
+      <c r="C31" t="s">
         <v>90</v>
-      </c>
-      <c r="B31" t="s">
-        <v>91</v>
-      </c>
-      <c r="C31" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>91</v>
+      </c>
+      <c r="B32" t="s">
+        <v>92</v>
+      </c>
+      <c r="C32" t="s">
         <v>93</v>
-      </c>
-      <c r="B32" t="s">
-        <v>94</v>
-      </c>
-      <c r="C32" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>94</v>
+      </c>
+      <c r="B33" t="s">
+        <v>95</v>
+      </c>
+      <c r="C33" t="s">
         <v>96</v>
-      </c>
-      <c r="B33" t="s">
-        <v>97</v>
-      </c>
-      <c r="C33" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>97</v>
+      </c>
+      <c r="B34" t="s">
+        <v>98</v>
+      </c>
+      <c r="C34" t="s">
         <v>99</v>
-      </c>
-      <c r="B34" t="s">
-        <v>100</v>
-      </c>
-      <c r="C34" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>100</v>
+      </c>
+      <c r="B35" t="s">
+        <v>101</v>
+      </c>
+      <c r="C35" t="s">
         <v>102</v>
-      </c>
-      <c r="B35" t="s">
-        <v>103</v>
-      </c>
-      <c r="C35" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>103</v>
+      </c>
+      <c r="B36" t="s">
+        <v>104</v>
+      </c>
+      <c r="C36" t="s">
         <v>105</v>
-      </c>
-      <c r="B36" t="s">
-        <v>106</v>
-      </c>
-      <c r="C36" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>106</v>
+      </c>
+      <c r="B37" t="s">
+        <v>107</v>
+      </c>
+      <c r="C37" t="s">
         <v>108</v>
-      </c>
-      <c r="B37" t="s">
-        <v>109</v>
-      </c>
-      <c r="C37" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>109</v>
+      </c>
+      <c r="B38" t="s">
+        <v>110</v>
+      </c>
+      <c r="C38" t="s">
         <v>111</v>
-      </c>
-      <c r="B38" t="s">
-        <v>112</v>
-      </c>
-      <c r="C38" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>112</v>
+      </c>
+      <c r="B39" t="s">
+        <v>113</v>
+      </c>
+      <c r="C39" t="s">
         <v>114</v>
-      </c>
-      <c r="B39" t="s">
-        <v>115</v>
-      </c>
-      <c r="C39" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>115</v>
+      </c>
+      <c r="B40" t="s">
+        <v>116</v>
+      </c>
+      <c r="C40" t="s">
         <v>117</v>
-      </c>
-      <c r="B40" t="s">
-        <v>118</v>
-      </c>
-      <c r="C40" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>118</v>
+      </c>
+      <c r="B41" t="s">
+        <v>119</v>
+      </c>
+      <c r="C41" t="s">
         <v>120</v>
-      </c>
-      <c r="B41" t="s">
-        <v>121</v>
-      </c>
-      <c r="C41" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>121</v>
+      </c>
+      <c r="B42" t="s">
+        <v>122</v>
+      </c>
+      <c r="C42" t="s">
         <v>123</v>
-      </c>
-      <c r="B42" t="s">
-        <v>124</v>
-      </c>
-      <c r="C42" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>124</v>
+      </c>
+      <c r="B43" t="s">
+        <v>125</v>
+      </c>
+      <c r="C43" t="s">
         <v>126</v>
-      </c>
-      <c r="B43" t="s">
-        <v>127</v>
-      </c>
-      <c r="C43" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>127</v>
+      </c>
+      <c r="B44" t="s">
+        <v>128</v>
+      </c>
+      <c r="C44" t="s">
         <v>129</v>
-      </c>
-      <c r="B44" t="s">
-        <v>130</v>
-      </c>
-      <c r="C44" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>130</v>
+      </c>
+      <c r="B45" t="s">
+        <v>131</v>
+      </c>
+      <c r="C45" t="s">
         <v>132</v>
-      </c>
-      <c r="B45" t="s">
-        <v>133</v>
-      </c>
-      <c r="C45" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
+        <v>133</v>
+      </c>
+      <c r="B46" t="s">
+        <v>134</v>
+      </c>
+      <c r="C46" t="s">
         <v>135</v>
-      </c>
-      <c r="B46" t="s">
-        <v>136</v>
-      </c>
-      <c r="C46" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
+        <v>136</v>
+      </c>
+      <c r="B47" t="s">
+        <v>137</v>
+      </c>
+      <c r="C47" t="s">
         <v>138</v>
-      </c>
-      <c r="B47" t="s">
-        <v>139</v>
-      </c>
-      <c r="C47" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>139</v>
+      </c>
+      <c r="B48" t="s">
+        <v>140</v>
+      </c>
+      <c r="C48" t="s">
         <v>141</v>
-      </c>
-      <c r="B48" t="s">
-        <v>142</v>
-      </c>
-      <c r="C48" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>142</v>
+      </c>
+      <c r="B49" t="s">
+        <v>143</v>
+      </c>
+      <c r="C49" t="s">
         <v>144</v>
-      </c>
-      <c r="B49" t="s">
-        <v>145</v>
-      </c>
-      <c r="C49" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>145</v>
+      </c>
+      <c r="B50" t="s">
+        <v>146</v>
+      </c>
+      <c r="C50" t="s">
         <v>147</v>
-      </c>
-      <c r="B50" t="s">
-        <v>148</v>
-      </c>
-      <c r="C50" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>148</v>
+      </c>
+      <c r="B51" t="s">
+        <v>149</v>
+      </c>
+      <c r="C51" t="s">
         <v>150</v>
-      </c>
-      <c r="B51" t="s">
-        <v>151</v>
-      </c>
-      <c r="C51" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>151</v>
+      </c>
+      <c r="B52" t="s">
+        <v>152</v>
+      </c>
+      <c r="C52" t="s">
         <v>153</v>
-      </c>
-      <c r="B52" t="s">
-        <v>154</v>
-      </c>
-      <c r="C52" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
+        <v>154</v>
+      </c>
+      <c r="B53" t="s">
+        <v>155</v>
+      </c>
+      <c r="C53" t="s">
         <v>156</v>
-      </c>
-      <c r="B53" t="s">
-        <v>157</v>
-      </c>
-      <c r="C53" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>157</v>
+      </c>
+      <c r="B54" t="s">
+        <v>158</v>
+      </c>
+      <c r="C54" t="s">
         <v>159</v>
-      </c>
-      <c r="B54" t="s">
-        <v>160</v>
-      </c>
-      <c r="C54" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>160</v>
+      </c>
+      <c r="B55" t="s">
+        <v>161</v>
+      </c>
+      <c r="C55" t="s">
         <v>162</v>
-      </c>
-      <c r="B55" t="s">
-        <v>163</v>
-      </c>
-      <c r="C55" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
+        <v>163</v>
+      </c>
+      <c r="B56" t="s">
+        <v>164</v>
+      </c>
+      <c r="C56" t="s">
         <v>165</v>
-      </c>
-      <c r="B56" t="s">
-        <v>166</v>
-      </c>
-      <c r="C56" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
+        <v>166</v>
+      </c>
+      <c r="B57" t="s">
+        <v>167</v>
+      </c>
+      <c r="C57" t="s">
         <v>168</v>
-      </c>
-      <c r="B57" t="s">
-        <v>169</v>
-      </c>
-      <c r="C57" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
+        <v>169</v>
+      </c>
+      <c r="B58" t="s">
+        <v>170</v>
+      </c>
+      <c r="C58" t="s">
         <v>171</v>
-      </c>
-      <c r="B58" t="s">
-        <v>172</v>
-      </c>
-      <c r="C58" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
+        <v>172</v>
+      </c>
+      <c r="B59" t="s">
+        <v>173</v>
+      </c>
+      <c r="C59" t="s">
         <v>174</v>
-      </c>
-      <c r="B59" t="s">
-        <v>175</v>
-      </c>
-      <c r="C59" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
+        <v>175</v>
+      </c>
+      <c r="B60" t="s">
+        <v>176</v>
+      </c>
+      <c r="C60" t="s">
         <v>177</v>
-      </c>
-      <c r="B60" t="s">
-        <v>178</v>
-      </c>
-      <c r="C60" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
+        <v>178</v>
+      </c>
+      <c r="B61" t="s">
+        <v>179</v>
+      </c>
+      <c r="C61" t="s">
         <v>180</v>
-      </c>
-      <c r="B61" t="s">
-        <v>181</v>
-      </c>
-      <c r="C61" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
+        <v>181</v>
+      </c>
+      <c r="B62" t="s">
+        <v>182</v>
+      </c>
+      <c r="C62" t="s">
         <v>183</v>
-      </c>
-      <c r="B62" t="s">
-        <v>184</v>
-      </c>
-      <c r="C62" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
+        <v>184</v>
+      </c>
+      <c r="B63" t="s">
+        <v>185</v>
+      </c>
+      <c r="C63" t="s">
         <v>186</v>
-      </c>
-      <c r="B63" t="s">
-        <v>187</v>
-      </c>
-      <c r="C63" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
+        <v>187</v>
+      </c>
+      <c r="B64" t="s">
+        <v>188</v>
+      </c>
+      <c r="C64" t="s">
         <v>189</v>
-      </c>
-      <c r="B64" t="s">
-        <v>190</v>
-      </c>
-      <c r="C64" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
+        <v>190</v>
+      </c>
+      <c r="B65" t="s">
+        <v>191</v>
+      </c>
+      <c r="C65" t="s">
         <v>192</v>
-      </c>
-      <c r="B65" t="s">
-        <v>193</v>
-      </c>
-      <c r="C65" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
+        <v>193</v>
+      </c>
+      <c r="B66" t="s">
+        <v>194</v>
+      </c>
+      <c r="C66" t="s">
         <v>195</v>
-      </c>
-      <c r="B66" t="s">
-        <v>196</v>
-      </c>
-      <c r="C66" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
+        <v>196</v>
+      </c>
+      <c r="B67" t="s">
+        <v>197</v>
+      </c>
+      <c r="C67" t="s">
         <v>198</v>
-      </c>
-      <c r="B67" t="s">
-        <v>199</v>
-      </c>
-      <c r="C67" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
+        <v>199</v>
+      </c>
+      <c r="B68" t="s">
+        <v>200</v>
+      </c>
+      <c r="C68" t="s">
         <v>201</v>
-      </c>
-      <c r="B68" t="s">
-        <v>202</v>
-      </c>
-      <c r="C68" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
+        <v>202</v>
+      </c>
+      <c r="B69" t="s">
+        <v>203</v>
+      </c>
+      <c r="C69" t="s">
         <v>204</v>
-      </c>
-      <c r="B69" t="s">
-        <v>205</v>
-      </c>
-      <c r="C69" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>205</v>
+      </c>
+      <c r="B70" t="s">
+        <v>206</v>
+      </c>
+      <c r="C70" t="s">
         <v>207</v>
-      </c>
-      <c r="B70" t="s">
-        <v>208</v>
-      </c>
-      <c r="C70" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
+        <v>208</v>
+      </c>
+      <c r="B71" t="s">
+        <v>209</v>
+      </c>
+      <c r="C71" t="s">
         <v>210</v>
-      </c>
-      <c r="B71" t="s">
-        <v>211</v>
-      </c>
-      <c r="C71" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>211</v>
+      </c>
+      <c r="B72" t="s">
+        <v>212</v>
+      </c>
+      <c r="C72" t="s">
         <v>213</v>
-      </c>
-      <c r="B72" t="s">
-        <v>214</v>
-      </c>
-      <c r="C72" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>214</v>
+      </c>
+      <c r="B73" t="s">
+        <v>215</v>
+      </c>
+      <c r="C73" t="s">
         <v>216</v>
-      </c>
-      <c r="B73" t="s">
-        <v>217</v>
-      </c>
-      <c r="C73" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>217</v>
+      </c>
+      <c r="B74" t="s">
+        <v>218</v>
+      </c>
+      <c r="C74" t="s">
         <v>219</v>
-      </c>
-      <c r="B74" t="s">
-        <v>220</v>
-      </c>
-      <c r="C74" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>220</v>
+      </c>
+      <c r="B75" t="s">
+        <v>221</v>
+      </c>
+      <c r="C75" t="s">
         <v>222</v>
-      </c>
-      <c r="B75" t="s">
-        <v>223</v>
-      </c>
-      <c r="C75" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
+        <v>223</v>
+      </c>
+      <c r="B76" t="s">
+        <v>224</v>
+      </c>
+      <c r="C76" t="s">
         <v>225</v>
-      </c>
-      <c r="B76" t="s">
-        <v>226</v>
-      </c>
-      <c r="C76" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
+        <v>226</v>
+      </c>
+      <c r="B77" t="s">
+        <v>227</v>
+      </c>
+      <c r="C77" t="s">
         <v>228</v>
-      </c>
-      <c r="B77" t="s">
-        <v>229</v>
-      </c>
-      <c r="C77" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
+        <v>229</v>
+      </c>
+      <c r="B78" t="s">
+        <v>230</v>
+      </c>
+      <c r="C78" t="s">
         <v>231</v>
-      </c>
-      <c r="B78" t="s">
-        <v>232</v>
-      </c>
-      <c r="C78" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
+        <v>232</v>
+      </c>
+      <c r="B79" t="s">
+        <v>233</v>
+      </c>
+      <c r="C79" t="s">
         <v>234</v>
-      </c>
-      <c r="B79" t="s">
-        <v>235</v>
-      </c>
-      <c r="C79" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
+        <v>235</v>
+      </c>
+      <c r="B80" t="s">
+        <v>236</v>
+      </c>
+      <c r="C80" t="s">
         <v>237</v>
-      </c>
-      <c r="B80" t="s">
-        <v>238</v>
-      </c>
-      <c r="C80" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
+        <v>238</v>
+      </c>
+      <c r="B81" t="s">
+        <v>239</v>
+      </c>
+      <c r="C81" t="s">
         <v>240</v>
-      </c>
-      <c r="B81" t="s">
-        <v>241</v>
-      </c>
-      <c r="C81" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
+        <v>241</v>
+      </c>
+      <c r="B82" t="s">
+        <v>242</v>
+      </c>
+      <c r="C82" t="s">
         <v>243</v>
-      </c>
-      <c r="B82" t="s">
-        <v>244</v>
-      </c>
-      <c r="C82" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
+        <v>244</v>
+      </c>
+      <c r="B83" t="s">
+        <v>245</v>
+      </c>
+      <c r="C83" t="s">
         <v>246</v>
-      </c>
-      <c r="B83" t="s">
-        <v>247</v>
-      </c>
-      <c r="C83" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
+        <v>247</v>
+      </c>
+      <c r="B84" t="s">
+        <v>248</v>
+      </c>
+      <c r="C84" t="s">
         <v>249</v>
-      </c>
-      <c r="B84" t="s">
-        <v>250</v>
-      </c>
-      <c r="C84" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
+        <v>250</v>
+      </c>
+      <c r="B85" t="s">
+        <v>251</v>
+      </c>
+      <c r="C85" t="s">
         <v>252</v>
-      </c>
-      <c r="B85" t="s">
-        <v>253</v>
-      </c>
-      <c r="C85" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
+        <v>253</v>
+      </c>
+      <c r="B86" t="s">
+        <v>254</v>
+      </c>
+      <c r="C86" t="s">
         <v>255</v>
-      </c>
-      <c r="B86" t="s">
-        <v>256</v>
-      </c>
-      <c r="C86" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
+        <v>256</v>
+      </c>
+      <c r="B87" t="s">
+        <v>257</v>
+      </c>
+      <c r="C87" t="s">
         <v>258</v>
-      </c>
-      <c r="B87" t="s">
-        <v>259</v>
-      </c>
-      <c r="C87" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
+        <v>259</v>
+      </c>
+      <c r="B88" t="s">
+        <v>260</v>
+      </c>
+      <c r="C88" t="s">
         <v>261</v>
-      </c>
-      <c r="B88" t="s">
-        <v>262</v>
-      </c>
-      <c r="C88" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
+        <v>262</v>
+      </c>
+      <c r="B89" t="s">
+        <v>263</v>
+      </c>
+      <c r="C89" t="s">
         <v>264</v>
-      </c>
-      <c r="B89" t="s">
-        <v>265</v>
-      </c>
-      <c r="C89" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
+        <v>265</v>
+      </c>
+      <c r="B90" t="s">
+        <v>266</v>
+      </c>
+      <c r="C90" t="s">
         <v>267</v>
-      </c>
-      <c r="B90" t="s">
-        <v>268</v>
-      </c>
-      <c r="C90" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
+        <v>268</v>
+      </c>
+      <c r="B91" t="s">
+        <v>269</v>
+      </c>
+      <c r="C91" t="s">
         <v>270</v>
-      </c>
-      <c r="B91" t="s">
-        <v>271</v>
-      </c>
-      <c r="C91" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
+        <v>271</v>
+      </c>
+      <c r="B92" t="s">
+        <v>272</v>
+      </c>
+      <c r="C92" t="s">
         <v>273</v>
-      </c>
-      <c r="B92" t="s">
-        <v>274</v>
-      </c>
-      <c r="C92" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
+        <v>274</v>
+      </c>
+      <c r="B93" t="s">
+        <v>275</v>
+      </c>
+      <c r="C93" t="s">
         <v>276</v>
-      </c>
-      <c r="B93" t="s">
-        <v>277</v>
-      </c>
-      <c r="C93" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
+        <v>277</v>
+      </c>
+      <c r="B94" t="s">
+        <v>278</v>
+      </c>
+      <c r="C94" t="s">
         <v>279</v>
-      </c>
-      <c r="B94" t="s">
-        <v>280</v>
-      </c>
-      <c r="C94" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
+        <v>280</v>
+      </c>
+      <c r="B95" t="s">
+        <v>281</v>
+      </c>
+      <c r="C95" t="s">
         <v>282</v>
-      </c>
-      <c r="B95" t="s">
-        <v>283</v>
-      </c>
-      <c r="C95" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
+        <v>283</v>
+      </c>
+      <c r="B96" t="s">
+        <v>284</v>
+      </c>
+      <c r="C96" t="s">
         <v>285</v>
-      </c>
-      <c r="B96" t="s">
-        <v>286</v>
-      </c>
-      <c r="C96" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
+        <v>286</v>
+      </c>
+      <c r="B97" t="s">
+        <v>287</v>
+      </c>
+      <c r="C97" t="s">
         <v>288</v>
-      </c>
-      <c r="B97" t="s">
-        <v>289</v>
-      </c>
-      <c r="C97" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
+        <v>289</v>
+      </c>
+      <c r="B98" t="s">
+        <v>290</v>
+      </c>
+      <c r="C98" t="s">
         <v>291</v>
-      </c>
-      <c r="B98" t="s">
-        <v>292</v>
-      </c>
-      <c r="C98" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
+        <v>292</v>
+      </c>
+      <c r="B99" t="s">
+        <v>293</v>
+      </c>
+      <c r="C99" t="s">
         <v>294</v>
-      </c>
-      <c r="B99" t="s">
-        <v>295</v>
-      </c>
-      <c r="C99" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
+        <v>295</v>
+      </c>
+      <c r="B100" t="s">
+        <v>296</v>
+      </c>
+      <c r="C100" t="s">
         <v>297</v>
-      </c>
-      <c r="B100" t="s">
-        <v>298</v>
-      </c>
-      <c r="C100" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
+        <v>298</v>
+      </c>
+      <c r="B101" t="s">
+        <v>299</v>
+      </c>
+      <c r="C101" t="s">
         <v>300</v>
-      </c>
-      <c r="B101" t="s">
-        <v>301</v>
-      </c>
-      <c r="C101" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
+        <v>301</v>
+      </c>
+      <c r="B102" t="s">
+        <v>302</v>
+      </c>
+      <c r="C102" t="s">
         <v>303</v>
-      </c>
-      <c r="B102" t="s">
-        <v>304</v>
-      </c>
-      <c r="C102" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
+        <v>304</v>
+      </c>
+      <c r="B103" t="s">
+        <v>305</v>
+      </c>
+      <c r="C103" t="s">
         <v>306</v>
-      </c>
-      <c r="B103" t="s">
-        <v>307</v>
-      </c>
-      <c r="C103" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
+        <v>307</v>
+      </c>
+      <c r="B104" t="s">
+        <v>308</v>
+      </c>
+      <c r="C104" t="s">
         <v>309</v>
-      </c>
-      <c r="B104" t="s">
-        <v>310</v>
-      </c>
-      <c r="C104" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
+        <v>310</v>
+      </c>
+      <c r="B105" t="s">
+        <v>311</v>
+      </c>
+      <c r="C105" t="s">
         <v>312</v>
-      </c>
-      <c r="B105" t="s">
-        <v>313</v>
-      </c>
-      <c r="C105" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
+        <v>313</v>
+      </c>
+      <c r="B106" t="s">
+        <v>314</v>
+      </c>
+      <c r="C106" t="s">
         <v>315</v>
-      </c>
-      <c r="B106" t="s">
-        <v>316</v>
-      </c>
-      <c r="C106" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
+        <v>316</v>
+      </c>
+      <c r="B107" t="s">
+        <v>317</v>
+      </c>
+      <c r="C107" t="s">
         <v>318</v>
-      </c>
-      <c r="B107" t="s">
-        <v>319</v>
-      </c>
-      <c r="C107" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
+        <v>319</v>
+      </c>
+      <c r="B108" t="s">
+        <v>320</v>
+      </c>
+      <c r="C108" t="s">
         <v>321</v>
-      </c>
-      <c r="B108" t="s">
-        <v>322</v>
-      </c>
-      <c r="C108" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
+        <v>322</v>
+      </c>
+      <c r="B109" t="s">
+        <v>323</v>
+      </c>
+      <c r="C109" t="s">
         <v>324</v>
-      </c>
-      <c r="B109" t="s">
-        <v>325</v>
-      </c>
-      <c r="C109" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
+        <v>325</v>
+      </c>
+      <c r="B110" t="s">
+        <v>326</v>
+      </c>
+      <c r="C110" t="s">
         <v>327</v>
-      </c>
-      <c r="B110" t="s">
-        <v>328</v>
-      </c>
-      <c r="C110" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
+        <v>328</v>
+      </c>
+      <c r="B111" t="s">
+        <v>329</v>
+      </c>
+      <c r="C111" t="s">
         <v>330</v>
-      </c>
-      <c r="B111" t="s">
-        <v>331</v>
-      </c>
-      <c r="C111" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
+        <v>331</v>
+      </c>
+      <c r="B112" t="s">
+        <v>332</v>
+      </c>
+      <c r="C112" t="s">
         <v>333</v>
-      </c>
-      <c r="B112" t="s">
-        <v>334</v>
-      </c>
-      <c r="C112" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
+        <v>334</v>
+      </c>
+      <c r="B113" t="s">
+        <v>335</v>
+      </c>
+      <c r="C113" t="s">
         <v>336</v>
-      </c>
-      <c r="B113" t="s">
-        <v>337</v>
-      </c>
-      <c r="C113" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
+        <v>337</v>
+      </c>
+      <c r="B114" t="s">
+        <v>338</v>
+      </c>
+      <c r="C114" t="s">
         <v>339</v>
-      </c>
-      <c r="B114" t="s">
-        <v>340</v>
-      </c>
-      <c r="C114" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
+        <v>340</v>
+      </c>
+      <c r="B115" t="s">
+        <v>341</v>
+      </c>
+      <c r="C115" t="s">
         <v>342</v>
-      </c>
-      <c r="B115" t="s">
-        <v>343</v>
-      </c>
-      <c r="C115" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
+        <v>343</v>
+      </c>
+      <c r="B116" t="s">
+        <v>344</v>
+      </c>
+      <c r="C116" t="s">
         <v>345</v>
-      </c>
-      <c r="B116" t="s">
-        <v>346</v>
-      </c>
-      <c r="C116" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
+        <v>346</v>
+      </c>
+      <c r="B117" t="s">
+        <v>347</v>
+      </c>
+      <c r="C117" t="s">
         <v>348</v>
-      </c>
-      <c r="B117" t="s">
-        <v>349</v>
-      </c>
-      <c r="C117" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
+        <v>349</v>
+      </c>
+      <c r="B118" t="s">
+        <v>350</v>
+      </c>
+      <c r="C118" t="s">
         <v>351</v>
-      </c>
-      <c r="B118" t="s">
-        <v>352</v>
-      </c>
-      <c r="C118" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
+        <v>352</v>
+      </c>
+      <c r="B119" t="s">
+        <v>353</v>
+      </c>
+      <c r="C119" t="s">
         <v>354</v>
-      </c>
-      <c r="B119" t="s">
-        <v>355</v>
-      </c>
-      <c r="C119" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
+        <v>355</v>
+      </c>
+      <c r="B120" t="s">
+        <v>356</v>
+      </c>
+      <c r="C120" t="s">
         <v>357</v>
-      </c>
-      <c r="B120" t="s">
-        <v>358</v>
-      </c>
-      <c r="C120" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
+        <v>358</v>
+      </c>
+      <c r="B121" t="s">
+        <v>359</v>
+      </c>
+      <c r="C121" t="s">
         <v>360</v>
-      </c>
-      <c r="B121" t="s">
-        <v>361</v>
-      </c>
-      <c r="C121" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
+        <v>361</v>
+      </c>
+      <c r="B122" t="s">
+        <v>362</v>
+      </c>
+      <c r="C122" t="s">
         <v>363</v>
-      </c>
-      <c r="B122" t="s">
-        <v>364</v>
-      </c>
-      <c r="C122" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
+        <v>364</v>
+      </c>
+      <c r="B123" t="s">
+        <v>365</v>
+      </c>
+      <c r="C123" t="s">
         <v>366</v>
-      </c>
-      <c r="B123" t="s">
-        <v>367</v>
-      </c>
-      <c r="C123" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
+        <v>367</v>
+      </c>
+      <c r="B124" t="s">
+        <v>368</v>
+      </c>
+      <c r="C124" t="s">
         <v>369</v>
-      </c>
-      <c r="B124" t="s">
-        <v>370</v>
-      </c>
-      <c r="C124" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
+        <v>370</v>
+      </c>
+      <c r="B125" t="s">
+        <v>371</v>
+      </c>
+      <c r="C125" t="s">
         <v>372</v>
-      </c>
-      <c r="B125" t="s">
-        <v>373</v>
-      </c>
-      <c r="C125" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
+        <v>373</v>
+      </c>
+      <c r="B126" t="s">
+        <v>374</v>
+      </c>
+      <c r="C126" t="s">
         <v>375</v>
-      </c>
-      <c r="B126" t="s">
-        <v>376</v>
-      </c>
-      <c r="C126" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
+        <v>376</v>
+      </c>
+      <c r="B127" t="s">
+        <v>377</v>
+      </c>
+      <c r="C127" t="s">
         <v>378</v>
-      </c>
-      <c r="B127" t="s">
-        <v>379</v>
-      </c>
-      <c r="C127" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
+        <v>379</v>
+      </c>
+      <c r="B128" t="s">
+        <v>380</v>
+      </c>
+      <c r="C128" t="s">
         <v>381</v>
-      </c>
-      <c r="B128" t="s">
-        <v>382</v>
-      </c>
-      <c r="C128" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
+        <v>382</v>
+      </c>
+      <c r="B129" t="s">
+        <v>383</v>
+      </c>
+      <c r="C129" t="s">
         <v>384</v>
-      </c>
-      <c r="B129" t="s">
-        <v>385</v>
-      </c>
-      <c r="C129" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
+        <v>385</v>
+      </c>
+      <c r="B130" t="s">
+        <v>386</v>
+      </c>
+      <c r="C130" t="s">
         <v>387</v>
-      </c>
-      <c r="B130" t="s">
-        <v>388</v>
-      </c>
-      <c r="C130" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
+        <v>388</v>
+      </c>
+      <c r="B131" t="s">
+        <v>389</v>
+      </c>
+      <c r="C131" t="s">
         <v>390</v>
-      </c>
-      <c r="B131" t="s">
-        <v>391</v>
-      </c>
-      <c r="C131" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
+        <v>391</v>
+      </c>
+      <c r="B132" t="s">
+        <v>392</v>
+      </c>
+      <c r="C132" t="s">
         <v>393</v>
-      </c>
-      <c r="B132" t="s">
-        <v>394</v>
-      </c>
-      <c r="C132" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
+        <v>394</v>
+      </c>
+      <c r="B133" t="s">
+        <v>395</v>
+      </c>
+      <c r="C133" t="s">
         <v>396</v>
-      </c>
-      <c r="B133" t="s">
-        <v>397</v>
-      </c>
-      <c r="C133" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
+        <v>397</v>
+      </c>
+      <c r="B134" t="s">
+        <v>398</v>
+      </c>
+      <c r="C134" t="s">
         <v>399</v>
-      </c>
-      <c r="B134" t="s">
-        <v>400</v>
-      </c>
-      <c r="C134" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
+        <v>400</v>
+      </c>
+      <c r="B135" t="s">
+        <v>401</v>
+      </c>
+      <c r="C135" t="s">
         <v>402</v>
-      </c>
-      <c r="B135" t="s">
-        <v>403</v>
-      </c>
-      <c r="C135" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
+        <v>403</v>
+      </c>
+      <c r="B136" t="s">
+        <v>404</v>
+      </c>
+      <c r="C136" t="s">
         <v>405</v>
-      </c>
-      <c r="B136" t="s">
-        <v>406</v>
-      </c>
-      <c r="C136" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
+        <v>406</v>
+      </c>
+      <c r="B137" t="s">
+        <v>407</v>
+      </c>
+      <c r="C137" t="s">
         <v>408</v>
-      </c>
-      <c r="B137" t="s">
-        <v>409</v>
-      </c>
-      <c r="C137" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
+        <v>409</v>
+      </c>
+      <c r="B138" t="s">
+        <v>410</v>
+      </c>
+      <c r="C138" t="s">
         <v>411</v>
-      </c>
-      <c r="B138" t="s">
-        <v>412</v>
-      </c>
-      <c r="C138" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
+        <v>412</v>
+      </c>
+      <c r="B139" t="s">
+        <v>413</v>
+      </c>
+      <c r="C139" t="s">
         <v>414</v>
-      </c>
-      <c r="B139" t="s">
-        <v>415</v>
-      </c>
-      <c r="C139" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
+        <v>415</v>
+      </c>
+      <c r="B140" t="s">
+        <v>416</v>
+      </c>
+      <c r="C140" t="s">
         <v>417</v>
-      </c>
-      <c r="B140" t="s">
-        <v>418</v>
-      </c>
-      <c r="C140" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
+        <v>418</v>
+      </c>
+      <c r="B141" t="s">
+        <v>419</v>
+      </c>
+      <c r="C141" t="s">
         <v>420</v>
-      </c>
-      <c r="B141" t="s">
-        <v>421</v>
-      </c>
-      <c r="C141" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
+        <v>421</v>
+      </c>
+      <c r="B142" t="s">
+        <v>422</v>
+      </c>
+      <c r="C142" t="s">
         <v>423</v>
-      </c>
-      <c r="B142" t="s">
-        <v>424</v>
-      </c>
-      <c r="C142" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
+        <v>424</v>
+      </c>
+      <c r="B143" t="s">
+        <v>425</v>
+      </c>
+      <c r="C143" t="s">
         <v>426</v>
-      </c>
-      <c r="B143" t="s">
-        <v>427</v>
-      </c>
-      <c r="C143" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
+        <v>427</v>
+      </c>
+      <c r="B144" t="s">
+        <v>428</v>
+      </c>
+      <c r="C144" t="s">
         <v>429</v>
-      </c>
-      <c r="B144" t="s">
-        <v>430</v>
-      </c>
-      <c r="C144" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
+        <v>430</v>
+      </c>
+      <c r="B145" t="s">
+        <v>431</v>
+      </c>
+      <c r="C145" t="s">
         <v>432</v>
-      </c>
-      <c r="B145" t="s">
-        <v>433</v>
-      </c>
-      <c r="C145" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
+        <v>433</v>
+      </c>
+      <c r="B146" t="s">
+        <v>434</v>
+      </c>
+      <c r="C146" t="s">
         <v>435</v>
-      </c>
-      <c r="B146" t="s">
-        <v>436</v>
-      </c>
-      <c r="C146" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
+        <v>436</v>
+      </c>
+      <c r="B147" t="s">
+        <v>437</v>
+      </c>
+      <c r="C147" t="s">
         <v>438</v>
-      </c>
-      <c r="B147" t="s">
-        <v>439</v>
-      </c>
-      <c r="C147" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
+        <v>439</v>
+      </c>
+      <c r="B148" t="s">
+        <v>440</v>
+      </c>
+      <c r="C148" t="s">
         <v>441</v>
-      </c>
-      <c r="B148" t="s">
-        <v>442</v>
-      </c>
-      <c r="C148" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
+        <v>442</v>
+      </c>
+      <c r="B149" t="s">
+        <v>443</v>
+      </c>
+      <c r="C149" t="s">
         <v>444</v>
-      </c>
-      <c r="B149" t="s">
-        <v>445</v>
-      </c>
-      <c r="C149" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
+        <v>445</v>
+      </c>
+      <c r="B150" t="s">
+        <v>446</v>
+      </c>
+      <c r="C150" t="s">
         <v>447</v>
-      </c>
-      <c r="B150" t="s">
-        <v>448</v>
-      </c>
-      <c r="C150" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
+        <v>448</v>
+      </c>
+      <c r="B151" t="s">
+        <v>449</v>
+      </c>
+      <c r="C151" t="s">
         <v>450</v>
-      </c>
-      <c r="B151" t="s">
-        <v>451</v>
-      </c>
-      <c r="C151" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
+        <v>451</v>
+      </c>
+      <c r="B152" t="s">
+        <v>452</v>
+      </c>
+      <c r="C152" t="s">
         <v>453</v>
-      </c>
-      <c r="B152" t="s">
-        <v>454</v>
-      </c>
-      <c r="C152" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
+        <v>454</v>
+      </c>
+      <c r="B153" t="s">
+        <v>455</v>
+      </c>
+      <c r="C153" t="s">
         <v>456</v>
-      </c>
-      <c r="B153" t="s">
-        <v>457</v>
-      </c>
-      <c r="C153" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
+        <v>457</v>
+      </c>
+      <c r="B154" t="s">
+        <v>458</v>
+      </c>
+      <c r="C154" t="s">
         <v>459</v>
-      </c>
-      <c r="B154" t="s">
-        <v>460</v>
-      </c>
-      <c r="C154" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
+        <v>460</v>
+      </c>
+      <c r="B155" t="s">
+        <v>461</v>
+      </c>
+      <c r="C155" t="s">
         <v>462</v>
-      </c>
-      <c r="B155" t="s">
-        <v>463</v>
-      </c>
-      <c r="C155" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
+        <v>463</v>
+      </c>
+      <c r="B156" t="s">
+        <v>464</v>
+      </c>
+      <c r="C156" t="s">
         <v>465</v>
-      </c>
-      <c r="B156" t="s">
-        <v>466</v>
-      </c>
-      <c r="C156" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
+        <v>466</v>
+      </c>
+      <c r="B157" t="s">
+        <v>467</v>
+      </c>
+      <c r="C157" t="s">
         <v>468</v>
-      </c>
-      <c r="B157" t="s">
-        <v>469</v>
-      </c>
-      <c r="C157" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
+        <v>469</v>
+      </c>
+      <c r="B158" t="s">
+        <v>470</v>
+      </c>
+      <c r="C158" t="s">
         <v>471</v>
-      </c>
-      <c r="B158" t="s">
-        <v>472</v>
-      </c>
-      <c r="C158" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
+        <v>472</v>
+      </c>
+      <c r="B159" t="s">
+        <v>473</v>
+      </c>
+      <c r="C159" t="s">
         <v>474</v>
-      </c>
-      <c r="B159" t="s">
-        <v>475</v>
-      </c>
-      <c r="C159" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
+        <v>475</v>
+      </c>
+      <c r="B160" t="s">
+        <v>476</v>
+      </c>
+      <c r="C160" t="s">
         <v>477</v>
-      </c>
-      <c r="B160" t="s">
-        <v>478</v>
-      </c>
-      <c r="C160" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
+        <v>478</v>
+      </c>
+      <c r="B161" t="s">
+        <v>479</v>
+      </c>
+      <c r="C161" t="s">
         <v>480</v>
-      </c>
-      <c r="B161" t="s">
-        <v>481</v>
-      </c>
-      <c r="C161" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
+        <v>481</v>
+      </c>
+      <c r="B162" t="s">
+        <v>482</v>
+      </c>
+      <c r="C162" t="s">
         <v>483</v>
-      </c>
-      <c r="B162" t="s">
-        <v>484</v>
-      </c>
-      <c r="C162" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
+        <v>484</v>
+      </c>
+      <c r="B163" t="s">
+        <v>485</v>
+      </c>
+      <c r="C163" t="s">
         <v>486</v>
-      </c>
-      <c r="B163" t="s">
-        <v>487</v>
-      </c>
-      <c r="C163" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
+        <v>487</v>
+      </c>
+      <c r="B164" t="s">
+        <v>488</v>
+      </c>
+      <c r="C164" t="s">
         <v>489</v>
-      </c>
-      <c r="B164" t="s">
-        <v>490</v>
-      </c>
-      <c r="C164" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
+        <v>490</v>
+      </c>
+      <c r="B165" t="s">
+        <v>491</v>
+      </c>
+      <c r="C165" t="s">
         <v>492</v>
-      </c>
-      <c r="B165" t="s">
-        <v>493</v>
-      </c>
-      <c r="C165" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
+        <v>493</v>
+      </c>
+      <c r="B166" t="s">
+        <v>494</v>
+      </c>
+      <c r="C166" t="s">
         <v>495</v>
-      </c>
-      <c r="B166" t="s">
-        <v>496</v>
-      </c>
-      <c r="C166" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
+        <v>496</v>
+      </c>
+      <c r="B167" t="s">
+        <v>497</v>
+      </c>
+      <c r="C167" t="s">
         <v>498</v>
-      </c>
-      <c r="B167" t="s">
-        <v>499</v>
-      </c>
-      <c r="C167" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
+        <v>499</v>
+      </c>
+      <c r="B168" t="s">
+        <v>500</v>
+      </c>
+      <c r="C168" t="s">
         <v>501</v>
-      </c>
-      <c r="B168" t="s">
-        <v>502</v>
-      </c>
-      <c r="C168" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
+        <v>502</v>
+      </c>
+      <c r="B169" t="s">
+        <v>503</v>
+      </c>
+      <c r="C169" t="s">
         <v>504</v>
-      </c>
-      <c r="B169" t="s">
-        <v>505</v>
-      </c>
-      <c r="C169" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
+        <v>505</v>
+      </c>
+      <c r="B170" t="s">
+        <v>506</v>
+      </c>
+      <c r="C170" t="s">
         <v>507</v>
-      </c>
-      <c r="B170" t="s">
-        <v>508</v>
-      </c>
-      <c r="C170" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
+        <v>508</v>
+      </c>
+      <c r="B171" t="s">
+        <v>509</v>
+      </c>
+      <c r="C171" t="s">
         <v>510</v>
-      </c>
-      <c r="B171" t="s">
-        <v>511</v>
-      </c>
-      <c r="C171" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
+        <v>511</v>
+      </c>
+      <c r="B172" t="s">
+        <v>512</v>
+      </c>
+      <c r="C172" t="s">
         <v>513</v>
-      </c>
-      <c r="B172" t="s">
-        <v>514</v>
-      </c>
-      <c r="C172" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
+        <v>514</v>
+      </c>
+      <c r="B173" t="s">
+        <v>515</v>
+      </c>
+      <c r="C173" t="s">
         <v>516</v>
-      </c>
-      <c r="B173" t="s">
-        <v>517</v>
-      </c>
-      <c r="C173" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
+        <v>517</v>
+      </c>
+      <c r="B174" t="s">
+        <v>518</v>
+      </c>
+      <c r="C174" t="s">
         <v>519</v>
-      </c>
-      <c r="B174" t="s">
-        <v>520</v>
-      </c>
-      <c r="C174" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
+        <v>520</v>
+      </c>
+      <c r="B175" t="s">
+        <v>521</v>
+      </c>
+      <c r="C175" t="s">
         <v>522</v>
-      </c>
-      <c r="B175" t="s">
-        <v>523</v>
-      </c>
-      <c r="C175" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
+        <v>523</v>
+      </c>
+      <c r="B176" t="s">
+        <v>524</v>
+      </c>
+      <c r="C176" t="s">
         <v>525</v>
-      </c>
-      <c r="B176" t="s">
-        <v>526</v>
-      </c>
-      <c r="C176" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
+        <v>526</v>
+      </c>
+      <c r="B177" t="s">
+        <v>527</v>
+      </c>
+      <c r="C177" t="s">
         <v>528</v>
-      </c>
-      <c r="B177" t="s">
-        <v>529</v>
-      </c>
-      <c r="C177" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
+        <v>529</v>
+      </c>
+      <c r="B178" t="s">
+        <v>530</v>
+      </c>
+      <c r="C178" t="s">
         <v>531</v>
-      </c>
-      <c r="B178" t="s">
-        <v>532</v>
-      </c>
-      <c r="C178" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
+        <v>532</v>
+      </c>
+      <c r="B179" t="s">
+        <v>533</v>
+      </c>
+      <c r="C179" t="s">
         <v>534</v>
-      </c>
-      <c r="B179" t="s">
-        <v>535</v>
-      </c>
-      <c r="C179" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
+        <v>535</v>
+      </c>
+      <c r="B180" t="s">
+        <v>536</v>
+      </c>
+      <c r="C180" t="s">
         <v>537</v>
-      </c>
-      <c r="B180" t="s">
-        <v>538</v>
-      </c>
-      <c r="C180" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
+        <v>538</v>
+      </c>
+      <c r="B181" t="s">
+        <v>539</v>
+      </c>
+      <c r="C181" t="s">
         <v>540</v>
-      </c>
-      <c r="B181" t="s">
-        <v>541</v>
-      </c>
-      <c r="C181" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
+        <v>541</v>
+      </c>
+      <c r="B182" t="s">
+        <v>542</v>
+      </c>
+      <c r="C182" t="s">
         <v>543</v>
-      </c>
-      <c r="B182" t="s">
-        <v>544</v>
-      </c>
-      <c r="C182" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
+        <v>544</v>
+      </c>
+      <c r="B183" t="s">
+        <v>545</v>
+      </c>
+      <c r="C183" t="s">
         <v>546</v>
-      </c>
-      <c r="B183" t="s">
-        <v>547</v>
-      </c>
-      <c r="C183" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
+        <v>547</v>
+      </c>
+      <c r="B184" t="s">
+        <v>548</v>
+      </c>
+      <c r="C184" t="s">
         <v>549</v>
-      </c>
-      <c r="B184" t="s">
-        <v>550</v>
-      </c>
-      <c r="C184" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
+        <v>550</v>
+      </c>
+      <c r="B185" t="s">
+        <v>551</v>
+      </c>
+      <c r="C185" t="s">
         <v>552</v>
-      </c>
-      <c r="B185" t="s">
-        <v>553</v>
-      </c>
-      <c r="C185" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
+        <v>553</v>
+      </c>
+      <c r="B186" t="s">
+        <v>554</v>
+      </c>
+      <c r="C186" t="s">
         <v>555</v>
-      </c>
-      <c r="B186" t="s">
-        <v>556</v>
-      </c>
-      <c r="C186" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
+        <v>556</v>
+      </c>
+      <c r="B187" t="s">
+        <v>557</v>
+      </c>
+      <c r="C187" t="s">
         <v>558</v>
-      </c>
-      <c r="B187" t="s">
-        <v>559</v>
-      </c>
-      <c r="C187" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
+        <v>559</v>
+      </c>
+      <c r="B188" t="s">
+        <v>560</v>
+      </c>
+      <c r="C188" t="s">
         <v>561</v>
-      </c>
-      <c r="B188" t="s">
-        <v>562</v>
-      </c>
-      <c r="C188" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
+        <v>562</v>
+      </c>
+      <c r="B189" t="s">
+        <v>563</v>
+      </c>
+      <c r="C189" t="s">
         <v>564</v>
-      </c>
-      <c r="B189" t="s">
-        <v>565</v>
-      </c>
-      <c r="C189" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
+        <v>565</v>
+      </c>
+      <c r="B190" t="s">
+        <v>566</v>
+      </c>
+      <c r="C190" t="s">
         <v>567</v>
-      </c>
-      <c r="B190" t="s">
-        <v>568</v>
-      </c>
-      <c r="C190" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
+        <v>568</v>
+      </c>
+      <c r="B191" t="s">
+        <v>569</v>
+      </c>
+      <c r="C191" t="s">
         <v>570</v>
-      </c>
-      <c r="B191" t="s">
-        <v>571</v>
-      </c>
-      <c r="C191" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
+        <v>571</v>
+      </c>
+      <c r="B192" t="s">
+        <v>572</v>
+      </c>
+      <c r="C192" t="s">
         <v>573</v>
-      </c>
-      <c r="B192" t="s">
-        <v>574</v>
-      </c>
-      <c r="C192" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
+        <v>574</v>
+      </c>
+      <c r="B193" t="s">
+        <v>575</v>
+      </c>
+      <c r="C193" t="s">
         <v>576</v>
-      </c>
-      <c r="B193" t="s">
-        <v>577</v>
-      </c>
-      <c r="C193" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
+        <v>577</v>
+      </c>
+      <c r="B194" t="s">
+        <v>578</v>
+      </c>
+      <c r="C194" t="s">
         <v>579</v>
-      </c>
-      <c r="B194" t="s">
-        <v>580</v>
-      </c>
-      <c r="C194" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
+        <v>580</v>
+      </c>
+      <c r="B195" t="s">
+        <v>581</v>
+      </c>
+      <c r="C195" t="s">
         <v>582</v>
-      </c>
-      <c r="B195" t="s">
-        <v>583</v>
-      </c>
-      <c r="C195" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B196" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C196" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="B197" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="C197" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="B198" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="C198" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="B199" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="C199" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="B200" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="C200" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="B201" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="C201" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="B202" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="C202" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="B203" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="C203" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="B204" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="C204" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="B205" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="C205" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="B206" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="C206" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="B207" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="C207" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="B208" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="C208" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="B209" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="C209" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="B210" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="C210" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="B211" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="C211" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="B212" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="C212" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="B213" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="C213" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="B214" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="C214" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="B215" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="C215" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="B216" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="C216" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="B217" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="C217" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="B218" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="C218" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="B219" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="C219" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="B220" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="C220" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="B221" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="C221" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="B222" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="C222" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="B223" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="C223" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="B224" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="C224" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="B225" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="C225" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="B226" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="C226" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="B227" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="C227" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B228" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="C228" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="B229" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="C229" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="B230" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="C230" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="B231" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="C231" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="B232" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="C232" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="B233" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="C233" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="B234" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
       <c r="C234" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="B235" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
       <c r="C235" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="B236" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="C236" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="B237" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="C237" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="B238" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="C238" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="B239" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="C239" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="B240" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="C240" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="B241" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="C241" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="B242" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="C242" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="B243" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="C243" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="B244" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="C244" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="B245" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="C245" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="B246" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="C246" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="B247" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="C247" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="B248" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="C248" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="B249" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="C249" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="B250" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="C250" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="B251" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="C251" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="B252" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="C252" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="B253" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="C253" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="B254" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="C254" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="B255" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="C255" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="B256" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="C256" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="B257" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="C257" t="s">
-        <v>770</v>
+        <v>765</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="B258" t="s">
-        <v>772</v>
+        <v>767</v>
       </c>
       <c r="C258" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="B259" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="C259" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="B260" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="C260" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="B261" t="s">
-        <v>781</v>
+        <v>776</v>
       </c>
       <c r="C261" t="s">
-        <v>782</v>
+        <v>777</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>783</v>
+        <v>778</v>
       </c>
       <c r="B262" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="C262" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="B263" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="C263" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="B264" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="C264" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="B265" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="C265" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="B266" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="C266" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="B267" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="C267" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="B268" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="C268" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="B269" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="C269" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="B270" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
       <c r="C270" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="B271" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="C271" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="B272" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="C272" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="B273" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="C273" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="B274" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="C274" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="B275" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="C275" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="B276" t="s">
-        <v>826</v>
+        <v>821</v>
       </c>
       <c r="C276" t="s">
-        <v>827</v>
+        <v>822</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="B277" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
       <c r="C277" t="s">
-        <v>830</v>
+        <v>825</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="B278" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="C278" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="B279" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="C279" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="B280" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
       <c r="C280" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="B281" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="C281" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>843</v>
+        <v>838</v>
       </c>
       <c r="B282" t="s">
-        <v>844</v>
+        <v>839</v>
       </c>
       <c r="C282" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="B283" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="C283" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="B284" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="C284" t="s">
-        <v>851</v>
+        <v>846</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="B285" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="C285" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="B286" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="C286" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="B287" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="C287" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="B288" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="C288" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="B289" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="C289" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="B290" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="C290" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="B291" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="C291" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="B292" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="C292" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="B293" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="C293" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="B294" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="C294" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="B295" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="C295" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="B296" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="C296" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="B297" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="C297" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="B298" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="C298" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="B299" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="C299" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
       <c r="B300" t="s">
-        <v>892</v>
+        <v>887</v>
       </c>
       <c r="C300" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="B301" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="C301" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>897</v>
+        <v>892</v>
       </c>
       <c r="B302" t="s">
-        <v>898</v>
+        <v>893</v>
       </c>
       <c r="C302" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="B303" t="s">
-        <v>901</v>
+        <v>896</v>
       </c>
       <c r="C303" t="s">
-        <v>902</v>
+        <v>897</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="B304" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="C304" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="B305" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="C305" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="B306" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="C306" t="s">
-        <v>911</v>
+        <v>906</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="B307" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="C307" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
       <c r="B308" t="s">
-        <v>916</v>
+        <v>911</v>
       </c>
       <c r="C308" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
       <c r="B309" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
       <c r="C309" t="s">
-        <v>920</v>
+        <v>915</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="B310" t="s">
-        <v>922</v>
+        <v>917</v>
       </c>
       <c r="C310" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>924</v>
+        <v>919</v>
       </c>
       <c r="B311" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="C311" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>927</v>
+        <v>922</v>
       </c>
       <c r="B312" t="s">
-        <v>928</v>
+        <v>923</v>
       </c>
       <c r="C312" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>930</v>
+        <v>925</v>
       </c>
       <c r="B313" t="s">
-        <v>931</v>
+        <v>926</v>
       </c>
       <c r="C313" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>933</v>
+        <v>928</v>
       </c>
       <c r="B314" t="s">
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="C314" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
       <c r="B315" t="s">
-        <v>937</v>
+        <v>932</v>
       </c>
       <c r="C315" t="s">
-        <v>938</v>
+        <v>933</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="B316" t="s">
-        <v>937</v>
+        <v>932</v>
       </c>
       <c r="C316" t="s">
-        <v>938</v>
+        <v>933</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="B317" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="C317" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="B318" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
       <c r="C318" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="B319" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="C319" t="s">
-        <v>948</v>
+        <v>943</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="B320" t="s">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="C320" t="s">
-        <v>951</v>
+        <v>946</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="B321" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="C321" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="B322" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
       <c r="C322" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>958</v>
+        <v>953</v>
       </c>
       <c r="B323" t="s">
-        <v>959</v>
+        <v>954</v>
       </c>
       <c r="C323" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="B324" t="s">
-        <v>962</v>
+        <v>957</v>
       </c>
       <c r="C324" t="s">
-        <v>963</v>
+        <v>958</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>964</v>
+        <v>959</v>
       </c>
       <c r="B325" t="s">
-        <v>965</v>
+        <v>960</v>
       </c>
       <c r="C325" t="s">
-        <v>966</v>
+        <v>961</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>967</v>
+        <v>962</v>
       </c>
       <c r="B326" t="s">
-        <v>968</v>
+        <v>963</v>
       </c>
       <c r="C326" t="s">
-        <v>969</v>
+        <v>964</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>970</v>
+        <v>965</v>
       </c>
       <c r="B327" t="s">
-        <v>971</v>
+        <v>966</v>
       </c>
       <c r="C327" t="s">
-        <v>972</v>
+        <v>967</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>973</v>
+        <v>968</v>
       </c>
       <c r="B328" t="s">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="C328" t="s">
-        <v>975</v>
+        <v>970</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="B329" t="s">
-        <v>977</v>
+        <v>972</v>
       </c>
       <c r="C329" t="s">
-        <v>978</v>
+        <v>973</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>979</v>
+        <v>974</v>
       </c>
       <c r="B330" t="s">
-        <v>980</v>
+        <v>975</v>
       </c>
       <c r="C330" t="s">
-        <v>981</v>
+        <v>976</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>982</v>
+        <v>977</v>
       </c>
       <c r="B331" t="s">
-        <v>983</v>
+        <v>978</v>
       </c>
       <c r="C331" t="s">
-        <v>984</v>
+        <v>979</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>985</v>
+        <v>980</v>
       </c>
       <c r="B332" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="C332" t="s">
-        <v>987</v>
+        <v>982</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>988</v>
+        <v>983</v>
       </c>
       <c r="B333" t="s">
-        <v>989</v>
+        <v>984</v>
       </c>
       <c r="C333" t="s">
-        <v>990</v>
+        <v>985</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>991</v>
+        <v>986</v>
       </c>
       <c r="B334" t="s">
-        <v>992</v>
+        <v>987</v>
       </c>
       <c r="C334" t="s">
-        <v>993</v>
+        <v>988</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>994</v>
+        <v>989</v>
       </c>
       <c r="B335" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="C335" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B336" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
       <c r="C336" t="s">
-        <v>999</v>
+        <v>994</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>1000</v>
+        <v>995</v>
       </c>
       <c r="B337" t="s">
-        <v>1001</v>
+        <v>996</v>
       </c>
       <c r="C337" t="s">
-        <v>1002</v>
+        <v>997</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>1003</v>
+        <v>998</v>
       </c>
       <c r="B338" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="C338" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="B339" t="s">
-        <v>1007</v>
+        <v>1002</v>
       </c>
       <c r="C339" t="s">
-        <v>1008</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>1009</v>
+        <v>1004</v>
       </c>
       <c r="B340" t="s">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="C340" t="s">
-        <v>1011</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>1012</v>
+        <v>1007</v>
       </c>
       <c r="B341" t="s">
-        <v>1013</v>
+        <v>1008</v>
       </c>
       <c r="C341" t="s">
-        <v>1014</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>1015</v>
+        <v>1010</v>
       </c>
       <c r="B342" t="s">
-        <v>1016</v>
+        <v>1011</v>
       </c>
       <c r="C342" t="s">
-        <v>1017</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>1018</v>
+        <v>1013</v>
       </c>
       <c r="B343" t="s">
-        <v>1019</v>
+        <v>1014</v>
       </c>
       <c r="C343" t="s">
-        <v>1020</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="B344" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="C344" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>1024</v>
+        <v>1019</v>
       </c>
       <c r="B345">
         <v>0</v>
       </c>
       <c r="C345" t="s">
-        <v>1025</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
       <c r="B346" t="s">
-        <v>1027</v>
+        <v>1022</v>
       </c>
       <c r="C346" t="s">
-        <v>1028</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="B347" t="s">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="C347" t="s">
-        <v>1031</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>1032</v>
+        <v>1027</v>
       </c>
       <c r="B348" t="s">
-        <v>1033</v>
+        <v>1028</v>
       </c>
       <c r="C348" t="s">
-        <v>1034</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="B349" t="s">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="C349" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="B350" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
       <c r="C350" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="B351" t="s">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="C351" t="s">
-        <v>1043</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="B352" t="s">
-        <v>1045</v>
+        <v>1040</v>
       </c>
       <c r="C352" t="s">
-        <v>1046</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>1047</v>
+        <v>1042</v>
       </c>
       <c r="B353" t="s">
-        <v>1048</v>
+        <v>1043</v>
       </c>
       <c r="C353" t="s">
-        <v>1049</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="B354" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="C354" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
       <c r="B355" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="C355" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="B356" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
       <c r="C356" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="B357" t="s">
-        <v>1058</v>
+        <v>1053</v>
       </c>
       <c r="C357" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="B358" t="s">
-        <v>1060</v>
+        <v>1055</v>
       </c>
       <c r="C358" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>1061</v>
+        <v>1056</v>
       </c>
       <c r="B359" t="s">
-        <v>1062</v>
+        <v>1057</v>
       </c>
       <c r="C359" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>1063</v>
+        <v>1058</v>
       </c>
       <c r="B360" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
       <c r="C360" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>1065</v>
+        <v>1060</v>
       </c>
       <c r="B361" t="s">
-        <v>1066</v>
+        <v>1061</v>
       </c>
       <c r="C361" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>1067</v>
+        <v>1062</v>
       </c>
       <c r="B362" t="s">
-        <v>1068</v>
+        <v>1063</v>
       </c>
       <c r="C362" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>1069</v>
+        <v>1064</v>
       </c>
       <c r="B363" t="s">
-        <v>1070</v>
+        <v>1065</v>
       </c>
       <c r="C363" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
     </row>
   </sheetData>

--- a/Plan/Table/TestData/00.LocaleData.xlsx
+++ b/Plan/Table/TestData/00.LocaleData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\인디\FluffyDisdog\Plan\Table\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7490191C-CDD7-4CA3-B34E-6B3A4DF6246E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A2B6B312-825C-4565-A627-BAAB620B40E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13230" yWindow="4980" windowWidth="14505" windowHeight="13485" xr2:uid="{DAD7A119-9706-4215-B2C0-59D23418D445}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{718AE3B4-58FC-4134-BE68-F2459601629D}"/>
   </bookViews>
   <sheets>
     <sheet name="00.LocaleData" sheetId="1" r:id="rId1"/>
@@ -245,7 +245,7 @@
     <t>Card_WeakeningNormal_Name</t>
   </si>
   <si>
-    <t>약화 카드 - 일반</t>
+    <t>균열 카드 - 일반</t>
   </si>
   <si>
     <t>Weakening Normal</t>
@@ -254,7 +254,7 @@
     <t>Card_WeakeningRare_Name</t>
   </si>
   <si>
-    <t>약화 카드 - 레어</t>
+    <t>균열 카드 - 레어</t>
   </si>
   <si>
     <t>Weakening Rare</t>
@@ -263,7 +263,7 @@
     <t>Card_WeakeningUnique_Name</t>
   </si>
   <si>
-    <t>약화 카드 - 유니크</t>
+    <t>균열 카드 - 유니크</t>
   </si>
   <si>
     <t>Weakening Unique</t>
@@ -1073,7 +1073,7 @@
     <t>Card_WeakeningNormal_Des</t>
   </si>
   <si>
-    <t>약화 카드 - 일반_설명</t>
+    <t>균열 카드 - 일반_설명</t>
   </si>
   <si>
     <t>Weakening Normal Des</t>
@@ -1082,7 +1082,7 @@
     <t>Card_WeakeningRare_Des</t>
   </si>
   <si>
-    <t>약화 카드 - 레어_설명</t>
+    <t>균열 카드 - 레어_설명</t>
   </si>
   <si>
     <t>Weakening Rare Des</t>
@@ -1091,7 +1091,7 @@
     <t>Card_WeakeningUnique_Des</t>
   </si>
   <si>
-    <t>약화 카드 - 유니크_설명</t>
+    <t>균열 카드 - 유니크_설명</t>
   </si>
   <si>
     <t>Weakening Unique Des</t>
@@ -3619,7 +3619,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C96EE684-554F-4E0F-82E4-9992425F531C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B58D71D-2545-40F7-A12E-9DCECEED4663}">
   <dimension ref="A1:C363"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>

--- a/Plan/Table/TestData/00.LocaleData.xlsx
+++ b/Plan/Table/TestData/00.LocaleData.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\인디\FluffyDisdog\Plan\Table\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A2B6B312-825C-4565-A627-BAAB620B40E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D1DC84F-DBAA-495B-8786-370E00EDE362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{718AE3B4-58FC-4134-BE68-F2459601629D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{30AAE311-E029-483E-8DA7-31CEBAE37FE7}"/>
   </bookViews>
   <sheets>
     <sheet name="00.LocaleData" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="1066">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="1054">
   <si>
     <t>key</t>
   </si>
@@ -875,219 +875,183 @@
     <t>Card_Shovel_Des</t>
   </si>
   <si>
-    <t>삽_설명</t>
-  </si>
-  <si>
-    <t>Shovel Des</t>
+    <t>노란색 타격범위에 타일을 100% 확률로 파괴합니다.\\n(도구) 카드를 사용하면 카드가 파괴될 수 있습니다.\\n카드 강화시 카드 파괴 효과는 사라집니다.</t>
+  </si>
+  <si>
+    <t>Destroys tiles in the yellow attack range with 100% chance.\\n(Tool) This card may be destroyed upon use.\\nUpgrading this card removes the destruction effect.</t>
   </si>
   <si>
     <t>Card_Rake_Des</t>
   </si>
   <si>
-    <t>갈퀴_설명</t>
-  </si>
-  <si>
-    <t>Rake Des</t>
+    <t>노란색 타격범위에 타일을 100% 확률로 파괴합니다.\\n흰색 타격 범위에 타일을 66% 확률로 파괴합니다.\\n(도구) 카드를 사용하면 카드가 파괴될 수 있습니다.\\n카드 강화시 카드 파괴 효과는 사라집니다.</t>
+  </si>
+  <si>
+    <t>Destroys tiles in the yellow attack range with 100% chance.\\nDestroys tiles in the white attack range with 66% chance.\\n(Tool) This card may be destroyed upon use.\\nUpgrading this card removes the destruction effect.</t>
   </si>
   <si>
     <t>Card_Shovel_Enhanced_Des</t>
   </si>
   <si>
-    <t>삽+_설명</t>
-  </si>
-  <si>
-    <t>Shovel+ Des</t>
+    <t>노란색 타격범위에 타일을 100% 확률로 파괴합니다.\\n(강화) 방해 블록을 무시하고 파괴합니다.</t>
+  </si>
+  <si>
+    <t>Destroys tiles in the yellow attack range with 100% chance.\\n(Enhanced) Destroys tiles ignoring obstacle blocks.</t>
   </si>
   <si>
     <t>Card_Rake_Enhanced_Des</t>
   </si>
   <si>
-    <t>갈퀴+_설명</t>
-  </si>
-  <si>
-    <t>Rake+ Des</t>
+    <t>노란색과 흰색 타격범위에 타일을 100% 확률로 파괴합니다.</t>
+  </si>
+  <si>
+    <t>Destroys tiles in both yellow and white attack ranges with 100% chance.</t>
   </si>
   <si>
     <t>Card_GoldenShovel_Des</t>
   </si>
   <si>
-    <t>황금 삽_설명</t>
-  </si>
-  <si>
-    <t>Golden Shovel Des</t>
+    <t>노란색 타격범위에 타일을 100% 확률로 파괴합니다.\\n(도구) 카드를 사용하면 카드가 파괴될 수 있습니다.\\n(황금) 카드 사용시 1골드를 획득합니다.</t>
+  </si>
+  <si>
+    <t>Destroys tiles in the yellow attack range with 100% chance.\\n(Tool) This card may be destroyed upon use.\\n(Golden) Grants 1 Gold upon use.</t>
   </si>
   <si>
     <t>Card_GoldenShovel_Enhanced_Des</t>
   </si>
   <si>
-    <t>황금 삽+_설명</t>
-  </si>
-  <si>
-    <t>Golden Shovel+ Des</t>
+    <t>노란색 타격범위에 타일을 100% 확률로 파괴합니다.\\n(황금) 카드 사용시 1골드를 획득합니다.</t>
+  </si>
+  <si>
+    <t>Destroys tiles in the yellow attack range with 100% chance.\\n(Golden) Grants 1 Gold upon use.</t>
   </si>
   <si>
     <t>Card_Axe_Des</t>
   </si>
   <si>
-    <t>도끼_설명</t>
-  </si>
-  <si>
-    <t>Axe Des</t>
-  </si>
-  <si>
     <t>Card_Axe_Enhanced_Des</t>
   </si>
   <si>
-    <t>도끼+_설명</t>
-  </si>
-  <si>
-    <t>Axe+ Des</t>
-  </si>
-  <si>
-    <t>Card_Cross Chisel_Des</t>
-  </si>
-  <si>
-    <t>십자 끌_설명</t>
-  </si>
-  <si>
-    <t>Cross Chisel Des</t>
-  </si>
-  <si>
-    <t>Card_Cross Chisel_Enhanced_Des</t>
-  </si>
-  <si>
-    <t>십자 끌+_설명</t>
-  </si>
-  <si>
-    <t>Cross Chisel+ Des</t>
+    <t>Card_Cross_Chisel_Des</t>
+  </si>
+  <si>
+    <t>노란색 타격범위에 타일을 100% 확률로 파괴합니다.\\n흰색 타격 범위에 타일을 50% 확률로 파괴합니다.\\n(도구) 카드를 사용하면 카드가 파괴될 수 있습니다.\\n카드 강화시 카드 파괴 효과는 사라집니다.</t>
+  </si>
+  <si>
+    <t>Destroys tiles in the yellow attack range with 100% chance.\\nDestroys tiles in the white attack range with 50% chance.\\n(Tool) This card may be destroyed upon use.\\nUpgrading this card removes the destruction effect.</t>
+  </si>
+  <si>
+    <t>Card_Cross_Chisel_Enhanced_Des</t>
+  </si>
+  <si>
+    <t>노란색 타격범위에 타일을 100% 확률로 파괴합니다.\\n흰색 타격 범위에 타일을 75% 확률로 파괴합니다.</t>
+  </si>
+  <si>
+    <t>Destroys tiles in the yellow attack range with 100% chance.\\nDestroys tiles in the white attack range with 75% chance.</t>
   </si>
   <si>
     <t>Card_Pickaxe_Des</t>
   </si>
   <si>
-    <t>곡괭이_설명</t>
-  </si>
-  <si>
-    <t>Pickaxe Des</t>
-  </si>
-  <si>
     <t>Card_Pickaxe_Enhanced_Des</t>
   </si>
   <si>
-    <t>곡괭이+_설명</t>
-  </si>
-  <si>
-    <t>Pickaxe+ Des</t>
-  </si>
-  <si>
     <t>Card_Slingshot_Des</t>
   </si>
   <si>
-    <t>새총_설명</t>
-  </si>
-  <si>
-    <t>Slingshot Des</t>
+    <t>카드 사용시 랜덤한 일반 타일을 5군데 타격합니다.\\n타격시 33% 확률로 타일이 파괴됩니다.\\n(도구) 카드를 사용하면 카드가 파괴될 수 있습니다.</t>
+  </si>
+  <si>
+    <t>Strikes 5 random normal tiles upon use.\\nEach strike has a 33% chance to destroy the tile.\\n(Tool) This card may be destroyed upon use.</t>
   </si>
   <si>
     <t>Card_Slingshot_Enhanced_Des</t>
   </si>
   <si>
-    <t>새총+_설명</t>
-  </si>
-  <si>
-    <t>Slingshot+ Des</t>
+    <t>카드 사용시 랜덤한 일반 타일을 7군데 타격합니다.\\n타격시 50% 확률로 타일이 파괴됩니다.</t>
+  </si>
+  <si>
+    <t>Strikes 7 random normal tiles upon use.\\nEach strike has a 50% chance to destroy the tile.</t>
   </si>
   <si>
     <t>Card_CornerCrushingHammer_Des</t>
   </si>
   <si>
-    <t>모서리 파쇄 해머_설명</t>
-  </si>
-  <si>
-    <t>Corner CrushingHammer Des</t>
+    <t>노란색 타격범위에 타일을 100% 확률로 파괴합니다.\\n노란색을 기준으로 상하좌우에 있는 흰색 타격 범위에 타일을 66% 확률로 파괴합니다.\\n노란색을 기준으로 대각선에 있는 흰색 타격 범위에 타일을 33% 확률로 파괴합니다.\\n(도구) 카드를 사용하면 카드가 파괴될 수 있습니다.\\n카드 강화시 카드 파괴 효과는 사라집니다.</t>
+  </si>
+  <si>
+    <t>Destroys tiles in the yellow attack range with 100% chance.\\nDestroys tiles in the white attack range adjacent to the yellow tile with 66% chance.\\nDestroys tiles in the white attack range diagonal to the yellow tile with 33% chance.\\n(Tool) This card may be destroyed upon use.\\nUpgrading this card removes the destruction effect.</t>
   </si>
   <si>
     <t>Card_CornerCrushingHammer_Enhanced_Des</t>
   </si>
   <si>
-    <t>모서리 파쇄 해머+_설명</t>
-  </si>
-  <si>
-    <t>Corner CrushingHammer+ Des</t>
+    <t>노란색 타격범위에 타일을 100% 확률로 파괴합니다.\\n노란색을 기준으로 상하좌우에 있는 흰색 타격 범위에 타일을 75% 확률로 파괴합니다.\\n노란색을 기준으로 대각선에 있는 흰색 타격 범위에 타일을 50% 확률로 파괴합니다.</t>
+  </si>
+  <si>
+    <t>Destroys tiles in the yellow attack range with 100% chance.\\nDestroys tiles in the white attack range adjacent to the yellow tile with 75% chance.\\nDestroys tiles in the white attack range diagonal to the yellow tile with 50% chance.</t>
   </si>
   <si>
     <t>Card_ConcentratedCrossDrill_Des</t>
   </si>
   <si>
-    <t>집중형 십자 드릴_설명</t>
-  </si>
-  <si>
-    <t>Concentrated CrossDrill Des</t>
+    <t>노란색 타격범위에 타일을 100% 확률로 파괴합니다.\\n노란색을 기준으로 대각선에 있는 흰색 타격 범위에 타일을 66% 확률로 파괴합니다.\\n노란색을 기준으로 상하좌우에 있는 흰색 타격 범위에 타일을 33% 확률로 파괴합니다.\\n(도구) 카드를 사용하면 카드가 파괴될 수 있습니다.\\n카드 강화시 카드 파괴 효과는 사라집니다.</t>
+  </si>
+  <si>
+    <t>Destroys tiles in the yellow attack range with 100% chance.\\nDestroys tiles in the white attack range diagonal to the yellow tile with 66% chance.\\nDestroys tiles in the white attack range adjacent to the yellow tile with 33% chance.\\n(Tool) This card may be destroyed upon use.\\nUpgrading this card removes the destruction effect.</t>
   </si>
   <si>
     <t>Card_ConcentratedCrossDrill_Enhanced_Des</t>
   </si>
   <si>
-    <t>집중형 십자 드릴+_설명</t>
-  </si>
-  <si>
-    <t>Concentrated CrossDrill+ Des</t>
+    <t>노란색 타격범위에 타일을 100% 확률로 파괴합니다.\\n노란색을 기준으로 대각선에 있는 흰색 타격 범위에 타일을 75% 확률로 파괴합니다.\\n노란색을 기준으로 상하좌우에 있는 흰색 타격 범위에 타일을 50% 확률로 파괴합니다.</t>
+  </si>
+  <si>
+    <t>Destroys tiles in the yellow attack range with 100% chance.\\nDestroys tiles in the white attack range diagonal to the yellow tile with 75% chance.\\nDestroys tiles in the white attack range adjacent to the yellow tile with 50% chance.</t>
   </si>
   <si>
     <t>Card_GoldenAxe_Des</t>
   </si>
   <si>
-    <t>황금 도끼_설명</t>
-  </si>
-  <si>
-    <t>Golden Axe Des</t>
+    <t>노란색 타격범위에 타일을 100% 확률로 파괴합니다.\\n흰색 타격 범위에 타일을 66% 확률로 파괴합니다.\\n(도구) 카드를 사용하면 카드가 파괴될 수 있습니다.\\n(황금) 카드 사용시 1골드를 획득합니다.</t>
+  </si>
+  <si>
+    <t>Destroys tiles in the yellow attack range with 100% chance.\\nDestroys tiles in the white attack range with 66% chance.\\n(Tool) This card may be destroyed upon use.\\n(Golden) Grants 1 Gold upon use.</t>
   </si>
   <si>
     <t>Card_GoldenAxe_Enhanced_Des</t>
   </si>
   <si>
-    <t>황금 도끼+_설명</t>
-  </si>
-  <si>
-    <t>Golden Axe+ Des</t>
-  </si>
-  <si>
-    <t>Card_Large Scissors_Des</t>
-  </si>
-  <si>
-    <t>대형 가위_설명</t>
-  </si>
-  <si>
-    <t>Large Scissors Des</t>
-  </si>
-  <si>
-    <t>Card_Large Scissors_Enhanced_Des</t>
-  </si>
-  <si>
-    <t>대형 가위+_설명</t>
-  </si>
-  <si>
-    <t>Large Scissors+ Des</t>
+    <t>노란색과 흰색 타격범위에 타일을 100% 확률로 파괴합니다.\\n(황금) 카드 사용시 1골드를 획득합니다.</t>
+  </si>
+  <si>
+    <t>Destroys tiles in both yellow and white attack ranges with 100% chance.\\n(Golden) Grants 1 Gold upon use.</t>
+  </si>
+  <si>
+    <t>Card_Large_Scissors_Des</t>
+  </si>
+  <si>
+    <t>노란색 타격범위에 타일을 100% 확률로 파괴합니다.\\n흰색 타격 범위에 타일을 75% 확률로 파괴합니다.\\n(도구) 카드를 사용하면 카드가 파괴될 수 있습니다.\\n카드 강화시 카드 파괴 효과는 사라집니다.</t>
+  </si>
+  <si>
+    <t>Destroys tiles in the yellow attack range with 100% chance.\\nDestroys tiles in the white attack range with 75% chance.\\n(Tool) This card may be destroyed upon use.\\nUpgrading this card removes the destruction effect.</t>
+  </si>
+  <si>
+    <t>Card_Large_Scissors_Enhanced_Des</t>
   </si>
   <si>
     <t>Card_WeakeningNormal_Des</t>
   </si>
   <si>
-    <t>균열 카드 - 일반_설명</t>
-  </si>
-  <si>
-    <t>Weakening Normal Des</t>
+    <t>노란색과 하늘색 타격범위에 일반 타일을 100% 확률로 균열 상태로 만듭니다.\\n균열된 타일은 다음 턴에 타격 시 타격 확률을 무시하고 파괴됩니다.</t>
+  </si>
+  <si>
+    <t>Inflicts Cracked status on normal tiles in the yellow and sky-blue attack ranges with 100% chance.\\nCracked tiles are destroyed on the next turn when struck, ignoring hit chance.</t>
   </si>
   <si>
     <t>Card_WeakeningRare_Des</t>
   </si>
   <si>
-    <t>균열 카드 - 레어_설명</t>
-  </si>
-  <si>
-    <t>Weakening Rare Des</t>
-  </si>
-  <si>
     <t>Card_WeakeningUnique_Des</t>
   </si>
   <si>
@@ -1163,19 +1127,19 @@
     <t>Card_RiftStartumAnalysis_Des</t>
   </si>
   <si>
-    <t>균열 지층 분석_설명</t>
-  </si>
-  <si>
-    <t>Rift StartumAnalysis Des</t>
+    <t>노란색 타격범위에 타일을 100% 확률로 파괴합니다.\\n흰색 타격 범위에 타일을 0% 확률로 파괴할 수 있다.\\n이 카드로 타일을 3개 이상 부술 경우, 타격 범위에 있는 모든 일반 타일을 파괴합니다.\\n파괴된 타일 중 균열 타일 1개당 2 Gold를 지급합니다.\\n이 카드로 타일을 5칸 부술 경우 덱에 존재하는 황금 태그 카드 1장을 드로우합니다.\\n(도구) 카드를 사용하면 카드가 파괴될 수 있습니다.\\n카드 강화시 카드 파괴 효과는 사라집니다.</t>
+  </si>
+  <si>
+    <t>Destroys tiles in the yellow attack range with 100% chance.\\nTiles in the white attack range cannot be destroyed.\\nIf 3 or more tiles are destroyed with this card, all normal tiles in the attack range are destroyed.\\nGrants 2 Gold for each Cracked tile destroyed.\\nIf 5 tiles are destroyed with this card, draw 1 Golden-tag card from your deck.\\n(Tool) This card may be destroyed upon use.\\nUpgrading this card removes the destruction effect.</t>
   </si>
   <si>
     <t>Card_RiftStartumAnalysis_Enhanced_Des</t>
   </si>
   <si>
-    <t>균열 지층 분석+_설명</t>
-  </si>
-  <si>
-    <t>Rift StartumAnalysis+ Des</t>
+    <t>노란색 타격범위에 타일을 100% 확률로 파괴합니다.\\n흰색 타격 범위에 타일을 0% 확률로 파괴할 수 있다.\\n이 카드로 타일을 3개 이상 부술 경우, 타격 범위에 있는 모든 일반 타일을 파괴합니다.\\n파괴된 타일 중 균열 타일 1개당 5 Gold를 지급합니다.\\n이 카드로 타일을 5칸 부술 경우 덱에 존재하는 황금 태그 카드 2장을 드로우합니다.</t>
+  </si>
+  <si>
+    <t>Destroys tiles in the yellow attack range with 100% chance.\\nTiles in the white attack range cannot be destroyed.\\nIf 3 or more tiles are destroyed with this card, all normal tiles in the attack range are destroyed.\\nGrants 5 Gold for each Cracked tile destroyed.\\nIf 5 tiles are destroyed with this card, draw 2 Golden-tag cards from your deck.</t>
   </si>
   <si>
     <t>Card_Novice_Wand_Des</t>
@@ -3619,7 +3583,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B58D71D-2545-40F7-A12E-9DCECEED4663}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17E3A1A9-230A-4B43-8ADF-E683A4F17058}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C363"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -4717,2903 +4682,2903 @@
         <v>295</v>
       </c>
       <c r="B100" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="C100" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B101" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="C101" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B102" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C102" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B103" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C103" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B104" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="C104" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="B105" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="C105" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="B106" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="C106" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="B107" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="C107" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="B108" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="C108" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="B109" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="C109" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="B110" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="C110" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="B111" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="C111" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="B112" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C112" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="B113" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="C113" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="B114" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="C114" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="B115" t="s">
-        <v>341</v>
+        <v>287</v>
       </c>
       <c r="C115" t="s">
-        <v>342</v>
+        <v>288</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="B116" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="C116" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="B117" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="C117" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="B118" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="C118" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="B119" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="C119" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="B120" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="C120" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="B121" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="C121" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="B122" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="C122" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="B123" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="C123" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="B124" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="C124" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="B125" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="C125" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="B126" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="C126" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="B127" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="C127" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="B128" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="C128" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="B129" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="C129" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="B130" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="C130" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="B131" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="C131" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="B132" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="C132" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="B133" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="C133" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="B134" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="C134" t="s">
-        <v>399</v>
+        <v>387</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="B135" t="s">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="C135" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="B136" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="C136" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="B137" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="C137" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="B138" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="C138" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="B139" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="C139" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="B140" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="C140" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="B141" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="C141" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="B142" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="C142" t="s">
-        <v>423</v>
+        <v>411</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="B143" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="C143" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="B144" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="C144" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="B145" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="C145" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="B146" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="C146" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="B147" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="C147" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="B148" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="C148" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="B149" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="C149" t="s">
-        <v>444</v>
+        <v>432</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="B150" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="C150" t="s">
-        <v>447</v>
+        <v>435</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="B151" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="C151" t="s">
-        <v>450</v>
+        <v>438</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="B152" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="C152" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="B153" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="C153" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="B154" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="C154" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="B155" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="C155" t="s">
-        <v>462</v>
+        <v>450</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="B156" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="C156" t="s">
-        <v>465</v>
+        <v>453</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="B157" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="C157" t="s">
-        <v>468</v>
+        <v>456</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="B158" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="C158" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="B159" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="C159" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="B160" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="C160" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="B161" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="C161" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="B162" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="C162" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="B163" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="C163" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="B164" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="C164" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="B165" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="C165" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="B166" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="C166" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="B167" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="C167" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="B168" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="C168" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="B169" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="C169" t="s">
-        <v>504</v>
+        <v>492</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="B170" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="C170" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="B171" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="C171" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="B172" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="C172" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="B173" t="s">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="C173" t="s">
-        <v>516</v>
+        <v>504</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="B174" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="C174" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>520</v>
+        <v>508</v>
       </c>
       <c r="B175" t="s">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="C175" t="s">
-        <v>522</v>
+        <v>510</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>523</v>
+        <v>511</v>
       </c>
       <c r="B176" t="s">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="C176" t="s">
-        <v>525</v>
+        <v>513</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>526</v>
+        <v>514</v>
       </c>
       <c r="B177" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="C177" t="s">
-        <v>528</v>
+        <v>516</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="B178" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="C178" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="B179" t="s">
-        <v>533</v>
+        <v>521</v>
       </c>
       <c r="C179" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="B180" t="s">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="C180" t="s">
-        <v>537</v>
+        <v>525</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="B181" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="C181" t="s">
-        <v>540</v>
+        <v>528</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="B182" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="C182" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="B183" t="s">
-        <v>545</v>
+        <v>533</v>
       </c>
       <c r="C183" t="s">
-        <v>546</v>
+        <v>534</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="B184" t="s">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="C184" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="B185" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="C185" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>553</v>
+        <v>541</v>
       </c>
       <c r="B186" t="s">
-        <v>554</v>
+        <v>542</v>
       </c>
       <c r="C186" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="B187" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="C187" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="B188" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
       <c r="C188" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="B189" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
       <c r="C189" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="B190" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="C190" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
       <c r="B191" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="C191" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="B192" t="s">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="C192" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="B193" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="C193" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="B194" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="C194" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
       <c r="B195" t="s">
-        <v>581</v>
+        <v>569</v>
       </c>
       <c r="C195" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="B196" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="C196" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>585</v>
+        <v>573</v>
       </c>
       <c r="B197" t="s">
-        <v>586</v>
+        <v>574</v>
       </c>
       <c r="C197" t="s">
-        <v>587</v>
+        <v>575</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>588</v>
+        <v>576</v>
       </c>
       <c r="B198" t="s">
-        <v>589</v>
+        <v>577</v>
       </c>
       <c r="C198" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>591</v>
+        <v>579</v>
       </c>
       <c r="B199" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="C199" t="s">
-        <v>593</v>
+        <v>581</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="B200" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="C200" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>597</v>
+        <v>585</v>
       </c>
       <c r="B201" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="C201" t="s">
-        <v>599</v>
+        <v>587</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="B202" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="C202" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="B203" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="C203" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>606</v>
+        <v>594</v>
       </c>
       <c r="B204" t="s">
-        <v>607</v>
+        <v>595</v>
       </c>
       <c r="C204" t="s">
-        <v>608</v>
+        <v>596</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="B205" t="s">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="C205" t="s">
-        <v>611</v>
+        <v>599</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="B206" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="C206" t="s">
-        <v>614</v>
+        <v>602</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>615</v>
+        <v>603</v>
       </c>
       <c r="B207" t="s">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="C207" t="s">
-        <v>616</v>
+        <v>604</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="B208" t="s">
-        <v>618</v>
+        <v>606</v>
       </c>
       <c r="C208" t="s">
-        <v>618</v>
+        <v>606</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>619</v>
+        <v>607</v>
       </c>
       <c r="B209" t="s">
-        <v>620</v>
+        <v>608</v>
       </c>
       <c r="C209" t="s">
-        <v>621</v>
+        <v>609</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="B210" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="C210" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="B211" t="s">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="C211" t="s">
-        <v>627</v>
+        <v>615</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>628</v>
+        <v>616</v>
       </c>
       <c r="B212" t="s">
-        <v>629</v>
+        <v>617</v>
       </c>
       <c r="C212" t="s">
-        <v>630</v>
+        <v>618</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>631</v>
+        <v>619</v>
       </c>
       <c r="B213" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="C213" t="s">
-        <v>633</v>
+        <v>621</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>634</v>
+        <v>622</v>
       </c>
       <c r="B214" t="s">
-        <v>635</v>
+        <v>623</v>
       </c>
       <c r="C214" t="s">
-        <v>636</v>
+        <v>624</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>637</v>
+        <v>625</v>
       </c>
       <c r="B215" t="s">
-        <v>638</v>
+        <v>626</v>
       </c>
       <c r="C215" t="s">
-        <v>639</v>
+        <v>627</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>640</v>
+        <v>628</v>
       </c>
       <c r="B216" t="s">
-        <v>641</v>
+        <v>629</v>
       </c>
       <c r="C216" t="s">
-        <v>642</v>
+        <v>630</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="B217" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="C217" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="B218" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="C218" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>649</v>
+        <v>637</v>
       </c>
       <c r="B219" t="s">
-        <v>650</v>
+        <v>638</v>
       </c>
       <c r="C219" t="s">
-        <v>651</v>
+        <v>639</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>652</v>
+        <v>640</v>
       </c>
       <c r="B220" t="s">
-        <v>653</v>
+        <v>641</v>
       </c>
       <c r="C220" t="s">
-        <v>654</v>
+        <v>642</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>655</v>
+        <v>643</v>
       </c>
       <c r="B221" t="s">
-        <v>656</v>
+        <v>644</v>
       </c>
       <c r="C221" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>658</v>
+        <v>646</v>
       </c>
       <c r="B222" t="s">
-        <v>659</v>
+        <v>647</v>
       </c>
       <c r="C222" t="s">
-        <v>660</v>
+        <v>648</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>661</v>
+        <v>649</v>
       </c>
       <c r="B223" t="s">
-        <v>662</v>
+        <v>650</v>
       </c>
       <c r="C223" t="s">
-        <v>663</v>
+        <v>651</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>664</v>
+        <v>652</v>
       </c>
       <c r="B224" t="s">
-        <v>665</v>
+        <v>653</v>
       </c>
       <c r="C224" t="s">
-        <v>666</v>
+        <v>654</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>667</v>
+        <v>655</v>
       </c>
       <c r="B225" t="s">
-        <v>668</v>
+        <v>656</v>
       </c>
       <c r="C225" t="s">
-        <v>669</v>
+        <v>657</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>670</v>
+        <v>658</v>
       </c>
       <c r="B226" t="s">
-        <v>671</v>
+        <v>659</v>
       </c>
       <c r="C226" t="s">
-        <v>672</v>
+        <v>660</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>673</v>
+        <v>661</v>
       </c>
       <c r="B227" t="s">
-        <v>674</v>
+        <v>662</v>
       </c>
       <c r="C227" t="s">
-        <v>675</v>
+        <v>663</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>676</v>
+        <v>664</v>
       </c>
       <c r="B228" t="s">
-        <v>677</v>
+        <v>665</v>
       </c>
       <c r="C228" t="s">
-        <v>678</v>
+        <v>666</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>679</v>
+        <v>667</v>
       </c>
       <c r="B229" t="s">
-        <v>680</v>
+        <v>668</v>
       </c>
       <c r="C229" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>682</v>
+        <v>670</v>
       </c>
       <c r="B230" t="s">
-        <v>683</v>
+        <v>671</v>
       </c>
       <c r="C230" t="s">
-        <v>684</v>
+        <v>672</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>685</v>
+        <v>673</v>
       </c>
       <c r="B231" t="s">
-        <v>686</v>
+        <v>674</v>
       </c>
       <c r="C231" t="s">
-        <v>687</v>
+        <v>675</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>688</v>
+        <v>676</v>
       </c>
       <c r="B232" t="s">
-        <v>689</v>
+        <v>677</v>
       </c>
       <c r="C232" t="s">
-        <v>690</v>
+        <v>678</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>691</v>
+        <v>679</v>
       </c>
       <c r="B233" t="s">
-        <v>692</v>
+        <v>680</v>
       </c>
       <c r="C233" t="s">
-        <v>693</v>
+        <v>681</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>694</v>
+        <v>682</v>
       </c>
       <c r="B234" t="s">
-        <v>695</v>
+        <v>683</v>
       </c>
       <c r="C234" t="s">
-        <v>696</v>
+        <v>684</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>697</v>
+        <v>685</v>
       </c>
       <c r="B235" t="s">
-        <v>698</v>
+        <v>686</v>
       </c>
       <c r="C235" t="s">
-        <v>699</v>
+        <v>687</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>700</v>
+        <v>688</v>
       </c>
       <c r="B236" t="s">
-        <v>701</v>
+        <v>689</v>
       </c>
       <c r="C236" t="s">
-        <v>702</v>
+        <v>690</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>703</v>
+        <v>691</v>
       </c>
       <c r="B237" t="s">
-        <v>704</v>
+        <v>692</v>
       </c>
       <c r="C237" t="s">
-        <v>705</v>
+        <v>693</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>706</v>
+        <v>694</v>
       </c>
       <c r="B238" t="s">
-        <v>707</v>
+        <v>695</v>
       </c>
       <c r="C238" t="s">
-        <v>708</v>
+        <v>696</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>709</v>
+        <v>697</v>
       </c>
       <c r="B239" t="s">
-        <v>710</v>
+        <v>698</v>
       </c>
       <c r="C239" t="s">
-        <v>711</v>
+        <v>699</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>712</v>
+        <v>700</v>
       </c>
       <c r="B240" t="s">
-        <v>713</v>
+        <v>701</v>
       </c>
       <c r="C240" t="s">
-        <v>714</v>
+        <v>702</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>715</v>
+        <v>703</v>
       </c>
       <c r="B241" t="s">
-        <v>716</v>
+        <v>704</v>
       </c>
       <c r="C241" t="s">
-        <v>717</v>
+        <v>705</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>718</v>
+        <v>706</v>
       </c>
       <c r="B242" t="s">
-        <v>719</v>
+        <v>707</v>
       </c>
       <c r="C242" t="s">
-        <v>720</v>
+        <v>708</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>721</v>
+        <v>709</v>
       </c>
       <c r="B243" t="s">
-        <v>722</v>
+        <v>710</v>
       </c>
       <c r="C243" t="s">
-        <v>723</v>
+        <v>711</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>724</v>
+        <v>712</v>
       </c>
       <c r="B244" t="s">
-        <v>725</v>
+        <v>713</v>
       </c>
       <c r="C244" t="s">
-        <v>726</v>
+        <v>714</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>727</v>
+        <v>715</v>
       </c>
       <c r="B245" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="C245" t="s">
-        <v>729</v>
+        <v>717</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>730</v>
+        <v>718</v>
       </c>
       <c r="B246" t="s">
-        <v>731</v>
+        <v>719</v>
       </c>
       <c r="C246" t="s">
-        <v>732</v>
+        <v>720</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>733</v>
+        <v>721</v>
       </c>
       <c r="B247" t="s">
-        <v>734</v>
+        <v>722</v>
       </c>
       <c r="C247" t="s">
-        <v>735</v>
+        <v>723</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>736</v>
+        <v>724</v>
       </c>
       <c r="B248" t="s">
-        <v>737</v>
+        <v>725</v>
       </c>
       <c r="C248" t="s">
-        <v>738</v>
+        <v>726</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>739</v>
+        <v>727</v>
       </c>
       <c r="B249" t="s">
-        <v>740</v>
+        <v>728</v>
       </c>
       <c r="C249" t="s">
-        <v>741</v>
+        <v>729</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>742</v>
+        <v>730</v>
       </c>
       <c r="B250" t="s">
-        <v>743</v>
+        <v>731</v>
       </c>
       <c r="C250" t="s">
-        <v>744</v>
+        <v>732</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>745</v>
+        <v>733</v>
       </c>
       <c r="B251" t="s">
-        <v>746</v>
+        <v>734</v>
       </c>
       <c r="C251" t="s">
-        <v>747</v>
+        <v>735</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>748</v>
+        <v>736</v>
       </c>
       <c r="B252" t="s">
-        <v>749</v>
+        <v>737</v>
       </c>
       <c r="C252" t="s">
-        <v>750</v>
+        <v>738</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>751</v>
+        <v>739</v>
       </c>
       <c r="B253" t="s">
-        <v>752</v>
+        <v>740</v>
       </c>
       <c r="C253" t="s">
-        <v>753</v>
+        <v>741</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>754</v>
+        <v>742</v>
       </c>
       <c r="B254" t="s">
-        <v>755</v>
+        <v>743</v>
       </c>
       <c r="C254" t="s">
-        <v>756</v>
+        <v>744</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>757</v>
+        <v>745</v>
       </c>
       <c r="B255" t="s">
-        <v>758</v>
+        <v>746</v>
       </c>
       <c r="C255" t="s">
-        <v>759</v>
+        <v>747</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>760</v>
+        <v>748</v>
       </c>
       <c r="B256" t="s">
-        <v>761</v>
+        <v>749</v>
       </c>
       <c r="C256" t="s">
-        <v>762</v>
+        <v>750</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>763</v>
+        <v>751</v>
       </c>
       <c r="B257" t="s">
-        <v>764</v>
+        <v>752</v>
       </c>
       <c r="C257" t="s">
-        <v>765</v>
+        <v>753</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>766</v>
+        <v>754</v>
       </c>
       <c r="B258" t="s">
-        <v>767</v>
+        <v>755</v>
       </c>
       <c r="C258" t="s">
-        <v>768</v>
+        <v>756</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="B259" t="s">
-        <v>770</v>
+        <v>758</v>
       </c>
       <c r="C259" t="s">
-        <v>771</v>
+        <v>759</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>772</v>
+        <v>760</v>
       </c>
       <c r="B260" t="s">
-        <v>773</v>
+        <v>761</v>
       </c>
       <c r="C260" t="s">
-        <v>774</v>
+        <v>762</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>775</v>
+        <v>763</v>
       </c>
       <c r="B261" t="s">
-        <v>776</v>
+        <v>764</v>
       </c>
       <c r="C261" t="s">
-        <v>777</v>
+        <v>765</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>778</v>
+        <v>766</v>
       </c>
       <c r="B262" t="s">
-        <v>779</v>
+        <v>767</v>
       </c>
       <c r="C262" t="s">
-        <v>780</v>
+        <v>768</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>781</v>
+        <v>769</v>
       </c>
       <c r="B263" t="s">
-        <v>782</v>
+        <v>770</v>
       </c>
       <c r="C263" t="s">
-        <v>783</v>
+        <v>771</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>784</v>
+        <v>772</v>
       </c>
       <c r="B264" t="s">
-        <v>785</v>
+        <v>773</v>
       </c>
       <c r="C264" t="s">
-        <v>786</v>
+        <v>774</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>787</v>
+        <v>775</v>
       </c>
       <c r="B265" t="s">
-        <v>788</v>
+        <v>776</v>
       </c>
       <c r="C265" t="s">
-        <v>789</v>
+        <v>777</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>790</v>
+        <v>778</v>
       </c>
       <c r="B266" t="s">
-        <v>791</v>
+        <v>779</v>
       </c>
       <c r="C266" t="s">
-        <v>792</v>
+        <v>780</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>793</v>
+        <v>781</v>
       </c>
       <c r="B267" t="s">
-        <v>794</v>
+        <v>782</v>
       </c>
       <c r="C267" t="s">
-        <v>795</v>
+        <v>783</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>796</v>
+        <v>784</v>
       </c>
       <c r="B268" t="s">
-        <v>797</v>
+        <v>785</v>
       </c>
       <c r="C268" t="s">
-        <v>798</v>
+        <v>786</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>799</v>
+        <v>787</v>
       </c>
       <c r="B269" t="s">
-        <v>800</v>
+        <v>788</v>
       </c>
       <c r="C269" t="s">
-        <v>801</v>
+        <v>789</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>802</v>
+        <v>790</v>
       </c>
       <c r="B270" t="s">
-        <v>803</v>
+        <v>791</v>
       </c>
       <c r="C270" t="s">
-        <v>804</v>
+        <v>792</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>805</v>
+        <v>793</v>
       </c>
       <c r="B271" t="s">
-        <v>806</v>
+        <v>794</v>
       </c>
       <c r="C271" t="s">
-        <v>807</v>
+        <v>795</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>808</v>
+        <v>796</v>
       </c>
       <c r="B272" t="s">
-        <v>809</v>
+        <v>797</v>
       </c>
       <c r="C272" t="s">
-        <v>810</v>
+        <v>798</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>811</v>
+        <v>799</v>
       </c>
       <c r="B273" t="s">
-        <v>812</v>
+        <v>800</v>
       </c>
       <c r="C273" t="s">
-        <v>813</v>
+        <v>801</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>814</v>
+        <v>802</v>
       </c>
       <c r="B274" t="s">
-        <v>815</v>
+        <v>803</v>
       </c>
       <c r="C274" t="s">
-        <v>816</v>
+        <v>804</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>817</v>
+        <v>805</v>
       </c>
       <c r="B275" t="s">
-        <v>818</v>
+        <v>806</v>
       </c>
       <c r="C275" t="s">
-        <v>819</v>
+        <v>807</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>820</v>
+        <v>808</v>
       </c>
       <c r="B276" t="s">
-        <v>821</v>
+        <v>809</v>
       </c>
       <c r="C276" t="s">
-        <v>822</v>
+        <v>810</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>823</v>
+        <v>811</v>
       </c>
       <c r="B277" t="s">
-        <v>824</v>
+        <v>812</v>
       </c>
       <c r="C277" t="s">
-        <v>825</v>
+        <v>813</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>826</v>
+        <v>814</v>
       </c>
       <c r="B278" t="s">
-        <v>827</v>
+        <v>815</v>
       </c>
       <c r="C278" t="s">
-        <v>828</v>
+        <v>816</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
       <c r="B279" t="s">
-        <v>830</v>
+        <v>818</v>
       </c>
       <c r="C279" t="s">
-        <v>831</v>
+        <v>819</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>832</v>
+        <v>820</v>
       </c>
       <c r="B280" t="s">
-        <v>833</v>
+        <v>821</v>
       </c>
       <c r="C280" t="s">
-        <v>834</v>
+        <v>822</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>835</v>
+        <v>823</v>
       </c>
       <c r="B281" t="s">
-        <v>836</v>
+        <v>824</v>
       </c>
       <c r="C281" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>838</v>
+        <v>826</v>
       </c>
       <c r="B282" t="s">
-        <v>839</v>
+        <v>827</v>
       </c>
       <c r="C282" t="s">
-        <v>840</v>
+        <v>828</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>841</v>
+        <v>829</v>
       </c>
       <c r="B283" t="s">
-        <v>842</v>
+        <v>830</v>
       </c>
       <c r="C283" t="s">
-        <v>843</v>
+        <v>831</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>844</v>
+        <v>832</v>
       </c>
       <c r="B284" t="s">
-        <v>845</v>
+        <v>833</v>
       </c>
       <c r="C284" t="s">
-        <v>846</v>
+        <v>834</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>847</v>
+        <v>835</v>
       </c>
       <c r="B285" t="s">
-        <v>848</v>
+        <v>836</v>
       </c>
       <c r="C285" t="s">
-        <v>849</v>
+        <v>837</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>850</v>
+        <v>838</v>
       </c>
       <c r="B286" t="s">
-        <v>851</v>
+        <v>839</v>
       </c>
       <c r="C286" t="s">
-        <v>852</v>
+        <v>840</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>853</v>
+        <v>841</v>
       </c>
       <c r="B287" t="s">
-        <v>854</v>
+        <v>842</v>
       </c>
       <c r="C287" t="s">
-        <v>855</v>
+        <v>843</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>856</v>
+        <v>844</v>
       </c>
       <c r="B288" t="s">
-        <v>857</v>
+        <v>845</v>
       </c>
       <c r="C288" t="s">
-        <v>858</v>
+        <v>846</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>859</v>
+        <v>847</v>
       </c>
       <c r="B289" t="s">
-        <v>860</v>
+        <v>848</v>
       </c>
       <c r="C289" t="s">
-        <v>861</v>
+        <v>849</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>862</v>
+        <v>850</v>
       </c>
       <c r="B290" t="s">
-        <v>863</v>
+        <v>851</v>
       </c>
       <c r="C290" t="s">
-        <v>864</v>
+        <v>852</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>865</v>
+        <v>853</v>
       </c>
       <c r="B291" t="s">
-        <v>866</v>
+        <v>854</v>
       </c>
       <c r="C291" t="s">
-        <v>867</v>
+        <v>855</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>868</v>
+        <v>856</v>
       </c>
       <c r="B292" t="s">
-        <v>869</v>
+        <v>857</v>
       </c>
       <c r="C292" t="s">
-        <v>870</v>
+        <v>858</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>871</v>
+        <v>859</v>
       </c>
       <c r="B293" t="s">
-        <v>872</v>
+        <v>860</v>
       </c>
       <c r="C293" t="s">
-        <v>873</v>
+        <v>861</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>874</v>
+        <v>862</v>
       </c>
       <c r="B294" t="s">
-        <v>875</v>
+        <v>863</v>
       </c>
       <c r="C294" t="s">
-        <v>876</v>
+        <v>864</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>877</v>
+        <v>865</v>
       </c>
       <c r="B295" t="s">
-        <v>878</v>
+        <v>866</v>
       </c>
       <c r="C295" t="s">
-        <v>879</v>
+        <v>867</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>880</v>
+        <v>868</v>
       </c>
       <c r="B296" t="s">
-        <v>881</v>
+        <v>869</v>
       </c>
       <c r="C296" t="s">
-        <v>882</v>
+        <v>870</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>883</v>
+        <v>871</v>
       </c>
       <c r="B297" t="s">
-        <v>881</v>
+        <v>869</v>
       </c>
       <c r="C297" t="s">
-        <v>882</v>
+        <v>870</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>884</v>
+        <v>872</v>
       </c>
       <c r="B298" t="s">
-        <v>881</v>
+        <v>869</v>
       </c>
       <c r="C298" t="s">
-        <v>882</v>
+        <v>870</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>885</v>
+        <v>873</v>
       </c>
       <c r="B299" t="s">
-        <v>881</v>
+        <v>869</v>
       </c>
       <c r="C299" t="s">
-        <v>882</v>
+        <v>870</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>886</v>
+        <v>874</v>
       </c>
       <c r="B300" t="s">
-        <v>887</v>
+        <v>875</v>
       </c>
       <c r="C300" t="s">
-        <v>888</v>
+        <v>876</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>889</v>
+        <v>877</v>
       </c>
       <c r="B301" t="s">
-        <v>890</v>
+        <v>878</v>
       </c>
       <c r="C301" t="s">
-        <v>891</v>
+        <v>879</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>892</v>
+        <v>880</v>
       </c>
       <c r="B302" t="s">
-        <v>893</v>
+        <v>881</v>
       </c>
       <c r="C302" t="s">
-        <v>894</v>
+        <v>882</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>895</v>
+        <v>883</v>
       </c>
       <c r="B303" t="s">
-        <v>896</v>
+        <v>884</v>
       </c>
       <c r="C303" t="s">
-        <v>897</v>
+        <v>885</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>898</v>
+        <v>886</v>
       </c>
       <c r="B304" t="s">
-        <v>899</v>
+        <v>887</v>
       </c>
       <c r="C304" t="s">
-        <v>900</v>
+        <v>888</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>901</v>
+        <v>889</v>
       </c>
       <c r="B305" t="s">
-        <v>902</v>
+        <v>890</v>
       </c>
       <c r="C305" t="s">
-        <v>903</v>
+        <v>891</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>904</v>
+        <v>892</v>
       </c>
       <c r="B306" t="s">
-        <v>905</v>
+        <v>893</v>
       </c>
       <c r="C306" t="s">
-        <v>906</v>
+        <v>894</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>907</v>
+        <v>895</v>
       </c>
       <c r="B307" t="s">
-        <v>908</v>
+        <v>896</v>
       </c>
       <c r="C307" t="s">
-        <v>909</v>
+        <v>897</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>910</v>
+        <v>898</v>
       </c>
       <c r="B308" t="s">
-        <v>911</v>
+        <v>899</v>
       </c>
       <c r="C308" t="s">
-        <v>912</v>
+        <v>900</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>913</v>
+        <v>901</v>
       </c>
       <c r="B309" t="s">
-        <v>914</v>
+        <v>902</v>
       </c>
       <c r="C309" t="s">
-        <v>915</v>
+        <v>903</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>916</v>
+        <v>904</v>
       </c>
       <c r="B310" t="s">
-        <v>917</v>
+        <v>905</v>
       </c>
       <c r="C310" t="s">
-        <v>918</v>
+        <v>906</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>919</v>
+        <v>907</v>
       </c>
       <c r="B311" t="s">
-        <v>920</v>
+        <v>908</v>
       </c>
       <c r="C311" t="s">
-        <v>921</v>
+        <v>909</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>922</v>
+        <v>910</v>
       </c>
       <c r="B312" t="s">
-        <v>923</v>
+        <v>911</v>
       </c>
       <c r="C312" t="s">
-        <v>924</v>
+        <v>912</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>925</v>
+        <v>913</v>
       </c>
       <c r="B313" t="s">
-        <v>926</v>
+        <v>914</v>
       </c>
       <c r="C313" t="s">
-        <v>927</v>
+        <v>915</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>928</v>
+        <v>916</v>
       </c>
       <c r="B314" t="s">
-        <v>929</v>
+        <v>917</v>
       </c>
       <c r="C314" t="s">
-        <v>930</v>
+        <v>918</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>931</v>
+        <v>919</v>
       </c>
       <c r="B315" t="s">
-        <v>932</v>
+        <v>920</v>
       </c>
       <c r="C315" t="s">
-        <v>933</v>
+        <v>921</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>934</v>
+        <v>922</v>
       </c>
       <c r="B316" t="s">
-        <v>932</v>
+        <v>920</v>
       </c>
       <c r="C316" t="s">
-        <v>933</v>
+        <v>921</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>935</v>
+        <v>923</v>
       </c>
       <c r="B317" t="s">
-        <v>936</v>
+        <v>924</v>
       </c>
       <c r="C317" t="s">
-        <v>937</v>
+        <v>925</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>938</v>
+        <v>926</v>
       </c>
       <c r="B318" t="s">
-        <v>939</v>
+        <v>927</v>
       </c>
       <c r="C318" t="s">
-        <v>940</v>
+        <v>928</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>941</v>
+        <v>929</v>
       </c>
       <c r="B319" t="s">
-        <v>942</v>
+        <v>930</v>
       </c>
       <c r="C319" t="s">
-        <v>943</v>
+        <v>931</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>944</v>
+        <v>932</v>
       </c>
       <c r="B320" t="s">
-        <v>945</v>
+        <v>933</v>
       </c>
       <c r="C320" t="s">
-        <v>946</v>
+        <v>934</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>947</v>
+        <v>935</v>
       </c>
       <c r="B321" t="s">
-        <v>948</v>
+        <v>936</v>
       </c>
       <c r="C321" t="s">
-        <v>949</v>
+        <v>937</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>950</v>
+        <v>938</v>
       </c>
       <c r="B322" t="s">
-        <v>951</v>
+        <v>939</v>
       </c>
       <c r="C322" t="s">
-        <v>952</v>
+        <v>940</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>953</v>
+        <v>941</v>
       </c>
       <c r="B323" t="s">
-        <v>954</v>
+        <v>942</v>
       </c>
       <c r="C323" t="s">
-        <v>955</v>
+        <v>943</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>956</v>
+        <v>944</v>
       </c>
       <c r="B324" t="s">
-        <v>957</v>
+        <v>945</v>
       </c>
       <c r="C324" t="s">
-        <v>958</v>
+        <v>946</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>959</v>
+        <v>947</v>
       </c>
       <c r="B325" t="s">
-        <v>960</v>
+        <v>948</v>
       </c>
       <c r="C325" t="s">
-        <v>961</v>
+        <v>949</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>962</v>
+        <v>950</v>
       </c>
       <c r="B326" t="s">
-        <v>963</v>
+        <v>951</v>
       </c>
       <c r="C326" t="s">
-        <v>964</v>
+        <v>952</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>965</v>
+        <v>953</v>
       </c>
       <c r="B327" t="s">
-        <v>966</v>
+        <v>954</v>
       </c>
       <c r="C327" t="s">
-        <v>967</v>
+        <v>955</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="B328" t="s">
-        <v>969</v>
+        <v>957</v>
       </c>
       <c r="C328" t="s">
-        <v>970</v>
+        <v>958</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>971</v>
+        <v>959</v>
       </c>
       <c r="B329" t="s">
-        <v>972</v>
+        <v>960</v>
       </c>
       <c r="C329" t="s">
-        <v>973</v>
+        <v>961</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>974</v>
+        <v>962</v>
       </c>
       <c r="B330" t="s">
-        <v>975</v>
+        <v>963</v>
       </c>
       <c r="C330" t="s">
-        <v>976</v>
+        <v>964</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>977</v>
+        <v>965</v>
       </c>
       <c r="B331" t="s">
-        <v>978</v>
+        <v>966</v>
       </c>
       <c r="C331" t="s">
-        <v>979</v>
+        <v>967</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>980</v>
+        <v>968</v>
       </c>
       <c r="B332" t="s">
-        <v>981</v>
+        <v>969</v>
       </c>
       <c r="C332" t="s">
-        <v>982</v>
+        <v>970</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>983</v>
+        <v>971</v>
       </c>
       <c r="B333" t="s">
-        <v>984</v>
+        <v>972</v>
       </c>
       <c r="C333" t="s">
-        <v>985</v>
+        <v>973</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>986</v>
+        <v>974</v>
       </c>
       <c r="B334" t="s">
-        <v>987</v>
+        <v>975</v>
       </c>
       <c r="C334" t="s">
-        <v>988</v>
+        <v>976</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>989</v>
+        <v>977</v>
       </c>
       <c r="B335" t="s">
-        <v>990</v>
+        <v>978</v>
       </c>
       <c r="C335" t="s">
-        <v>991</v>
+        <v>979</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>992</v>
+        <v>980</v>
       </c>
       <c r="B336" t="s">
-        <v>993</v>
+        <v>981</v>
       </c>
       <c r="C336" t="s">
-        <v>994</v>
+        <v>982</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>995</v>
+        <v>983</v>
       </c>
       <c r="B337" t="s">
-        <v>996</v>
+        <v>984</v>
       </c>
       <c r="C337" t="s">
-        <v>997</v>
+        <v>985</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>998</v>
+        <v>986</v>
       </c>
       <c r="B338" t="s">
-        <v>999</v>
+        <v>987</v>
       </c>
       <c r="C338" t="s">
-        <v>1000</v>
+        <v>988</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>1001</v>
+        <v>989</v>
       </c>
       <c r="B339" t="s">
-        <v>1002</v>
+        <v>990</v>
       </c>
       <c r="C339" t="s">
-        <v>1003</v>
+        <v>991</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>1004</v>
+        <v>992</v>
       </c>
       <c r="B340" t="s">
-        <v>1005</v>
+        <v>993</v>
       </c>
       <c r="C340" t="s">
-        <v>1006</v>
+        <v>994</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>1007</v>
+        <v>995</v>
       </c>
       <c r="B341" t="s">
-        <v>1008</v>
+        <v>996</v>
       </c>
       <c r="C341" t="s">
-        <v>1009</v>
+        <v>997</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>1010</v>
+        <v>998</v>
       </c>
       <c r="B342" t="s">
-        <v>1011</v>
+        <v>999</v>
       </c>
       <c r="C342" t="s">
-        <v>1012</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>1013</v>
+        <v>1001</v>
       </c>
       <c r="B343" t="s">
-        <v>1014</v>
+        <v>1002</v>
       </c>
       <c r="C343" t="s">
-        <v>1015</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>1016</v>
+        <v>1004</v>
       </c>
       <c r="B344" t="s">
-        <v>1017</v>
+        <v>1005</v>
       </c>
       <c r="C344" t="s">
-        <v>1018</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>1019</v>
+        <v>1007</v>
       </c>
       <c r="B345">
         <v>0</v>
       </c>
       <c r="C345" t="s">
-        <v>1020</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>1021</v>
+        <v>1009</v>
       </c>
       <c r="B346" t="s">
-        <v>1022</v>
+        <v>1010</v>
       </c>
       <c r="C346" t="s">
-        <v>1023</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>1024</v>
+        <v>1012</v>
       </c>
       <c r="B347" t="s">
-        <v>1025</v>
+        <v>1013</v>
       </c>
       <c r="C347" t="s">
-        <v>1026</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>1027</v>
+        <v>1015</v>
       </c>
       <c r="B348" t="s">
-        <v>1028</v>
+        <v>1016</v>
       </c>
       <c r="C348" t="s">
-        <v>1029</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>1030</v>
+        <v>1018</v>
       </c>
       <c r="B349" t="s">
-        <v>1031</v>
+        <v>1019</v>
       </c>
       <c r="C349" t="s">
-        <v>1032</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>1033</v>
+        <v>1021</v>
       </c>
       <c r="B350" t="s">
-        <v>1034</v>
+        <v>1022</v>
       </c>
       <c r="C350" t="s">
-        <v>1035</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>1036</v>
+        <v>1024</v>
       </c>
       <c r="B351" t="s">
-        <v>1037</v>
+        <v>1025</v>
       </c>
       <c r="C351" t="s">
-        <v>1038</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>1039</v>
+        <v>1027</v>
       </c>
       <c r="B352" t="s">
-        <v>1040</v>
+        <v>1028</v>
       </c>
       <c r="C352" t="s">
-        <v>1041</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>1042</v>
+        <v>1030</v>
       </c>
       <c r="B353" t="s">
-        <v>1043</v>
+        <v>1031</v>
       </c>
       <c r="C353" t="s">
-        <v>1044</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>1045</v>
+        <v>1033</v>
       </c>
       <c r="B354" t="s">
-        <v>1046</v>
+        <v>1034</v>
       </c>
       <c r="C354" t="s">
-        <v>1047</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>1048</v>
+        <v>1036</v>
       </c>
       <c r="B355" t="s">
-        <v>1049</v>
+        <v>1037</v>
       </c>
       <c r="C355" t="s">
-        <v>1047</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>1050</v>
+        <v>1038</v>
       </c>
       <c r="B356" t="s">
-        <v>1051</v>
+        <v>1039</v>
       </c>
       <c r="C356" t="s">
-        <v>1047</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>1052</v>
+        <v>1040</v>
       </c>
       <c r="B357" t="s">
-        <v>1053</v>
+        <v>1041</v>
       </c>
       <c r="C357" t="s">
-        <v>1047</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>1054</v>
+        <v>1042</v>
       </c>
       <c r="B358" t="s">
-        <v>1055</v>
+        <v>1043</v>
       </c>
       <c r="C358" t="s">
-        <v>1047</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>1056</v>
+        <v>1044</v>
       </c>
       <c r="B359" t="s">
-        <v>1057</v>
+        <v>1045</v>
       </c>
       <c r="C359" t="s">
-        <v>1047</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>1058</v>
+        <v>1046</v>
       </c>
       <c r="B360" t="s">
-        <v>1059</v>
+        <v>1047</v>
       </c>
       <c r="C360" t="s">
-        <v>1047</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>1060</v>
+        <v>1048</v>
       </c>
       <c r="B361" t="s">
-        <v>1061</v>
+        <v>1049</v>
       </c>
       <c r="C361" t="s">
-        <v>1047</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>1062</v>
+        <v>1050</v>
       </c>
       <c r="B362" t="s">
-        <v>1063</v>
+        <v>1051</v>
       </c>
       <c r="C362" t="s">
-        <v>1047</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>1064</v>
+        <v>1052</v>
       </c>
       <c r="B363" t="s">
-        <v>1065</v>
+        <v>1053</v>
       </c>
       <c r="C363" t="s">
-        <v>1047</v>
+        <v>1035</v>
       </c>
     </row>
   </sheetData>

--- a/Plan/Table/TestData/00.LocaleData.xlsx
+++ b/Plan/Table/TestData/00.LocaleData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\인디\FluffyDisdog\Plan\Table\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D1DC84F-DBAA-495B-8786-370E00EDE362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD9D8018-C190-49E6-A178-ABC3212F390B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{30AAE311-E029-483E-8DA7-31CEBAE37FE7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A3F8BECA-BED9-4861-84BD-0B1E73E11484}"/>
   </bookViews>
   <sheets>
     <sheet name="00.LocaleData" sheetId="1" r:id="rId1"/>
@@ -122,13 +122,13 @@
     <t>Axe+</t>
   </si>
   <si>
-    <t>Card_Cross Chisel_Name</t>
+    <t>Card_Cross_Chisel_Name</t>
   </si>
   <si>
     <t>나무 망치</t>
   </si>
   <si>
-    <t>Card_Cross Chisel_Enhanced_Name</t>
+    <t>Card_Cross_Chisel_Enhanced_Name</t>
   </si>
   <si>
     <t>나무 망치+</t>
@@ -224,7 +224,7 @@
     <t>Golden Axe+</t>
   </si>
   <si>
-    <t>Card_Large Scissors_Name</t>
+    <t>Card_Large_Scissors_Name</t>
   </si>
   <si>
     <t>대형 가위</t>
@@ -233,7 +233,7 @@
     <t>Large Scissors</t>
   </si>
   <si>
-    <t>Card_Large Scissors_Enhanced_Name</t>
+    <t>Card_Large_Scissors_Enhanced_Name</t>
   </si>
   <si>
     <t>대형 가위+</t>
@@ -3583,7 +3583,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17E3A1A9-230A-4B43-8ADF-E683A4F17058}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9F29214-BB63-47C0-9C3F-3E5C369A2ACD}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C363"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>

--- a/Plan/Table/TestData/00.LocaleData.xlsx
+++ b/Plan/Table/TestData/00.LocaleData.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\인디\FluffyDisdog\Plan\Table\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD9D8018-C190-49E6-A178-ABC3212F390B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F18C48D0-82D5-4E2C-BAB4-94802AEB544A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A3F8BECA-BED9-4861-84BD-0B1E73E11484}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{0D94B96B-AFBA-4F5C-A2F9-89D9A5E8125A}"/>
   </bookViews>
   <sheets>
     <sheet name="00.LocaleData" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="1054">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="1059">
   <si>
     <t>key</t>
   </si>
@@ -128,12 +128,18 @@
     <t>나무 망치</t>
   </si>
   <si>
+    <t>Wooden Hammer</t>
+  </si>
+  <si>
     <t>Card_Cross_Chisel_Enhanced_Name</t>
   </si>
   <si>
     <t>나무 망치+</t>
   </si>
   <si>
+    <t>Wooden Hammer+</t>
+  </si>
+  <si>
     <t>Card_Pickaxe_Name</t>
   </si>
   <si>
@@ -1760,6 +1766,9 @@
     <t>긴급 수리 테이프</t>
   </si>
   <si>
+    <t>Emergency Repair Tape</t>
+  </si>
+  <si>
     <t>relic112_Name</t>
   </si>
   <si>
@@ -1802,13 +1811,13 @@
     <t>대못</t>
   </si>
   <si>
-    <t>Rift Generator</t>
+    <t>Large Nail</t>
   </si>
   <si>
     <t>relic117_Name</t>
   </si>
   <si>
-    <t>균열 파편 강화*</t>
+    <t>균열 파편 강화</t>
   </si>
   <si>
     <t>Rift Fragment Reinforcement</t>
@@ -1856,10 +1865,16 @@
     <t>수평계</t>
   </si>
   <si>
+    <t>Spirit Level</t>
+  </si>
+  <si>
     <t>relic123_Name</t>
   </si>
   <si>
     <t>세로추</t>
+  </si>
+  <si>
+    <t>Plumb Bob</t>
   </si>
   <si>
     <t>relic201_Name</t>
@@ -3583,8 +3598,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9F29214-BB63-47C0-9C3F-3E5C369A2ACD}">
-  <sheetPr codeName="Sheet1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{527CDD1D-BA3C-4FC2-974E-432ACF109AEC}">
   <dimension ref="A1:C363"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -3695,3890 +3709,3890 @@
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B19" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C19" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B20" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B21" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C21" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B22" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C22" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B23" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C23" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B24" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C24" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B25" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C25" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B26" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C26" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B27" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C27" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B28" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C28" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B29" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C29" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B30" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B31" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C31" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B32" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C32" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B33" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C33" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B34" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C34" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B35" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C35" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B36" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C36" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B37" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C37" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B38" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C38" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B39" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C39" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B40" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C40" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B41" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C41" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B42" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C42" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B43" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C43" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B44" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C44" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B45" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C45" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B46" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C46" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B47" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C47" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B48" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C48" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B49" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C49" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B50" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C50" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B51" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C51" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B52" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C52" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B53" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C53" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B54" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C54" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B55" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C55" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B56" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C56" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B57" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C57" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B58" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C58" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B59" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C59" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B60" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C60" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B61" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C61" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B62" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C62" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B63" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C63" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B64" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C64" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B65" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C65" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B66" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C66" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B67" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C67" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B68" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C68" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B69" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C69" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B70" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C70" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B71" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C71" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B72" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C72" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B73" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C73" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B74" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C74" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B75" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C75" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B76" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C76" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B77" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C77" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B78" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C78" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B79" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C79" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B80" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C80" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B81" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C81" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B82" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C82" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B83" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C83" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B84" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C84" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B85" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C85" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B86" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C86" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B87" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C87" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B88" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B89" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C89" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B90" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C90" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B91" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C91" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B92" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C92" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B93" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C93" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B94" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C94" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B95" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C95" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B96" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C96" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B97" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C97" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B98" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C98" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B99" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C99" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B100" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C100" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B101" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C101" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B102" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C102" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B103" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C103" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B104" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C104" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
+        <v>306</v>
+      </c>
+      <c r="B105" t="s">
+        <v>303</v>
+      </c>
+      <c r="C105" t="s">
         <v>304</v>
-      </c>
-      <c r="B105" t="s">
-        <v>301</v>
-      </c>
-      <c r="C105" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B106" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C106" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B107" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C107" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B108" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C108" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B109" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C109" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B110" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C110" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B111" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C111" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B112" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C112" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B113" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C113" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B114" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C114" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B115" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C115" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B116" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C116" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
+        <v>338</v>
+      </c>
+      <c r="B117" t="s">
         <v>336</v>
       </c>
-      <c r="B117" t="s">
-        <v>334</v>
-      </c>
       <c r="C117" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B118" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C118" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B119" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C119" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B120" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C120" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B121" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C121" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B122" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C122" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B123" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C123" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B124" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C124" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B125" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C125" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B126" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C126" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B127" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C127" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B128" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C128" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B129" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C129" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B130" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C130" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B131" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C131" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B132" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C132" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B133" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C133" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B134" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C134" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B135" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C135" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B136" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C136" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B137" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C137" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B138" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C138" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B139" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C139" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B140" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C140" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B141" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C141" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B142" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C142" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B143" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C143" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B144" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C144" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B145" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C145" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B146" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C146" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B147" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C147" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B148" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C148" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B149" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C149" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B150" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C150" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B151" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C151" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B152" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C152" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B153" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C153" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B154" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C154" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B155" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C155" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B156" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C156" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B157" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C157" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B158" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C158" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B159" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C159" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B160" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C160" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B161" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C161" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B162" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C162" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B163" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C163" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B164" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C164" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B165" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C165" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B166" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C166" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B167" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C167" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B168" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C168" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B169" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C169" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B170" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C170" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B171" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C171" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B172" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C172" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B173" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C173" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B174" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C174" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B175" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C175" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B176" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C176" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B177" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C177" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B178" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C178" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B179" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C179" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B180" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C180" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B181" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C181" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B182" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C182" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B183" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C183" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B184" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C184" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B185" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C185" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B186" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C186" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B187" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C187" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B188" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C188" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B189" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C189" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B190" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C190" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B191" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C191" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B192" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C192" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B193" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C193" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B194" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C194" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B195" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C195" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B196" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C196" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="B197" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="C197" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B198" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C198" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="B199" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C199" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="B200" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="C200" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="B201" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="C201" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B202" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C202" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="B203" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="C203" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B204" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="C204" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="B205" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="C205" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="B206" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="C206" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="B207" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="C207" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="B208" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="C208" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="B209" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="C209" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="B210" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="C210" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="B211" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="C211" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="B212" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="C212" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="B213" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="C213" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="B214" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="C214" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="B215" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="C215" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="B216" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="C216" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="B217" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="C217" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="B218" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="C218" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="B219" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="C219" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="B220" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="C220" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="B221" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="C221" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="B222" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="C222" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="B223" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="C223" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="B224" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="C224" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="B225" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="C225" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="B226" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="C226" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="B227" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="C227" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="B228" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="C228" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="B229" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="C229" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="B230" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="C230" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="B231" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="C231" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="B232" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="C232" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="B233" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="C233" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="B234" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="C234" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="B235" t="s">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="C235" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="B236" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="C236" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="B237" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="C237" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>694</v>
+        <v>699</v>
       </c>
       <c r="B238" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="C238" t="s">
-        <v>696</v>
+        <v>701</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="B239" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="C239" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="B240" t="s">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="C240" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="B241" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="C241" t="s">
-        <v>705</v>
+        <v>710</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="B242" t="s">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="C242" t="s">
-        <v>708</v>
+        <v>713</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="B243" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="C243" t="s">
-        <v>711</v>
+        <v>716</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="B244" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="C244" t="s">
-        <v>714</v>
+        <v>719</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="B245" t="s">
-        <v>716</v>
+        <v>721</v>
       </c>
       <c r="C245" t="s">
-        <v>717</v>
+        <v>722</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>718</v>
+        <v>723</v>
       </c>
       <c r="B246" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="C246" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="B247" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
       <c r="C247" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>724</v>
+        <v>729</v>
       </c>
       <c r="B248" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="C248" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="B249" t="s">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="C249" t="s">
-        <v>729</v>
+        <v>734</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="B250" t="s">
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="C250" t="s">
-        <v>732</v>
+        <v>737</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="B251" t="s">
-        <v>734</v>
+        <v>739</v>
       </c>
       <c r="C251" t="s">
-        <v>735</v>
+        <v>740</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="B252" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="C252" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="B253" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="C253" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="B254" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="C254" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="B255" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="C255" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>748</v>
+        <v>753</v>
       </c>
       <c r="B256" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="C256" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="B257" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="C257" t="s">
-        <v>753</v>
+        <v>758</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>754</v>
+        <v>759</v>
       </c>
       <c r="B258" t="s">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="C258" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="B259" t="s">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="C259" t="s">
-        <v>759</v>
+        <v>764</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="B260" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="C260" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="B261" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="C261" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="B262" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
       <c r="C262" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>769</v>
+        <v>774</v>
       </c>
       <c r="B263" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
       <c r="C263" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="B264" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="C264" t="s">
-        <v>774</v>
+        <v>779</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="B265" t="s">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="C265" t="s">
-        <v>777</v>
+        <v>782</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="B266" t="s">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="C266" t="s">
-        <v>780</v>
+        <v>785</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="B267" t="s">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="C267" t="s">
-        <v>783</v>
+        <v>788</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="B268" t="s">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="C268" t="s">
-        <v>786</v>
+        <v>791</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="B269" t="s">
-        <v>788</v>
+        <v>793</v>
       </c>
       <c r="C269" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="B270" t="s">
-        <v>791</v>
+        <v>796</v>
       </c>
       <c r="C270" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>793</v>
+        <v>798</v>
       </c>
       <c r="B271" t="s">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="C271" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="B272" t="s">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="C272" t="s">
-        <v>798</v>
+        <v>803</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>799</v>
+        <v>804</v>
       </c>
       <c r="B273" t="s">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="C273" t="s">
-        <v>801</v>
+        <v>806</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>802</v>
+        <v>807</v>
       </c>
       <c r="B274" t="s">
-        <v>803</v>
+        <v>808</v>
       </c>
       <c r="C274" t="s">
-        <v>804</v>
+        <v>809</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="B275" t="s">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="C275" t="s">
-        <v>807</v>
+        <v>812</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>808</v>
+        <v>813</v>
       </c>
       <c r="B276" t="s">
-        <v>809</v>
+        <v>814</v>
       </c>
       <c r="C276" t="s">
-        <v>810</v>
+        <v>815</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>811</v>
+        <v>816</v>
       </c>
       <c r="B277" t="s">
-        <v>812</v>
+        <v>817</v>
       </c>
       <c r="C277" t="s">
-        <v>813</v>
+        <v>818</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>814</v>
+        <v>819</v>
       </c>
       <c r="B278" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="C278" t="s">
-        <v>816</v>
+        <v>821</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>817</v>
+        <v>822</v>
       </c>
       <c r="B279" t="s">
-        <v>818</v>
+        <v>823</v>
       </c>
       <c r="C279" t="s">
-        <v>819</v>
+        <v>824</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>820</v>
+        <v>825</v>
       </c>
       <c r="B280" t="s">
-        <v>821</v>
+        <v>826</v>
       </c>
       <c r="C280" t="s">
-        <v>822</v>
+        <v>827</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>823</v>
+        <v>828</v>
       </c>
       <c r="B281" t="s">
-        <v>824</v>
+        <v>829</v>
       </c>
       <c r="C281" t="s">
-        <v>825</v>
+        <v>830</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>826</v>
+        <v>831</v>
       </c>
       <c r="B282" t="s">
-        <v>827</v>
+        <v>832</v>
       </c>
       <c r="C282" t="s">
-        <v>828</v>
+        <v>833</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>829</v>
+        <v>834</v>
       </c>
       <c r="B283" t="s">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="C283" t="s">
-        <v>831</v>
+        <v>836</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>832</v>
+        <v>837</v>
       </c>
       <c r="B284" t="s">
-        <v>833</v>
+        <v>838</v>
       </c>
       <c r="C284" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="B285" t="s">
-        <v>836</v>
+        <v>841</v>
       </c>
       <c r="C285" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>838</v>
+        <v>843</v>
       </c>
       <c r="B286" t="s">
-        <v>839</v>
+        <v>844</v>
       </c>
       <c r="C286" t="s">
-        <v>840</v>
+        <v>845</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>841</v>
+        <v>846</v>
       </c>
       <c r="B287" t="s">
-        <v>842</v>
+        <v>847</v>
       </c>
       <c r="C287" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>844</v>
+        <v>849</v>
       </c>
       <c r="B288" t="s">
-        <v>845</v>
+        <v>850</v>
       </c>
       <c r="C288" t="s">
-        <v>846</v>
+        <v>851</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>847</v>
+        <v>852</v>
       </c>
       <c r="B289" t="s">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="C289" t="s">
-        <v>849</v>
+        <v>854</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>850</v>
+        <v>855</v>
       </c>
       <c r="B290" t="s">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="C290" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="B291" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C291" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="B292" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="C292" t="s">
-        <v>858</v>
+        <v>863</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>859</v>
+        <v>864</v>
       </c>
       <c r="B293" t="s">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="C293" t="s">
-        <v>861</v>
+        <v>866</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>862</v>
+        <v>867</v>
       </c>
       <c r="B294" t="s">
-        <v>863</v>
+        <v>868</v>
       </c>
       <c r="C294" t="s">
-        <v>864</v>
+        <v>869</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>865</v>
+        <v>870</v>
       </c>
       <c r="B295" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="C295" t="s">
-        <v>867</v>
+        <v>872</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>868</v>
+        <v>873</v>
       </c>
       <c r="B296" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="C296" t="s">
-        <v>870</v>
+        <v>875</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>871</v>
+        <v>876</v>
       </c>
       <c r="B297" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="C297" t="s">
-        <v>870</v>
+        <v>875</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="B298" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="C298" t="s">
-        <v>870</v>
+        <v>875</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>873</v>
+        <v>878</v>
       </c>
       <c r="B299" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="C299" t="s">
-        <v>870</v>
+        <v>875</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="B300" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="C300" t="s">
-        <v>876</v>
+        <v>881</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="B301" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="C301" t="s">
-        <v>879</v>
+        <v>884</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>880</v>
+        <v>885</v>
       </c>
       <c r="B302" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="C302" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>883</v>
+        <v>888</v>
       </c>
       <c r="B303" t="s">
-        <v>884</v>
+        <v>889</v>
       </c>
       <c r="C303" t="s">
-        <v>885</v>
+        <v>890</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>886</v>
+        <v>891</v>
       </c>
       <c r="B304" t="s">
-        <v>887</v>
+        <v>892</v>
       </c>
       <c r="C304" t="s">
-        <v>888</v>
+        <v>893</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>889</v>
+        <v>894</v>
       </c>
       <c r="B305" t="s">
-        <v>890</v>
+        <v>895</v>
       </c>
       <c r="C305" t="s">
-        <v>891</v>
+        <v>896</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="B306" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="C306" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="B307" t="s">
-        <v>896</v>
+        <v>901</v>
       </c>
       <c r="C307" t="s">
-        <v>897</v>
+        <v>902</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>898</v>
+        <v>903</v>
       </c>
       <c r="B308" t="s">
-        <v>899</v>
+        <v>904</v>
       </c>
       <c r="C308" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="B309" t="s">
-        <v>902</v>
+        <v>907</v>
       </c>
       <c r="C309" t="s">
-        <v>903</v>
+        <v>908</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>904</v>
+        <v>909</v>
       </c>
       <c r="B310" t="s">
-        <v>905</v>
+        <v>910</v>
       </c>
       <c r="C310" t="s">
-        <v>906</v>
+        <v>911</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>907</v>
+        <v>912</v>
       </c>
       <c r="B311" t="s">
-        <v>908</v>
+        <v>913</v>
       </c>
       <c r="C311" t="s">
-        <v>909</v>
+        <v>914</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>910</v>
+        <v>915</v>
       </c>
       <c r="B312" t="s">
-        <v>911</v>
+        <v>916</v>
       </c>
       <c r="C312" t="s">
-        <v>912</v>
+        <v>917</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>913</v>
+        <v>918</v>
       </c>
       <c r="B313" t="s">
-        <v>914</v>
+        <v>919</v>
       </c>
       <c r="C313" t="s">
-        <v>915</v>
+        <v>920</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>916</v>
+        <v>921</v>
       </c>
       <c r="B314" t="s">
-        <v>917</v>
+        <v>922</v>
       </c>
       <c r="C314" t="s">
-        <v>918</v>
+        <v>923</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>919</v>
+        <v>924</v>
       </c>
       <c r="B315" t="s">
-        <v>920</v>
+        <v>925</v>
       </c>
       <c r="C315" t="s">
-        <v>921</v>
+        <v>926</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>922</v>
+        <v>927</v>
       </c>
       <c r="B316" t="s">
-        <v>920</v>
+        <v>925</v>
       </c>
       <c r="C316" t="s">
-        <v>921</v>
+        <v>926</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>923</v>
+        <v>928</v>
       </c>
       <c r="B317" t="s">
-        <v>924</v>
+        <v>929</v>
       </c>
       <c r="C317" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="B318" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="C318" t="s">
-        <v>928</v>
+        <v>933</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>929</v>
+        <v>934</v>
       </c>
       <c r="B319" t="s">
-        <v>930</v>
+        <v>935</v>
       </c>
       <c r="C319" t="s">
-        <v>931</v>
+        <v>936</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>932</v>
+        <v>937</v>
       </c>
       <c r="B320" t="s">
-        <v>933</v>
+        <v>938</v>
       </c>
       <c r="C320" t="s">
-        <v>934</v>
+        <v>939</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>935</v>
+        <v>940</v>
       </c>
       <c r="B321" t="s">
-        <v>936</v>
+        <v>941</v>
       </c>
       <c r="C321" t="s">
-        <v>937</v>
+        <v>942</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>938</v>
+        <v>943</v>
       </c>
       <c r="B322" t="s">
-        <v>939</v>
+        <v>944</v>
       </c>
       <c r="C322" t="s">
-        <v>940</v>
+        <v>945</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>941</v>
+        <v>946</v>
       </c>
       <c r="B323" t="s">
-        <v>942</v>
+        <v>947</v>
       </c>
       <c r="C323" t="s">
-        <v>943</v>
+        <v>948</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>944</v>
+        <v>949</v>
       </c>
       <c r="B324" t="s">
-        <v>945</v>
+        <v>950</v>
       </c>
       <c r="C324" t="s">
-        <v>946</v>
+        <v>951</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>947</v>
+        <v>952</v>
       </c>
       <c r="B325" t="s">
-        <v>948</v>
+        <v>953</v>
       </c>
       <c r="C325" t="s">
-        <v>949</v>
+        <v>954</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>950</v>
+        <v>955</v>
       </c>
       <c r="B326" t="s">
-        <v>951</v>
+        <v>956</v>
       </c>
       <c r="C326" t="s">
-        <v>952</v>
+        <v>957</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>953</v>
+        <v>958</v>
       </c>
       <c r="B327" t="s">
-        <v>954</v>
+        <v>959</v>
       </c>
       <c r="C327" t="s">
-        <v>955</v>
+        <v>960</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>956</v>
+        <v>961</v>
       </c>
       <c r="B328" t="s">
-        <v>957</v>
+        <v>962</v>
       </c>
       <c r="C328" t="s">
-        <v>958</v>
+        <v>963</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>959</v>
+        <v>964</v>
       </c>
       <c r="B329" t="s">
-        <v>960</v>
+        <v>965</v>
       </c>
       <c r="C329" t="s">
-        <v>961</v>
+        <v>966</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>962</v>
+        <v>967</v>
       </c>
       <c r="B330" t="s">
-        <v>963</v>
+        <v>968</v>
       </c>
       <c r="C330" t="s">
-        <v>964</v>
+        <v>969</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>965</v>
+        <v>970</v>
       </c>
       <c r="B331" t="s">
-        <v>966</v>
+        <v>971</v>
       </c>
       <c r="C331" t="s">
-        <v>967</v>
+        <v>972</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>968</v>
+        <v>973</v>
       </c>
       <c r="B332" t="s">
-        <v>969</v>
+        <v>974</v>
       </c>
       <c r="C332" t="s">
-        <v>970</v>
+        <v>975</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>971</v>
+        <v>976</v>
       </c>
       <c r="B333" t="s">
-        <v>972</v>
+        <v>977</v>
       </c>
       <c r="C333" t="s">
-        <v>973</v>
+        <v>978</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>974</v>
+        <v>979</v>
       </c>
       <c r="B334" t="s">
-        <v>975</v>
+        <v>980</v>
       </c>
       <c r="C334" t="s">
-        <v>976</v>
+        <v>981</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>977</v>
+        <v>982</v>
       </c>
       <c r="B335" t="s">
-        <v>978</v>
+        <v>983</v>
       </c>
       <c r="C335" t="s">
-        <v>979</v>
+        <v>984</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>980</v>
+        <v>985</v>
       </c>
       <c r="B336" t="s">
-        <v>981</v>
+        <v>986</v>
       </c>
       <c r="C336" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>983</v>
+        <v>988</v>
       </c>
       <c r="B337" t="s">
-        <v>984</v>
+        <v>989</v>
       </c>
       <c r="C337" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="B338" t="s">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="C338" t="s">
-        <v>988</v>
+        <v>993</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>989</v>
+        <v>994</v>
       </c>
       <c r="B339" t="s">
-        <v>990</v>
+        <v>995</v>
       </c>
       <c r="C339" t="s">
-        <v>991</v>
+        <v>996</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B340" t="s">
-        <v>993</v>
+        <v>998</v>
       </c>
       <c r="C340" t="s">
-        <v>994</v>
+        <v>999</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>995</v>
+        <v>1000</v>
       </c>
       <c r="B341" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="C341" t="s">
-        <v>997</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>998</v>
+        <v>1003</v>
       </c>
       <c r="B342" t="s">
-        <v>999</v>
+        <v>1004</v>
       </c>
       <c r="C342" t="s">
-        <v>1000</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>1001</v>
+        <v>1006</v>
       </c>
       <c r="B343" t="s">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="C343" t="s">
-        <v>1003</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>1004</v>
+        <v>1009</v>
       </c>
       <c r="B344" t="s">
-        <v>1005</v>
+        <v>1010</v>
       </c>
       <c r="C344" t="s">
-        <v>1006</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>1007</v>
+        <v>1012</v>
       </c>
       <c r="B345">
         <v>0</v>
       </c>
       <c r="C345" t="s">
-        <v>1008</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>1009</v>
+        <v>1014</v>
       </c>
       <c r="B346" t="s">
-        <v>1010</v>
+        <v>1015</v>
       </c>
       <c r="C346" t="s">
-        <v>1011</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="B347" t="s">
-        <v>1013</v>
+        <v>1018</v>
       </c>
       <c r="C347" t="s">
-        <v>1014</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
       <c r="B348" t="s">
-        <v>1016</v>
+        <v>1021</v>
       </c>
       <c r="C348" t="s">
-        <v>1017</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>1018</v>
+        <v>1023</v>
       </c>
       <c r="B349" t="s">
-        <v>1019</v>
+        <v>1024</v>
       </c>
       <c r="C349" t="s">
-        <v>1020</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>1021</v>
+        <v>1026</v>
       </c>
       <c r="B350" t="s">
-        <v>1022</v>
+        <v>1027</v>
       </c>
       <c r="C350" t="s">
-        <v>1023</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>1024</v>
+        <v>1029</v>
       </c>
       <c r="B351" t="s">
-        <v>1025</v>
+        <v>1030</v>
       </c>
       <c r="C351" t="s">
-        <v>1026</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>1027</v>
+        <v>1032</v>
       </c>
       <c r="B352" t="s">
-        <v>1028</v>
+        <v>1033</v>
       </c>
       <c r="C352" t="s">
-        <v>1029</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>1030</v>
+        <v>1035</v>
       </c>
       <c r="B353" t="s">
-        <v>1031</v>
+        <v>1036</v>
       </c>
       <c r="C353" t="s">
-        <v>1032</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>1033</v>
+        <v>1038</v>
       </c>
       <c r="B354" t="s">
-        <v>1034</v>
+        <v>1039</v>
       </c>
       <c r="C354" t="s">
-        <v>1035</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>1036</v>
+        <v>1041</v>
       </c>
       <c r="B355" t="s">
-        <v>1037</v>
+        <v>1042</v>
       </c>
       <c r="C355" t="s">
-        <v>1035</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>1038</v>
+        <v>1043</v>
       </c>
       <c r="B356" t="s">
-        <v>1039</v>
+        <v>1044</v>
       </c>
       <c r="C356" t="s">
-        <v>1035</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B357" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C357" t="s">
         <v>1040</v>
-      </c>
-      <c r="B357" t="s">
-        <v>1041</v>
-      </c>
-      <c r="C357" t="s">
-        <v>1035</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>1042</v>
+        <v>1047</v>
       </c>
       <c r="B358" t="s">
-        <v>1043</v>
+        <v>1048</v>
       </c>
       <c r="C358" t="s">
-        <v>1035</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>1044</v>
+        <v>1049</v>
       </c>
       <c r="B359" t="s">
-        <v>1045</v>
+        <v>1050</v>
       </c>
       <c r="C359" t="s">
-        <v>1035</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>1046</v>
+        <v>1051</v>
       </c>
       <c r="B360" t="s">
-        <v>1047</v>
+        <v>1052</v>
       </c>
       <c r="C360" t="s">
-        <v>1035</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="B361" t="s">
-        <v>1049</v>
+        <v>1054</v>
       </c>
       <c r="C361" t="s">
-        <v>1035</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>1050</v>
+        <v>1055</v>
       </c>
       <c r="B362" t="s">
-        <v>1051</v>
+        <v>1056</v>
       </c>
       <c r="C362" t="s">
-        <v>1035</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>1052</v>
+        <v>1057</v>
       </c>
       <c r="B363" t="s">
-        <v>1053</v>
+        <v>1058</v>
       </c>
       <c r="C363" t="s">
-        <v>1035</v>
+        <v>1040</v>
       </c>
     </row>
   </sheetData>

--- a/Plan/Table/TestData/00.LocaleData.xlsx
+++ b/Plan/Table/TestData/00.LocaleData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\인디\FluffyDisdog\Plan\Table\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F18C48D0-82D5-4E2C-BAB4-94802AEB544A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F7BBC251-4AAD-41B7-A16B-00B66907D974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{0D94B96B-AFBA-4F5C-A2F9-89D9A5E8125A}"/>
+    <workbookView xWindow="-28920" yWindow="5280" windowWidth="29040" windowHeight="15720" xr2:uid="{573C7557-5C36-423B-A838-0F9F5090E712}"/>
   </bookViews>
   <sheets>
     <sheet name="00.LocaleData" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="1059">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="1054">
   <si>
     <t>key</t>
   </si>
@@ -881,7 +881,7 @@
     <t>Card_Shovel_Des</t>
   </si>
   <si>
-    <t>노란색 타격범위에 타일을 100% 확률로 파괴합니다.\\n(도구) 카드를 사용하면 카드가 파괴될 수 있습니다.\\n카드 강화시 카드 파괴 효과는 사라집니다.</t>
+    <t>&lt;#fbc531&gt; ■&lt;/color&gt; 100% 파괴</t>
   </si>
   <si>
     <t>Destroys tiles in the yellow attack range with 100% chance.\\n(Tool) This card may be destroyed upon use.\\nUpgrading this card removes the destruction effect.</t>
@@ -890,7 +890,7 @@
     <t>Card_Rake_Des</t>
   </si>
   <si>
-    <t>노란색 타격범위에 타일을 100% 확률로 파괴합니다.\\n흰색 타격 범위에 타일을 66% 확률로 파괴합니다.\\n(도구) 카드를 사용하면 카드가 파괴될 수 있습니다.\\n카드 강화시 카드 파괴 효과는 사라집니다.</t>
+    <t>&lt;#fbc531&gt; ■&lt;/color&gt; 100% 파괴&lt;br&gt;&lt;#efefe9&gt; ■&lt;/color&gt; 66% 파괴</t>
   </si>
   <si>
     <t>Destroys tiles in the yellow attack range with 100% chance.\\nDestroys tiles in the white attack range with 66% chance.\\n(Tool) This card may be destroyed upon use.\\nUpgrading this card removes the destruction effect.</t>
@@ -899,16 +899,13 @@
     <t>Card_Shovel_Enhanced_Des</t>
   </si>
   <si>
-    <t>노란색 타격범위에 타일을 100% 확률로 파괴합니다.\\n(강화) 방해 블록을 무시하고 파괴합니다.</t>
-  </si>
-  <si>
     <t>Destroys tiles in the yellow attack range with 100% chance.\\n(Enhanced) Destroys tiles ignoring obstacle blocks.</t>
   </si>
   <si>
     <t>Card_Rake_Enhanced_Des</t>
   </si>
   <si>
-    <t>노란색과 흰색 타격범위에 타일을 100% 확률로 파괴합니다.</t>
+    <t>&lt;#fbc531&gt; ■&lt;/color&gt;&lt;#efefe9&gt; ■&lt;/color&gt; 100% 파괴</t>
   </si>
   <si>
     <t>Destroys tiles in both yellow and white attack ranges with 100% chance.</t>
@@ -917,31 +914,28 @@
     <t>Card_GoldenShovel_Des</t>
   </si>
   <si>
-    <t>노란색 타격범위에 타일을 100% 확률로 파괴합니다.\\n(도구) 카드를 사용하면 카드가 파괴될 수 있습니다.\\n(황금) 카드 사용시 1골드를 획득합니다.</t>
-  </si>
-  <si>
     <t>Destroys tiles in the yellow attack range with 100% chance.\\n(Tool) This card may be destroyed upon use.\\n(Golden) Grants 1 Gold upon use.</t>
   </si>
   <si>
     <t>Card_GoldenShovel_Enhanced_Des</t>
   </si>
   <si>
-    <t>노란색 타격범위에 타일을 100% 확률로 파괴합니다.\\n(황금) 카드 사용시 1골드를 획득합니다.</t>
-  </si>
-  <si>
     <t>Destroys tiles in the yellow attack range with 100% chance.\\n(Golden) Grants 1 Gold upon use.</t>
   </si>
   <si>
     <t>Card_Axe_Des</t>
   </si>
   <si>
+    <t>&lt;#fbc531&gt; ■&lt;/color&gt; 100% 파괴 &lt;br&gt;&lt;#efefe9&gt; ■&lt;/color&gt; 66% 파괴</t>
+  </si>
+  <si>
     <t>Card_Axe_Enhanced_Des</t>
   </si>
   <si>
     <t>Card_Cross_Chisel_Des</t>
   </si>
   <si>
-    <t>노란색 타격범위에 타일을 100% 확률로 파괴합니다.\\n흰색 타격 범위에 타일을 50% 확률로 파괴합니다.\\n(도구) 카드를 사용하면 카드가 파괴될 수 있습니다.\\n카드 강화시 카드 파괴 효과는 사라집니다.</t>
+    <t>&lt;#fbc531&gt; ■&lt;/color&gt; 100% 파괴 &lt;br&gt;&lt;#efefe9&gt; ■&lt;/color&gt; 50% 파괴</t>
   </si>
   <si>
     <t>Destroys tiles in the yellow attack range with 100% chance.\\nDestroys tiles in the white attack range with 50% chance.\\n(Tool) This card may be destroyed upon use.\\nUpgrading this card removes the destruction effect.</t>
@@ -950,7 +944,7 @@
     <t>Card_Cross_Chisel_Enhanced_Des</t>
   </si>
   <si>
-    <t>노란색 타격범위에 타일을 100% 확률로 파괴합니다.\\n흰색 타격 범위에 타일을 75% 확률로 파괴합니다.</t>
+    <t>&lt;#fbc531&gt; ■&lt;/color&gt; 100% 파괴 &lt;br&gt;&lt;#efefe9&gt; ■&lt;/color&gt; 75% 파괴</t>
   </si>
   <si>
     <t>Destroys tiles in the yellow attack range with 100% chance.\\nDestroys tiles in the white attack range with 75% chance.</t>
@@ -965,7 +959,7 @@
     <t>Card_Slingshot_Des</t>
   </si>
   <si>
-    <t>카드 사용시 랜덤한 일반 타일을 5군데 타격합니다.\\n타격시 33% 확률로 타일이 파괴됩니다.\\n(도구) 카드를 사용하면 카드가 파괴될 수 있습니다.</t>
+    <t xml:space="preserve"> 무작위 타일 5개&lt;br&gt; 33% 파괴</t>
   </si>
   <si>
     <t>Strikes 5 random normal tiles upon use.\\nEach strike has a 33% chance to destroy the tile.\\n(Tool) This card may be destroyed upon use.</t>
@@ -974,7 +968,7 @@
     <t>Card_Slingshot_Enhanced_Des</t>
   </si>
   <si>
-    <t>카드 사용시 랜덤한 일반 타일을 7군데 타격합니다.\\n타격시 50% 확률로 타일이 파괴됩니다.</t>
+    <t xml:space="preserve"> 무작위 타일 7개&lt;br&gt; 50% 파괴</t>
   </si>
   <si>
     <t>Strikes 7 random normal tiles upon use.\\nEach strike has a 50% chance to destroy the tile.</t>
@@ -983,7 +977,7 @@
     <t>Card_CornerCrushingHammer_Des</t>
   </si>
   <si>
-    <t>노란색 타격범위에 타일을 100% 확률로 파괴합니다.\\n노란색을 기준으로 상하좌우에 있는 흰색 타격 범위에 타일을 66% 확률로 파괴합니다.\\n노란색을 기준으로 대각선에 있는 흰색 타격 범위에 타일을 33% 확률로 파괴합니다.\\n(도구) 카드를 사용하면 카드가 파괴될 수 있습니다.\\n카드 강화시 카드 파괴 효과는 사라집니다.</t>
+    <t>&lt;#fbc531&gt; ■&lt;/color&gt; 100% 파괴 &lt;br&gt;&lt;#efefe9&gt; ■ ←↑↓→&lt;/color&gt; 66% 파괴&lt;br&gt;&lt;#efefe9&gt; ■ ↖↗↙↘&lt;/color&gt; 33% 파괴</t>
   </si>
   <si>
     <t>Destroys tiles in the yellow attack range with 100% chance.\\nDestroys tiles in the white attack range adjacent to the yellow tile with 66% chance.\\nDestroys tiles in the white attack range diagonal to the yellow tile with 33% chance.\\n(Tool) This card may be destroyed upon use.\\nUpgrading this card removes the destruction effect.</t>
@@ -992,7 +986,7 @@
     <t>Card_CornerCrushingHammer_Enhanced_Des</t>
   </si>
   <si>
-    <t>노란색 타격범위에 타일을 100% 확률로 파괴합니다.\\n노란색을 기준으로 상하좌우에 있는 흰색 타격 범위에 타일을 75% 확률로 파괴합니다.\\n노란색을 기준으로 대각선에 있는 흰색 타격 범위에 타일을 50% 확률로 파괴합니다.</t>
+    <t>&lt;#fbc531&gt; ■&lt;/color&gt; 100% 파괴 &lt;br&gt;&lt;#efefe9&gt; ■ ←↑↓→&lt;/color&gt; 75% 파괴&lt;br&gt;&lt;#efefe9&gt; ■ ↖↗↙↘&lt;/color&gt; 50% 파괴</t>
   </si>
   <si>
     <t>Destroys tiles in the yellow attack range with 100% chance.\\nDestroys tiles in the white attack range adjacent to the yellow tile with 75% chance.\\nDestroys tiles in the white attack range diagonal to the yellow tile with 50% chance.</t>
@@ -1001,7 +995,7 @@
     <t>Card_ConcentratedCrossDrill_Des</t>
   </si>
   <si>
-    <t>노란색 타격범위에 타일을 100% 확률로 파괴합니다.\\n노란색을 기준으로 대각선에 있는 흰색 타격 범위에 타일을 66% 확률로 파괴합니다.\\n노란색을 기준으로 상하좌우에 있는 흰색 타격 범위에 타일을 33% 확률로 파괴합니다.\\n(도구) 카드를 사용하면 카드가 파괴될 수 있습니다.\\n카드 강화시 카드 파괴 효과는 사라집니다.</t>
+    <t>&lt;#fbc531&gt; ■&lt;/color&gt; 100% 파괴 &lt;br&gt;&lt;#efefe9&gt; ■ ↖↗↙↘&lt;/color&gt; 33% 파괴&lt;br&gt;&lt;#efefe9&gt; ■ ←↑↓→&lt;/color&gt; 66% 파괴</t>
   </si>
   <si>
     <t>Destroys tiles in the yellow attack range with 100% chance.\\nDestroys tiles in the white attack range diagonal to the yellow tile with 66% chance.\\nDestroys tiles in the white attack range adjacent to the yellow tile with 33% chance.\\n(Tool) This card may be destroyed upon use.\\nUpgrading this card removes the destruction effect.</t>
@@ -1010,7 +1004,7 @@
     <t>Card_ConcentratedCrossDrill_Enhanced_Des</t>
   </si>
   <si>
-    <t>노란색 타격범위에 타일을 100% 확률로 파괴합니다.\\n노란색을 기준으로 대각선에 있는 흰색 타격 범위에 타일을 75% 확률로 파괴합니다.\\n노란색을 기준으로 상하좌우에 있는 흰색 타격 범위에 타일을 50% 확률로 파괴합니다.</t>
+    <t>&lt;#fbc531&gt; ■&lt;/color&gt; 100% 파괴 &lt;br&gt;&lt;#efefe9&gt; ■ ↖↗↙↘&lt;/color&gt; 75% 파괴&lt;br&gt;&lt;#efefe9&gt; ■ ←↑↓→&lt;/color&gt; 50% 파괴</t>
   </si>
   <si>
     <t>Destroys tiles in the yellow attack range with 100% chance.\\nDestroys tiles in the white attack range diagonal to the yellow tile with 75% chance.\\nDestroys tiles in the white attack range adjacent to the yellow tile with 50% chance.</t>
@@ -1019,27 +1013,18 @@
     <t>Card_GoldenAxe_Des</t>
   </si>
   <si>
-    <t>노란색 타격범위에 타일을 100% 확률로 파괴합니다.\\n흰색 타격 범위에 타일을 66% 확률로 파괴합니다.\\n(도구) 카드를 사용하면 카드가 파괴될 수 있습니다.\\n(황금) 카드 사용시 1골드를 획득합니다.</t>
-  </si>
-  <si>
     <t>Destroys tiles in the yellow attack range with 100% chance.\\nDestroys tiles in the white attack range with 66% chance.\\n(Tool) This card may be destroyed upon use.\\n(Golden) Grants 1 Gold upon use.</t>
   </si>
   <si>
     <t>Card_GoldenAxe_Enhanced_Des</t>
   </si>
   <si>
-    <t>노란색과 흰색 타격범위에 타일을 100% 확률로 파괴합니다.\\n(황금) 카드 사용시 1골드를 획득합니다.</t>
-  </si>
-  <si>
     <t>Destroys tiles in both yellow and white attack ranges with 100% chance.\\n(Golden) Grants 1 Gold upon use.</t>
   </si>
   <si>
     <t>Card_Large_Scissors_Des</t>
   </si>
   <si>
-    <t>노란색 타격범위에 타일을 100% 확률로 파괴합니다.\\n흰색 타격 범위에 타일을 75% 확률로 파괴합니다.\\n(도구) 카드를 사용하면 카드가 파괴될 수 있습니다.\\n카드 강화시 카드 파괴 효과는 사라집니다.</t>
-  </si>
-  <si>
     <t>Destroys tiles in the yellow attack range with 100% chance.\\nDestroys tiles in the white attack range with 75% chance.\\n(Tool) This card may be destroyed upon use.\\nUpgrading this card removes the destruction effect.</t>
   </si>
   <si>
@@ -1049,7 +1034,7 @@
     <t>Card_WeakeningNormal_Des</t>
   </si>
   <si>
-    <t>노란색과 하늘색 타격범위에 일반 타일을 100% 확률로 균열 상태로 만듭니다.\\n균열된 타일은 다음 턴에 타격 시 타격 확률을 무시하고 파괴됩니다.</t>
+    <t>&lt;#fbc531&gt; ■&lt;/color&gt; 100% 균열 부여</t>
   </si>
   <si>
     <t>Inflicts Cracked status on normal tiles in the yellow and sky-blue attack ranges with 100% chance.\\nCracked tiles are destroyed on the next turn when struck, ignoring hit chance.</t>
@@ -1058,6 +1043,9 @@
     <t>Card_WeakeningRare_Des</t>
   </si>
   <si>
+    <t>&lt;#fbc531&gt; ■&lt;/color&gt;&lt;#49e3da&gt; ■&lt;/color&gt; 100% 균열 부여</t>
+  </si>
+  <si>
     <t>Card_WeakeningUnique_Des</t>
   </si>
   <si>
@@ -1133,16 +1121,13 @@
     <t>Card_RiftStartumAnalysis_Des</t>
   </si>
   <si>
-    <t>노란색 타격범위에 타일을 100% 확률로 파괴합니다.\\n흰색 타격 범위에 타일을 0% 확률로 파괴할 수 있다.\\n이 카드로 타일을 3개 이상 부술 경우, 타격 범위에 있는 모든 일반 타일을 파괴합니다.\\n파괴된 타일 중 균열 타일 1개당 2 Gold를 지급합니다.\\n이 카드로 타일을 5칸 부술 경우 덱에 존재하는 황금 태그 카드 1장을 드로우합니다.\\n(도구) 카드를 사용하면 카드가 파괴될 수 있습니다.\\n카드 강화시 카드 파괴 효과는 사라집니다.</t>
+    <t>&lt;#fbc531&gt; ■&lt;/color&gt; 100% 파괴 &lt;br&gt;&lt;#efefe9&gt; ■&lt;/color&gt; 0% 파괴</t>
   </si>
   <si>
     <t>Destroys tiles in the yellow attack range with 100% chance.\\nTiles in the white attack range cannot be destroyed.\\nIf 3 or more tiles are destroyed with this card, all normal tiles in the attack range are destroyed.\\nGrants 2 Gold for each Cracked tile destroyed.\\nIf 5 tiles are destroyed with this card, draw 1 Golden-tag card from your deck.\\n(Tool) This card may be destroyed upon use.\\nUpgrading this card removes the destruction effect.</t>
   </si>
   <si>
     <t>Card_RiftStartumAnalysis_Enhanced_Des</t>
-  </si>
-  <si>
-    <t>노란색 타격범위에 타일을 100% 확률로 파괴합니다.\\n흰색 타격 범위에 타일을 0% 확률로 파괴할 수 있다.\\n이 카드로 타일을 3개 이상 부술 경우, 타격 범위에 있는 모든 일반 타일을 파괴합니다.\\n파괴된 타일 중 균열 타일 1개당 5 Gold를 지급합니다.\\n이 카드로 타일을 5칸 부술 경우 덱에 존재하는 황금 태그 카드 2장을 드로우합니다.</t>
   </si>
   <si>
     <t>Destroys tiles in the yellow attack range with 100% chance.\\nTiles in the white attack range cannot be destroyed.\\nIf 3 or more tiles are destroyed with this card, all normal tiles in the attack range are destroyed.\\nGrants 5 Gold for each Cracked tile destroyed.\\nIf 5 tiles are destroyed with this card, draw 2 Golden-tag cards from your deck.</t>
@@ -3598,7 +3583,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{527CDD1D-BA3C-4FC2-974E-432ACF109AEC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7174173E-B864-4D1E-B610-1C2C91A5960A}">
   <dimension ref="A1:C363"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -4652,51 +4637,51 @@
         <v>285</v>
       </c>
       <c r="B96" t="s">
+        <v>280</v>
+      </c>
+      <c r="C96" t="s">
         <v>286</v>
-      </c>
-      <c r="C96" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
+        <v>287</v>
+      </c>
+      <c r="B97" t="s">
         <v>288</v>
       </c>
-      <c r="B97" t="s">
+      <c r="C97" t="s">
         <v>289</v>
-      </c>
-      <c r="C97" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
+        <v>290</v>
+      </c>
+      <c r="B98" t="s">
+        <v>280</v>
+      </c>
+      <c r="C98" t="s">
         <v>291</v>
-      </c>
-      <c r="B98" t="s">
-        <v>292</v>
-      </c>
-      <c r="C98" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B99" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="C99" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B100" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="C100" t="s">
         <v>284</v>
@@ -4704,2895 +4689,2895 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B101" t="s">
+        <v>288</v>
+      </c>
+      <c r="C101" t="s">
         <v>289</v>
-      </c>
-      <c r="C101" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
+        <v>297</v>
+      </c>
+      <c r="B102" t="s">
+        <v>298</v>
+      </c>
+      <c r="C102" t="s">
         <v>299</v>
-      </c>
-      <c r="B102" t="s">
-        <v>300</v>
-      </c>
-      <c r="C102" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
+        <v>300</v>
+      </c>
+      <c r="B103" t="s">
+        <v>301</v>
+      </c>
+      <c r="C103" t="s">
         <v>302</v>
-      </c>
-      <c r="B103" t="s">
-        <v>303</v>
-      </c>
-      <c r="C103" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B104" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C104" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B105" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C105" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
+        <v>305</v>
+      </c>
+      <c r="B106" t="s">
+        <v>306</v>
+      </c>
+      <c r="C106" t="s">
         <v>307</v>
-      </c>
-      <c r="B106" t="s">
-        <v>308</v>
-      </c>
-      <c r="C106" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
+        <v>308</v>
+      </c>
+      <c r="B107" t="s">
+        <v>309</v>
+      </c>
+      <c r="C107" t="s">
         <v>310</v>
-      </c>
-      <c r="B107" t="s">
-        <v>311</v>
-      </c>
-      <c r="C107" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
+        <v>311</v>
+      </c>
+      <c r="B108" t="s">
+        <v>312</v>
+      </c>
+      <c r="C108" t="s">
         <v>313</v>
-      </c>
-      <c r="B108" t="s">
-        <v>314</v>
-      </c>
-      <c r="C108" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
+        <v>314</v>
+      </c>
+      <c r="B109" t="s">
+        <v>315</v>
+      </c>
+      <c r="C109" t="s">
         <v>316</v>
-      </c>
-      <c r="B109" t="s">
-        <v>317</v>
-      </c>
-      <c r="C109" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
+        <v>317</v>
+      </c>
+      <c r="B110" t="s">
+        <v>318</v>
+      </c>
+      <c r="C110" t="s">
         <v>319</v>
-      </c>
-      <c r="B110" t="s">
-        <v>320</v>
-      </c>
-      <c r="C110" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
+        <v>320</v>
+      </c>
+      <c r="B111" t="s">
+        <v>321</v>
+      </c>
+      <c r="C111" t="s">
         <v>322</v>
-      </c>
-      <c r="B111" t="s">
-        <v>323</v>
-      </c>
-      <c r="C111" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B112" t="s">
-        <v>326</v>
+        <v>295</v>
       </c>
       <c r="C112" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B113" t="s">
-        <v>329</v>
+        <v>288</v>
       </c>
       <c r="C113" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B114" t="s">
-        <v>332</v>
+        <v>301</v>
       </c>
       <c r="C114" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="B115" t="s">
+        <v>288</v>
+      </c>
+      <c r="C115" t="s">
         <v>289</v>
-      </c>
-      <c r="C115" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="B116" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C116" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="B117" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C117" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B118" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C118" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="B119" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C119" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B120" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C120" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="B121" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C121" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B122" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C122" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B123" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="C123" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="B124" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="C124" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="B125" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="C125" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="B126" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C126" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B127" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C127" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="B128" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="C128" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="B129" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="C129" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="B130" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C130" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="B131" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C131" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="B132" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="C132" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="B133" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="C133" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="B134" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="C134" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="B135" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C135" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="B136" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="C136" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="B137" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="C137" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="B138" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="C138" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="B139" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="C139" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="B140" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C140" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="B141" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="C141" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B142" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="C142" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="B143" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="C143" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="B144" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="C144" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B145" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="C145" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="B146" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="C146" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="B147" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="C147" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="B148" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="C148" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="B149" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="C149" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="B150" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="C150" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="B151" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="C151" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="B152" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="C152" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="B153" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C153" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="B154" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="C154" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="B155" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="C155" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="B156" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="C156" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="B157" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="C157" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="B158" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="C158" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="B159" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="C159" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B160" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C160" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="B161" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="C161" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="B162" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="C162" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="B163" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="C163" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="B164" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="C164" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="B165" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="C165" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="B166" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="C166" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="B167" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="C167" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B168" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C168" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="B169" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="C169" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="B170" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="C170" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="B171" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="C171" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="B172" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="C172" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="B173" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="C173" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="B174" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="C174" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="B175" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="C175" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="B176" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="C176" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="B177" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="C177" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="B178" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="C178" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="B179" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="C179" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="B180" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="C180" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="B181" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="C181" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="B182" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="C182" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="B183" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="C183" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="B184" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="C184" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="B185" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="C185" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="B186" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="C186" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="B187" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="C187" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="B188" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="C188" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="B189" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="C189" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="B190" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="C190" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="B191" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="C191" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="B192" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="C192" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="B193" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="C193" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="B194" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="C194" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="B195" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="C195" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="B196" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="C196" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="B197" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="C197" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="B198" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="C198" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="B199" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="C199" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="B200" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C200" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="B201" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="C201" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="B202" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="C202" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="B203" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="C203" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="B204" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="C204" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="B205" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="C205" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="B206" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="C206" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="B207" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="C207" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="B208" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="C208" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="B209" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="C209" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="B210" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="C210" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="B211" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="C211" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="B212" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="C212" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="B213" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="C213" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="B214" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="C214" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="B215" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="C215" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="B216" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="C216" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="B217" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="C217" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="B218" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="C218" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="B219" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="C219" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="B220" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="C220" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="B221" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="C221" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="B222" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="C222" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="B223" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="C223" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="B224" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="C224" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="B225" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="C225" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="B226" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="C226" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="B227" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="C227" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="B228" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="C228" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="B229" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="C229" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="B230" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="C230" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="B231" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="C231" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B232" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="C232" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="B233" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="C233" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="B234" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="C234" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="B235" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="C235" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="B236" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="C236" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="B237" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="C237" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="B238" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
       <c r="C238" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="B239" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
       <c r="C239" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="B240" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="C240" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="B241" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="C241" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="B242" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="C242" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="B243" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="C243" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="B244" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="C244" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="B245" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="C245" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="B246" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="C246" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="B247" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="C247" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="B248" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="C248" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="B249" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="C249" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="B250" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="C250" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="B251" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="C251" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="B252" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="C252" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="B253" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="C253" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="B254" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="C254" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="B255" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="C255" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="B256" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="C256" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="B257" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="C257" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="B258" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="C258" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="B259" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="C259" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="B260" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="C260" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="B261" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="C261" t="s">
-        <v>770</v>
+        <v>765</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="B262" t="s">
-        <v>772</v>
+        <v>767</v>
       </c>
       <c r="C262" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="B263" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="C263" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="B264" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="C264" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="B265" t="s">
-        <v>781</v>
+        <v>776</v>
       </c>
       <c r="C265" t="s">
-        <v>782</v>
+        <v>777</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>783</v>
+        <v>778</v>
       </c>
       <c r="B266" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="C266" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="B267" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="C267" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="B268" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="C268" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="B269" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="C269" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="B270" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="C270" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="B271" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="C271" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="B272" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="C272" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="B273" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="C273" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="B274" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
       <c r="C274" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="B275" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="C275" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="B276" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="C276" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="B277" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="C277" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="B278" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="C278" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="B279" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="C279" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="B280" t="s">
-        <v>826</v>
+        <v>821</v>
       </c>
       <c r="C280" t="s">
-        <v>827</v>
+        <v>822</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="B281" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
       <c r="C281" t="s">
-        <v>830</v>
+        <v>825</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="B282" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="C282" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="B283" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="C283" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="B284" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
       <c r="C284" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="B285" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="C285" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>843</v>
+        <v>838</v>
       </c>
       <c r="B286" t="s">
-        <v>844</v>
+        <v>839</v>
       </c>
       <c r="C286" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="B287" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="C287" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="B288" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="C288" t="s">
-        <v>851</v>
+        <v>846</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="B289" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="C289" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="B290" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="C290" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="B291" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="C291" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="B292" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="C292" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="B293" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="C293" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="B294" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="C294" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="B295" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="C295" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="B296" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="C296" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="B297" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="C297" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="B298" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="C298" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="B299" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="C299" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="B300" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="C300" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="B301" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="C301" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="B302" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="C302" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="B303" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="C303" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
       <c r="B304" t="s">
-        <v>892</v>
+        <v>887</v>
       </c>
       <c r="C304" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="B305" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="C305" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>897</v>
+        <v>892</v>
       </c>
       <c r="B306" t="s">
-        <v>898</v>
+        <v>893</v>
       </c>
       <c r="C306" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="B307" t="s">
-        <v>901</v>
+        <v>896</v>
       </c>
       <c r="C307" t="s">
-        <v>902</v>
+        <v>897</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="B308" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="C308" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="B309" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="C309" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="B310" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="C310" t="s">
-        <v>911</v>
+        <v>906</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="B311" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="C311" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
       <c r="B312" t="s">
-        <v>916</v>
+        <v>911</v>
       </c>
       <c r="C312" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
       <c r="B313" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
       <c r="C313" t="s">
-        <v>920</v>
+        <v>915</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="B314" t="s">
-        <v>922</v>
+        <v>917</v>
       </c>
       <c r="C314" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>924</v>
+        <v>919</v>
       </c>
       <c r="B315" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="C315" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>927</v>
+        <v>922</v>
       </c>
       <c r="B316" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="C316" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>928</v>
+        <v>923</v>
       </c>
       <c r="B317" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="C317" t="s">
-        <v>930</v>
+        <v>925</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>931</v>
+        <v>926</v>
       </c>
       <c r="B318" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="C318" t="s">
-        <v>933</v>
+        <v>928</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="B319" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
       <c r="C319" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>937</v>
+        <v>932</v>
       </c>
       <c r="B320" t="s">
-        <v>938</v>
+        <v>933</v>
       </c>
       <c r="C320" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="B321" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="C321" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="B322" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
       <c r="C322" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="B323" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="C323" t="s">
-        <v>948</v>
+        <v>943</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="B324" t="s">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="C324" t="s">
-        <v>951</v>
+        <v>946</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="B325" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="C325" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="B326" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
       <c r="C326" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>958</v>
+        <v>953</v>
       </c>
       <c r="B327" t="s">
-        <v>959</v>
+        <v>954</v>
       </c>
       <c r="C327" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="B328" t="s">
-        <v>962</v>
+        <v>957</v>
       </c>
       <c r="C328" t="s">
-        <v>963</v>
+        <v>958</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>964</v>
+        <v>959</v>
       </c>
       <c r="B329" t="s">
-        <v>965</v>
+        <v>960</v>
       </c>
       <c r="C329" t="s">
-        <v>966</v>
+        <v>961</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>967</v>
+        <v>962</v>
       </c>
       <c r="B330" t="s">
-        <v>968</v>
+        <v>963</v>
       </c>
       <c r="C330" t="s">
-        <v>969</v>
+        <v>964</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>970</v>
+        <v>965</v>
       </c>
       <c r="B331" t="s">
-        <v>971</v>
+        <v>966</v>
       </c>
       <c r="C331" t="s">
-        <v>972</v>
+        <v>967</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>973</v>
+        <v>968</v>
       </c>
       <c r="B332" t="s">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="C332" t="s">
-        <v>975</v>
+        <v>970</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="B333" t="s">
-        <v>977</v>
+        <v>972</v>
       </c>
       <c r="C333" t="s">
-        <v>978</v>
+        <v>973</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>979</v>
+        <v>974</v>
       </c>
       <c r="B334" t="s">
-        <v>980</v>
+        <v>975</v>
       </c>
       <c r="C334" t="s">
-        <v>981</v>
+        <v>976</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>982</v>
+        <v>977</v>
       </c>
       <c r="B335" t="s">
-        <v>983</v>
+        <v>978</v>
       </c>
       <c r="C335" t="s">
-        <v>984</v>
+        <v>979</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>985</v>
+        <v>980</v>
       </c>
       <c r="B336" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="C336" t="s">
-        <v>987</v>
+        <v>982</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>988</v>
+        <v>983</v>
       </c>
       <c r="B337" t="s">
-        <v>989</v>
+        <v>984</v>
       </c>
       <c r="C337" t="s">
-        <v>990</v>
+        <v>985</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>991</v>
+        <v>986</v>
       </c>
       <c r="B338" t="s">
-        <v>992</v>
+        <v>987</v>
       </c>
       <c r="C338" t="s">
-        <v>993</v>
+        <v>988</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>994</v>
+        <v>989</v>
       </c>
       <c r="B339" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="C339" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B340" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
       <c r="C340" t="s">
-        <v>999</v>
+        <v>994</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>1000</v>
+        <v>995</v>
       </c>
       <c r="B341" t="s">
-        <v>1001</v>
+        <v>996</v>
       </c>
       <c r="C341" t="s">
-        <v>1002</v>
+        <v>997</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>1003</v>
+        <v>998</v>
       </c>
       <c r="B342" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="C342" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="B343" t="s">
-        <v>1007</v>
+        <v>1002</v>
       </c>
       <c r="C343" t="s">
-        <v>1008</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>1009</v>
+        <v>1004</v>
       </c>
       <c r="B344" t="s">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="C344" t="s">
-        <v>1011</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>1012</v>
+        <v>1007</v>
       </c>
       <c r="B345">
         <v>0</v>
       </c>
       <c r="C345" t="s">
-        <v>1013</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>1014</v>
+        <v>1009</v>
       </c>
       <c r="B346" t="s">
-        <v>1015</v>
+        <v>1010</v>
       </c>
       <c r="C346" t="s">
-        <v>1016</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>1017</v>
+        <v>1012</v>
       </c>
       <c r="B347" t="s">
-        <v>1018</v>
+        <v>1013</v>
       </c>
       <c r="C347" t="s">
-        <v>1019</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="B348" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="C348" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="B349" t="s">
-        <v>1024</v>
+        <v>1019</v>
       </c>
       <c r="C349" t="s">
-        <v>1025</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
       <c r="B350" t="s">
-        <v>1027</v>
+        <v>1022</v>
       </c>
       <c r="C350" t="s">
-        <v>1028</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="B351" t="s">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="C351" t="s">
-        <v>1031</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>1032</v>
+        <v>1027</v>
       </c>
       <c r="B352" t="s">
-        <v>1033</v>
+        <v>1028</v>
       </c>
       <c r="C352" t="s">
-        <v>1034</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="B353" t="s">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="C353" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="B354" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
       <c r="C354" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="B355" t="s">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="C355" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>1043</v>
+        <v>1038</v>
       </c>
       <c r="B356" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="C356" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>1045</v>
+        <v>1040</v>
       </c>
       <c r="B357" t="s">
-        <v>1046</v>
+        <v>1041</v>
       </c>
       <c r="C357" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>1047</v>
+        <v>1042</v>
       </c>
       <c r="B358" t="s">
-        <v>1048</v>
+        <v>1043</v>
       </c>
       <c r="C358" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>1049</v>
+        <v>1044</v>
       </c>
       <c r="B359" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="C359" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="B360" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
       <c r="C360" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
       <c r="B361" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="C361" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="B362" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
       <c r="C362" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="B363" t="s">
-        <v>1058</v>
+        <v>1053</v>
       </c>
       <c r="C363" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
     </row>
   </sheetData>

--- a/Plan/Table/TestData/00.LocaleData.xlsx
+++ b/Plan/Table/TestData/00.LocaleData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\인디\FluffyDisdog\Plan\Table\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F7BBC251-4AAD-41B7-A16B-00B66907D974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C94B2BC-9E38-4E0A-B5C2-2C69EF3E0336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="5280" windowWidth="29040" windowHeight="15720" xr2:uid="{573C7557-5C36-423B-A838-0F9F5090E712}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{ACC90571-B6CD-4C5D-8958-9053FB4EA2D7}"/>
   </bookViews>
   <sheets>
     <sheet name="00.LocaleData" sheetId="1" r:id="rId1"/>
@@ -3583,7 +3583,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7174173E-B864-4D1E-B610-1C2C91A5960A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E2C2F42-74FE-4D83-8AC1-7B5D5D77C5DD}">
   <dimension ref="A1:C363"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>

--- a/Plan/Table/TestData/00.LocaleData.xlsx
+++ b/Plan/Table/TestData/00.LocaleData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\인디\FluffyDisdog\Plan\Table\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C94B2BC-9E38-4E0A-B5C2-2C69EF3E0336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8976041-3FC0-43D1-918A-8A6CFA806EE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{ACC90571-B6CD-4C5D-8958-9053FB4EA2D7}"/>
+    <workbookView xWindow="13260" yWindow="5130" windowWidth="14505" windowHeight="13485" xr2:uid="{17669B23-41F7-4FCA-81B6-1834F83E7404}"/>
   </bookViews>
   <sheets>
     <sheet name="00.LocaleData" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="1054">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="1086">
   <si>
     <t>key</t>
   </si>
@@ -2504,7 +2504,7 @@
     <t>relic116_Des</t>
   </si>
   <si>
-    <t>타일 파괴 실패 시, 해당 타일이 30% 확률로 균열 타일로 변경된다.</t>
+    <t>타일 파괴 실패 시, 해당 타일이 균열 타일로 변경된다.</t>
   </si>
   <si>
     <t>Upon failing to destroy a tile, there is a 30% chance the tile changes into a Rift tile.</t>
@@ -3201,6 +3201,102 @@
   </si>
   <si>
     <t>마법_설명</t>
+  </si>
+  <si>
+    <t>Card_Dummy_100_Name</t>
+  </si>
+  <si>
+    <t>그레이트 소드</t>
+  </si>
+  <si>
+    <t>Dummy_Text</t>
+  </si>
+  <si>
+    <t>Card_Dummy_101_Name</t>
+  </si>
+  <si>
+    <t>그레이트 소드+</t>
+  </si>
+  <si>
+    <t>Card_Dummy_200_Name</t>
+  </si>
+  <si>
+    <t>실버 스피어</t>
+  </si>
+  <si>
+    <t>Card_Dummy_201_Name</t>
+  </si>
+  <si>
+    <t>실버 스피어+</t>
+  </si>
+  <si>
+    <t>Card_Dummy_300_Name</t>
+  </si>
+  <si>
+    <t>스네이크 윕</t>
+  </si>
+  <si>
+    <t>Card_Dummy_301_Name</t>
+  </si>
+  <si>
+    <t>스네이크 윕+</t>
+  </si>
+  <si>
+    <t>Card_Dummy_400_Name</t>
+  </si>
+  <si>
+    <t>장궁</t>
+  </si>
+  <si>
+    <t>Card_Dummy_401_Name</t>
+  </si>
+  <si>
+    <t>장궁+</t>
+  </si>
+  <si>
+    <t>Card_Dummy_100_Des</t>
+  </si>
+  <si>
+    <t>&lt;#fbc531&gt; ■&lt;/color&gt; 100% 파괴 &lt;br&gt;&lt;#49e3da&gt; ■&lt;/color&gt; 66% 파괴&lt;br&gt;&lt;#efefe9&gt; ■&lt;/color&gt; 33% 파괴</t>
+  </si>
+  <si>
+    <t>Card_Dummy_101_Des</t>
+  </si>
+  <si>
+    <t>&lt;#fbc531&gt; ■&lt;/color&gt; 100% 파괴 &lt;br&gt;&lt;#49e3da&gt; ■&lt;/color&gt; 75% 파괴&lt;br&gt;&lt;#efefe9&gt; ■&lt;/color&gt; 50% 파괴</t>
+  </si>
+  <si>
+    <t>Card_Dummy_200_Des</t>
+  </si>
+  <si>
+    <t>&lt;#49e3da&gt; ■&lt;/color&gt; 75% 파괴 &lt;br&gt;&lt;#efefe9&gt; ■&lt;/color&gt; 50% 파괴&lt;br&gt;&lt;#fbc531&gt; ■&lt;/color&gt; 25% 파괴</t>
+  </si>
+  <si>
+    <t>Card_Dummy_201_Des</t>
+  </si>
+  <si>
+    <t>&lt;#49e3da&gt; ■&lt;/color&gt; 100% 파괴 &lt;br&gt;&lt;#efefe9&gt; ■&lt;/color&gt; 75% 파괴&lt;br&gt;&lt;#fbc531&gt; ■&lt;/color&gt; 50% 파괴</t>
+  </si>
+  <si>
+    <t>Card_Dummy_300_Des</t>
+  </si>
+  <si>
+    <t>&lt;#efefe9&gt; ■&lt;/color&gt; 66% 파괴&lt;br&gt;&lt;#fbc531&gt; ■&lt;/color&gt; 33% 파괴</t>
+  </si>
+  <si>
+    <t>Card_Dummy_301_Des</t>
+  </si>
+  <si>
+    <t>Card_Dummy_400_Des</t>
+  </si>
+  <si>
+    <t>&lt;#efefe9&gt; ■&lt;/color&gt; 99% 파괴&lt;br&gt;&lt;#fbc531&gt; ■&lt;/color&gt; 1% 파괴</t>
+  </si>
+  <si>
+    <t>Card_Dummy_401_Des</t>
+  </si>
+  <si>
+    <t>&lt;#efefe9&gt; ■&lt;/color&gt; 99% 파괴&lt;br&gt;&lt;#49e3da&gt; ■&lt;/color&gt; 75% 파괴 &lt;br&gt;&lt;#fbc531&gt; ■&lt;/color&gt; 1% 파괴</t>
   </si>
 </sst>
 </file>
@@ -3583,8 +3679,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E2C2F42-74FE-4D83-8AC1-7B5D5D77C5DD}">
-  <dimension ref="A1:C363"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABDA5425-8E78-468F-B44E-6A8F768C91BE}">
+  <dimension ref="A1:C379"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -7580,6 +7676,182 @@
         <v>1035</v>
       </c>
     </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A364" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B364" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C364" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A365" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B365" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C365" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A366" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B366" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C366" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A367" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B367" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C367" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A368" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B368" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C368" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A369" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B369" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C369" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A370" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B370" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C370" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A371" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B371" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C371" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A372" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B372" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C372" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A373" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B373" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C373" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A374" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B374" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C374" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A375" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B375" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C375" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A376" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B376" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C376" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A377" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B377" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C377" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A378" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B378" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C378" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A379" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B379" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C379" t="s">
+        <v>1056</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Plan/Table/TestData/00.LocaleData.xlsx
+++ b/Plan/Table/TestData/00.LocaleData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\인디\FluffyDisdog\Plan\Table\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8976041-3FC0-43D1-918A-8A6CFA806EE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EBC195C2-731F-4BBF-990B-804056D5E6F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13260" yWindow="5130" windowWidth="14505" windowHeight="13485" xr2:uid="{17669B23-41F7-4FCA-81B6-1834F83E7404}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{2F7D3B21-FE3C-4C8C-855C-78A3CF90E2F9}"/>
   </bookViews>
   <sheets>
     <sheet name="00.LocaleData" sheetId="1" r:id="rId1"/>
@@ -995,7 +995,7 @@
     <t>Card_ConcentratedCrossDrill_Des</t>
   </si>
   <si>
-    <t>&lt;#fbc531&gt; ■&lt;/color&gt; 100% 파괴 &lt;br&gt;&lt;#efefe9&gt; ■ ↖↗↙↘&lt;/color&gt; 33% 파괴&lt;br&gt;&lt;#efefe9&gt; ■ ←↑↓→&lt;/color&gt; 66% 파괴</t>
+    <t>&lt;#fbc531&gt; ■&lt;/color&gt; 100% 파괴 &lt;br&gt;&lt;#efefe9&gt; ■ ↖↗↙↘&lt;/color&gt; 66% 파괴&lt;br&gt;&lt;#efefe9&gt; ■ ←↑↓→&lt;/color&gt; 33% 파괴</t>
   </si>
   <si>
     <t>Destroys tiles in the yellow attack range with 100% chance.\\nDestroys tiles in the white attack range diagonal to the yellow tile with 66% chance.\\nDestroys tiles in the white attack range adjacent to the yellow tile with 33% chance.\\n(Tool) This card may be destroyed upon use.\\nUpgrading this card removes the destruction effect.</t>
@@ -3679,7 +3679,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABDA5425-8E78-468F-B44E-6A8F768C91BE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D413E684-54D9-490B-AA42-9D51B27F4B3E}">
   <dimension ref="A1:C379"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
